--- a/data/病人设定.xlsx
+++ b/data/病人设定.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2359" uniqueCount="1392">
   <si>
     <t>情境编号</t>
   </si>
@@ -2205,6 +2205,2004 @@
   </si>
   <si>
     <t>患者行颈椎肿瘤切除内固定+肋骨肿瘤切除术，术后症状好转。病理确诊肺来源转移性腺癌。家属咨询后续治疗方案。请你向家属解释后续治疗（化疗、靶向等）及预后。</t>
+  </si>
+  <si>
+    <t>“脑中风的警报”</t>
+  </si>
+  <si>
+    <t>突发右侧肢体无力、麻木，言语不清，口角左偏</t>
+  </si>
+  <si>
+    <t>右侧鼻唇沟变浅，右侧肢体肌力2级，右侧巴氏征(+)</t>
+  </si>
+  <si>
+    <t>头颅CT未见出血；血压160/95mmHg</t>
+  </si>
+  <si>
+    <t>高血压10年</t>
+  </si>
+  <si>
+    <t>紧张、恐惧</t>
+  </si>
+  <si>
+    <t>不知道发生了什么</t>
+  </si>
+  <si>
+    <t>我这是中风了吗？能治好吗？</t>
+  </si>
+  <si>
+    <t>急性缺血性脑卒中</t>
+  </si>
+  <si>
+    <t>张大爷，68岁，有高血压史，晨起突然出现右侧肢体无力、麻木，言语不清，口角左偏。急诊头颅CT未见出血，考虑急性缺血性脑卒中。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>右侧肢体无力仍明显，言语稍好转</t>
+  </si>
+  <si>
+    <t>血压150/90mmHg，右侧肌力3级</t>
+  </si>
+  <si>
+    <t>MRI示左侧大脑中动脉区梗死；颈动脉超声示左侧颈内动脉斑块</t>
+  </si>
+  <si>
+    <t>知道是脑梗，但担心后遗症</t>
+  </si>
+  <si>
+    <t>能不能溶栓？会不会瘫痪？</t>
+  </si>
+  <si>
+    <t>脑梗死（急性期）</t>
+  </si>
+  <si>
+    <t>错过溶栓窗</t>
+  </si>
+  <si>
+    <t>患者入院后血压160/95mmHg，NIHSS评分8分，MRI示左侧大脑中动脉供血区急性梗死。需尽快评估溶栓或取栓治疗。请你向家属解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>康复期</t>
+  </si>
+  <si>
+    <t>右侧肢体肌力恢复至3级，可扶走</t>
+  </si>
+  <si>
+    <t>血压140/85mmHg，右侧肌力3级</t>
+  </si>
+  <si>
+    <t>复查CT示梗死灶稳定</t>
+  </si>
+  <si>
+    <t>病情稳定，但担心复发</t>
+  </si>
+  <si>
+    <t>以后要怎么预防？还能恢复到正常吗？</t>
+  </si>
+  <si>
+    <t>脑梗死（恢复期）</t>
+  </si>
+  <si>
+    <t>二级预防中</t>
+  </si>
+  <si>
+    <t>患者错过溶栓时间窗，给予抗血小板、降脂、康复治疗。病情稳定但右侧肢体肌力仍3级，需长期二级预防。请你向患者及家属说明后续治疗及康复计划。</t>
+  </si>
+  <si>
+    <t>右侧肢体肌力4级，言语清晰</t>
+  </si>
+  <si>
+    <t>血压135/80mmHg，右侧肌力4级</t>
+  </si>
+  <si>
+    <t>各项指标平稳</t>
+  </si>
+  <si>
+    <t>出院后要注意什么？药要吃多久？</t>
+  </si>
+  <si>
+    <t>已行二级预防指导</t>
+  </si>
+  <si>
+    <t>出院前患者右侧肢体肌力恢复至4级，言语清晰。需指导二级预防药物（阿司匹林、他汀）、生活方式调整及定期随访。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“半身风云”</t>
+  </si>
+  <si>
+    <t>“惊厥之舞”</t>
+  </si>
+  <si>
+    <t>突发意识丧失、四肢抽搐、口吐白沫，发作后昏睡</t>
+  </si>
+  <si>
+    <t>生命体征平稳，神经系统（-）</t>
+  </si>
+  <si>
+    <t>急诊生化正常，头颅CT未见异常</t>
+  </si>
+  <si>
+    <t>紧张、困惑</t>
+  </si>
+  <si>
+    <t>我怎么会突然抽搐？</t>
+  </si>
+  <si>
+    <t>癫痫待查</t>
+  </si>
+  <si>
+    <t>小王，25岁，2小时前在办公室突然意识丧失、倒地、四肢抽搐、口吐白沫，持续约3分钟后自行停止，醒后对发作无记忆。同事呼叫120送诊。既往体健。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>无发作，仍感疲惫</t>
+  </si>
+  <si>
+    <t>脑电图示额区棘慢波，头颅MRI正常</t>
+  </si>
+  <si>
+    <t>知道可能是癫痫，但不确定</t>
+  </si>
+  <si>
+    <t>能治好吗？会不会影响工作？</t>
+  </si>
+  <si>
+    <t>癫痫（全身性发作）</t>
+  </si>
+  <si>
+    <t>患者入院后生命体征平稳，神经系统检查无异常。脑电图示双侧额区棘慢波发放。头颅MRI未见异常。诊断为癫痫（全身性发作）。需开始抗癫痫治疗。请你向患者解释病情。</t>
+  </si>
+  <si>
+    <t>服药后嗜睡，无抽搐</t>
+  </si>
+  <si>
+    <t>血常规、肝功正常，丙戊酸钠血药浓度偏低</t>
+  </si>
+  <si>
+    <t>开始服药，但担心副作用</t>
+  </si>
+  <si>
+    <t>这个药要吃多久？会有什么副作用？</t>
+  </si>
+  <si>
+    <t>已开始丙戊酸钠</t>
+  </si>
+  <si>
+    <t>给予丙戊酸钠治疗后，患者未再发作，但出现轻微嗜睡。需调整剂量并监测血药浓度。请你向患者说明药物副作用及注意事项。</t>
+  </si>
+  <si>
+    <t>无发作，嗜睡好转</t>
+  </si>
+  <si>
+    <t>生命体征平稳，肝功正常</t>
+  </si>
+  <si>
+    <t>复查脑电图较前好转，血药浓度达标</t>
+  </si>
+  <si>
+    <t>病情控制，准备出院</t>
+  </si>
+  <si>
+    <t>出院后要注意什么？能不能开车？</t>
+  </si>
+  <si>
+    <t>癫痫（控制期）</t>
+  </si>
+  <si>
+    <t>准备出院</t>
+  </si>
+  <si>
+    <t>患者病情控制良好，准备出院。需指导长期用药、避免诱因、定期复查脑电图及肝功能。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“隐形的枷锁”</t>
+  </si>
+  <si>
+    <t>情绪低落、兴趣减退、失眠、食欲下降、自杀念头</t>
+  </si>
+  <si>
+    <t>生命体征平稳，精神萎靡</t>
+  </si>
+  <si>
+    <t>PHQ-9 18分，血常规、甲功正常</t>
+  </si>
+  <si>
+    <t>内向</t>
+  </si>
+  <si>
+    <t>沉默寡言</t>
+  </si>
+  <si>
+    <t>不知道为什么会这样</t>
+  </si>
+  <si>
+    <t>我是怎么了？活着没意思</t>
+  </si>
+  <si>
+    <t>中度抑郁发作</t>
+  </si>
+  <si>
+    <t>李女士，35岁，近3个月来情绪低落、兴趣减退、失眠、食欲下降，自觉乏力，有自杀念头，由家属陪同就诊。查体无异常。PHQ-9评分18分。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>情绪仍低落，自杀念头持续</t>
+  </si>
+  <si>
+    <t>评估量表无变化</t>
+  </si>
+  <si>
+    <t>知道是抑郁症，但担心药物</t>
+  </si>
+  <si>
+    <t>吃药会不会上瘾？副作用大吗？</t>
+  </si>
+  <si>
+    <t>患者诊断为中度抑郁发作，建议抗抑郁药物治疗联合心理治疗。家属担心药物副作用及依赖性。请你向患者及家属解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>调整治疗</t>
+  </si>
+  <si>
+    <t>情绪稍好转，出现恶心，睡眠仍差</t>
+  </si>
+  <si>
+    <t>药物调整中</t>
+  </si>
+  <si>
+    <t>开始服药，但副作用难受</t>
+  </si>
+  <si>
+    <t>这药要多久起效？副作用怎么办？</t>
+  </si>
+  <si>
+    <t>服用舍曲林2周</t>
+  </si>
+  <si>
+    <t>给予舍曲林治疗2周后，患者情绪稍好转，但仍睡眠差，出现恶心。需调整方案。请你向患者说明药物起效时间及副作用处理。</t>
+  </si>
+  <si>
+    <t>情绪明显好转，无自杀念头</t>
+  </si>
+  <si>
+    <t>精神可，睡眠改善</t>
+  </si>
+  <si>
+    <t>量表评分显著下降</t>
+  </si>
+  <si>
+    <t>外向</t>
+  </si>
+  <si>
+    <t>以后还要吃药吗？怎么预防复发？</t>
+  </si>
+  <si>
+    <t>抑郁发作（缓解期）</t>
+  </si>
+  <si>
+    <t>治疗8周后，患者情绪明显改善，自杀念头消失，准备出院。需指导继续服药、心理治疗及预防复发。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“心弦紧绷”</t>
+  </si>
+  <si>
+    <t>胸骨后压榨性疼痛，向左肩放射，活动后诱发，休息或含服硝酸甘油可缓解</t>
+  </si>
+  <si>
+    <t>血压145/90mmHg，心率78次/分，心肺听诊无异常</t>
+  </si>
+  <si>
+    <t>心电图：II、III、avF导联ST段压低0.1mV，心肌酶正常</t>
+  </si>
+  <si>
+    <t>高血压、高血脂</t>
+  </si>
+  <si>
+    <t>怎么会心绞痛？严重吗？</t>
+  </si>
+  <si>
+    <t>不稳定心绞痛</t>
+  </si>
+  <si>
+    <t>赵先生，58岁，公司高管，近1周反复出现胸骨后压榨性疼痛，向左肩放射，每次持续5-10分钟，劳累或情绪激动时诱发，休息或含服硝酸甘油可缓解。既往高血压、高血脂史。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>胸痛发作较前减少，仍偶有胸闷</t>
+  </si>
+  <si>
+    <t>血压140/85mmHg，心率72次/分</t>
+  </si>
+  <si>
+    <t>心电图动态改变，心肌酶正常，冠脉CTA示前降支中段狭窄</t>
+  </si>
+  <si>
+    <t>知道是冠心病，但担心支架</t>
+  </si>
+  <si>
+    <t>一定要放支架吗？有没有风险？</t>
+  </si>
+  <si>
+    <t>不稳定心绞痛，冠心病</t>
+  </si>
+  <si>
+    <t>已建议冠脉造影</t>
+  </si>
+  <si>
+    <t>患者入院后心电图示ST段压低，心肌酶正常。考虑不稳定心绞痛，需行冠脉造影评估。家属担心手术风险。请你向患者及家属解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>术后胸痛消失，无不适</t>
+  </si>
+  <si>
+    <t>生命体征平稳，穿刺点愈合好</t>
+  </si>
+  <si>
+    <t>冠脉造影示前降支中段狭窄85%，支架植入后血流通畅</t>
+  </si>
+  <si>
+    <t>手术成功，担心复发</t>
+  </si>
+  <si>
+    <t>放了支架以后要注意什么？还能干活吗？</t>
+  </si>
+  <si>
+    <t>已行PCI术</t>
+  </si>
+  <si>
+    <t>冠脉造影示前降支中段狭窄85%，植入支架1枚，术后胸痛消失。需指导双抗治疗及二级预防。请你向患者说明术后注意事项。</t>
+  </si>
+  <si>
+    <t>无胸痛，精神好</t>
+  </si>
+  <si>
+    <t>血压135/80mmHg，心率70次/分</t>
+  </si>
+  <si>
+    <t>复查心电图正常，血脂、血糖控制可</t>
+  </si>
+  <si>
+    <t>准备出院，关心长期用药</t>
+  </si>
+  <si>
+    <t>药要吃多久？多久复查一次？</t>
+  </si>
+  <si>
+    <t>患者出院前无胸痛发作，需指导长期用药（阿司匹林、氯吡格雷、他汀）、生活方式调整及定期随访。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“心跳乱了”</t>
+  </si>
+  <si>
+    <t>突感心悸、胸闷、气短，伴头晕</t>
+  </si>
+  <si>
+    <t>血压150/90mmHg，心率150次/分，心律绝对不齐，第一心音强弱不等</t>
+  </si>
+  <si>
+    <t>心电图：快速房颤，心室率150次/分</t>
+  </si>
+  <si>
+    <t>从来没这样过</t>
+  </si>
+  <si>
+    <t>我这是怎么了？心脏要跳出来了</t>
+  </si>
+  <si>
+    <t>快速房颤</t>
+  </si>
+  <si>
+    <t>陈大爷，72岁，退休工人，1小时前突感心悸、胸闷、气短，伴头晕，无胸痛。急诊心电图示快速房颤，心室率150次/分。既往高血压史。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>心悸稍好转，但仍感乏力</t>
+  </si>
+  <si>
+    <t>血压130/80mmHg，心率120次/分，心律不齐</t>
+  </si>
+  <si>
+    <t>心脏超声示左房增大，TEE排除左房血栓，CHA2DS2-VASc评分4分，HAS-BLED评分2分</t>
+  </si>
+  <si>
+    <t>知道是房颤，但不知危害</t>
+  </si>
+  <si>
+    <t>会中风吗？能治好吗？</t>
+  </si>
+  <si>
+    <t>房颤（快速型）</t>
+  </si>
+  <si>
+    <t>已开始胺碘酮及抗凝</t>
+  </si>
+  <si>
+    <t>患者入院后血压130/80mmHg，心室率120次/分，予胺碘酮复律及抗凝治疗。需评估卒中风险（CHA2DS2-VASc评分）及出血风险（HAS-BLED评分）。请你向患者及家属解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>转复后</t>
+  </si>
+  <si>
+    <t>心悸消失，精神好转</t>
+  </si>
+  <si>
+    <t>血压125/75mmHg，心率70次/分，律齐</t>
+  </si>
+  <si>
+    <t>心电图示窦性心律，INR未达标</t>
+  </si>
+  <si>
+    <t>转复成功，担心长期吃药</t>
+  </si>
+  <si>
+    <t>抗凝药要吃多久？有副作用吗？</t>
+  </si>
+  <si>
+    <t>房颤（转复后）</t>
+  </si>
+  <si>
+    <t>已开始华法林</t>
+  </si>
+  <si>
+    <t>患者转复为窦性心律，心室率70次/分。需长期抗凝预防卒中，选择华法林或NOAC。请你向患者说明抗凝治疗的必要性及注意事项。</t>
+  </si>
+  <si>
+    <t>血压120/70mmHg，心率68次/分，律齐</t>
+  </si>
+  <si>
+    <t>INR达标（2.0-3.0）</t>
+  </si>
+  <si>
+    <t>准备出院，关心监测</t>
+  </si>
+  <si>
+    <t>多久查一次血？能不能停？</t>
+  </si>
+  <si>
+    <t>房颤（控制期）</t>
+  </si>
+  <si>
+    <t>已用华法林</t>
+  </si>
+  <si>
+    <t>出院前患者病情稳定，需指导长期抗凝、定期监测INR（若用华法林）、控制心率及预防复发。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“泵的挣扎”</t>
+  </si>
+  <si>
+    <t>急诊抢救</t>
+  </si>
+  <si>
+    <t>突发严重呼吸困难、端坐呼吸、咳粉红色泡沫样痰</t>
+  </si>
+  <si>
+    <t>血压210/110mmHg，心率120次/分，双肺满布湿啰音，双下肢水肿</t>
+  </si>
+  <si>
+    <t>急诊血气：PaO2 60mmHg，心电图示左室肥厚，心肌酶轻度升高</t>
+  </si>
+  <si>
+    <t>冠心病史10年，高血压</t>
+  </si>
+  <si>
+    <t>从没这么难受过</t>
+  </si>
+  <si>
+    <t>我是不是快不行了？</t>
+  </si>
+  <si>
+    <t>急性左心衰竭，高血压急症</t>
+  </si>
+  <si>
+    <t>吴大爷，76岁，有冠心病史，3天前受凉后咳嗽、咳痰，今晨突发严重呼吸困难、端坐呼吸、咳粉红色泡沫样痰。急诊血压210/110mmHg，双肺满布湿啰音。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>呼吸困难缓解，但仍乏力、活动后气促</t>
+  </si>
+  <si>
+    <t>血压150/90mmHg，心率95次/分，双肺底少量湿啰音</t>
+  </si>
+  <si>
+    <t>心脏超声示左室射血分数35%，左室扩大，NT-proBNP 5000pg/ml</t>
+  </si>
+  <si>
+    <t>知道是心衰，但不知严重程度</t>
+  </si>
+  <si>
+    <t>能治好吗？以后还能走路吗？</t>
+  </si>
+  <si>
+    <t>急性心衰（缓解期），冠心病</t>
+  </si>
+  <si>
+    <t>已行利尿扩血管治疗</t>
+  </si>
+  <si>
+    <t>患者入院后诊断为急性左心衰，给予吸氧、利尿、扩血管、强心治疗后症状缓解。需明确病因及评估心功能。请你向患者及家属解释病情及治疗。</t>
+  </si>
+  <si>
+    <t>症状平稳，但仍需限制活动</t>
+  </si>
+  <si>
+    <t>血压140/85mmHg，心率85次/分，肺底少量湿啰音</t>
+  </si>
+  <si>
+    <t>复查心脏超声LVEF 35%，24h尿量1800ml</t>
+  </si>
+  <si>
+    <t>知道需要长期吃药</t>
+  </si>
+  <si>
+    <t>药要吃到什么时候？能治根吗？</t>
+  </si>
+  <si>
+    <t>缺血性心肌病，慢性心衰（NYHA Ⅲ级）</t>
+  </si>
+  <si>
+    <t>已开始ACEI/β阻滞剂</t>
+  </si>
+  <si>
+    <t>心脏超声示左室射血分数35%，左室扩大，考虑缺血性心肌病。需长期药物治疗及心衰管理。请你向患者说明长期治疗方案。</t>
+  </si>
+  <si>
+    <t>无呼吸困难，活动耐量改善</t>
+  </si>
+  <si>
+    <t>血压135/80mmHg，心率80次/分，肺底无啰音，下肢无水肿</t>
+  </si>
+  <si>
+    <t>复查NT-proBNP 1500pg/ml，电解质正常</t>
+  </si>
+  <si>
+    <t>回家后要注意什么？多久复查一次？</t>
+  </si>
+  <si>
+    <t>慢性心衰（NYHA Ⅱ级）</t>
+  </si>
+  <si>
+    <t>药物调整稳定</t>
+  </si>
+  <si>
+    <t>出院前患者病情稳定，心功能Ⅱ级，需指导长期用药（ACEI/ARB、β阻滞剂、利尿剂）、限盐限水、监测体重及定期随访。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“喘息的风箱”</t>
+  </si>
+  <si>
+    <t>突发呼吸困难、喘息、胸闷、咳嗽，端坐呼吸</t>
+  </si>
+  <si>
+    <t>呼吸急促，双肺满布哮鸣音，心率110次/分，血压130/80mmHg</t>
+  </si>
+  <si>
+    <t>血常规正常，胸部X线未见异常，血气分析示轻度低氧血症</t>
+  </si>
+  <si>
+    <t>过敏性鼻炎</t>
+  </si>
+  <si>
+    <t>以为是空调吹感冒了</t>
+  </si>
+  <si>
+    <t>怎么突然喘不上气？会憋死吗？</t>
+  </si>
+  <si>
+    <t>哮喘急性发作</t>
+  </si>
+  <si>
+    <t>小刘，25岁，程序员，2小时前加班时突然发作性呼吸困难、喘息、胸闷，伴咳嗽，端坐呼吸，自述有过敏性鼻炎史。急诊查体双肺满布哮鸣音。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>症状缓解，仍感胸闷</t>
+  </si>
+  <si>
+    <t>双肺少量哮鸣音，生命体征平稳</t>
+  </si>
+  <si>
+    <t>肺功能检查：FEV1/FVC 65%，支气管舒张试验阳性，过敏原检测示尘螨强阳性</t>
+  </si>
+  <si>
+    <t>知道是哮喘，但不知如何控制</t>
+  </si>
+  <si>
+    <t>以后还能运动吗？会不会经常发作？</t>
+  </si>
+  <si>
+    <t>支气管哮喘（急性发作后）</t>
+  </si>
+  <si>
+    <t>已行雾化治疗</t>
+  </si>
+  <si>
+    <t>患者入院后予吸氧、雾化吸入β2受体激动剂及糖皮质激素，症状缓解。需进一步明确过敏原及哮喘控制水平。请你向患者解释病情及长期治疗计划。</t>
+  </si>
+  <si>
+    <t>无特殊不适，可平卧</t>
+  </si>
+  <si>
+    <t>双肺呼吸音清，无干湿啰音</t>
+  </si>
+  <si>
+    <t>肺功能基本正常，峰流速监测正常</t>
+  </si>
+  <si>
+    <t>确诊哮喘，需长期用药</t>
+  </si>
+  <si>
+    <t>吸入激素有副作用吗？要吸多久？</t>
+  </si>
+  <si>
+    <t>支气管哮喘（控制期）</t>
+  </si>
+  <si>
+    <t>已开始吸入布地奈德</t>
+  </si>
+  <si>
+    <t>患者肺功能检查示FEV1/FVC&lt;70%，支气管舒张试验阳性，确诊支气管哮喘。需长期吸入激素控制气道炎症。请你向患者说明用药注意事项。</t>
+  </si>
+  <si>
+    <t>峰流速变异率&lt;20%</t>
+  </si>
+  <si>
+    <t>准备出院，关心日常管理</t>
+  </si>
+  <si>
+    <t>平时要注意什么？能不能养宠物？</t>
+  </si>
+  <si>
+    <t>支气管哮喘（稳定期）</t>
+  </si>
+  <si>
+    <t>已行健康教育</t>
+  </si>
+  <si>
+    <t>患者症状控制良好，准备出院。需指导规律用药、峰流速监测、避免诱因及定期复查。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“被困的气泡”</t>
+  </si>
+  <si>
+    <t>打篮球时突发右侧胸痛、呼吸困难，深吸气加重</t>
+  </si>
+  <si>
+    <t>右肺呼吸音消失，叩诊鼓音，气管居中</t>
+  </si>
+  <si>
+    <t>胸部X线示右侧气胸，肺压缩约40%</t>
+  </si>
+  <si>
+    <t>以为是肌肉拉伤</t>
+  </si>
+  <si>
+    <t>怎么突然喘不上气？严重吗？</t>
+  </si>
+  <si>
+    <t>自发性气胸</t>
+  </si>
+  <si>
+    <t>小张，22岁，大学生，打篮球时突然右侧胸痛、呼吸困难，呈针刺样疼痛，深吸气加重。既往体健。急诊查体右肺呼吸音消失。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>胸痛稍缓，仍胸闷</t>
+  </si>
+  <si>
+    <t>右肺呼吸音低，叩诊鼓音</t>
+  </si>
+  <si>
+    <t>胸部CT示右肺尖肺大疱，肺压缩40%</t>
+  </si>
+  <si>
+    <t>知道是气胸，但害怕引流</t>
+  </si>
+  <si>
+    <t>一定要插管子吗？能不能自己吸收？</t>
+  </si>
+  <si>
+    <t>自发性气胸（肺压缩40%）</t>
+  </si>
+  <si>
+    <t>肺大疱患者入院后胸部X线示右侧气胸，肺压缩约40%。需行胸腔闭式引流。患者害怕手术。请你向患者解释病情及治疗必要性。</t>
+  </si>
+  <si>
+    <t>症状明显缓解，无胸痛</t>
+  </si>
+  <si>
+    <t>引流管在位，无气泡逸出，水柱波动正常</t>
+  </si>
+  <si>
+    <t>复查X线示肺复张良好</t>
+  </si>
+  <si>
+    <t>引流后好转，担心拔管</t>
+  </si>
+  <si>
+    <t>管子要插多久？拔管疼吗？</t>
+  </si>
+  <si>
+    <t>气胸（引流术后）</t>
+  </si>
+  <si>
+    <t>已行闭式引流</t>
+  </si>
+  <si>
+    <t>行胸腔闭式引流后，症状缓解，引流管在位。需观察有无漏气及肺复张情况。请你向患者说明术后注意事项。</t>
+  </si>
+  <si>
+    <t>无不适，伤口愈合好</t>
+  </si>
+  <si>
+    <t>生命体征平稳，双肺呼吸音清</t>
+  </si>
+  <si>
+    <t>拔管后X线示肺完全复张</t>
+  </si>
+  <si>
+    <t>准备出院，关心复发</t>
+  </si>
+  <si>
+    <t>以后还能打球吗？会不会复发？</t>
+  </si>
+  <si>
+    <t>自发性气胸（治愈）</t>
+  </si>
+  <si>
+    <t>已拔管</t>
+  </si>
+  <si>
+    <t>拔管后复查X线示肺完全复张，准备出院。需指导避免剧烈运动、潜水及乘飞机，预防复发。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“沉默的阴影”</t>
+  </si>
+  <si>
+    <t>刺激性干咳3个月，痰中带血丝，消瘦、乏力</t>
+  </si>
+  <si>
+    <t>生命体征平稳，右肺呼吸音稍低，无啰音</t>
+  </si>
+  <si>
+    <t>胸部X线示右肺门肿块影，血常规正常</t>
+  </si>
+  <si>
+    <t>长期吸烟（40包年）</t>
+  </si>
+  <si>
+    <t>紧张、隐瞒</t>
+  </si>
+  <si>
+    <t>以为是抽烟引起的咳嗽</t>
+  </si>
+  <si>
+    <t>咳嗽带血是不是肺癌？</t>
+  </si>
+  <si>
+    <t>肺癌待查</t>
+  </si>
+  <si>
+    <t>老李，65岁，退休工人，长期吸烟（40包年），近3个月出现刺激性干咳、痰中带血丝，伴消瘦、乏力。胸部X线示右肺门肿块影。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>咳嗽如前，无明显加重</t>
+  </si>
+  <si>
+    <t>右肺呼吸音低，无其他阳性体征</t>
+  </si>
+  <si>
+    <t>胸部CT示右肺上叶占位，纵隔淋巴结肿大；支气管镜活检示肺鳞癌；肿瘤标志物CYFRA21-1升高</t>
+  </si>
+  <si>
+    <t>担忧、恐惧</t>
+  </si>
+  <si>
+    <t>知道是肺癌，但不知分期</t>
+  </si>
+  <si>
+    <t>还能治吗？要不要化疗？</t>
+  </si>
+  <si>
+    <t>右肺鳞癌</t>
+  </si>
+  <si>
+    <t>待分期</t>
+  </si>
+  <si>
+    <t>患者入院后胸部CT示右肺上叶占位，伴纵隔淋巴结肿大。支气管镜活检病理回报：肺鳞癌。需进一步分期及制定治疗方案。请你向患者及家属解释病情。</t>
+  </si>
+  <si>
+    <t>治疗选择</t>
+  </si>
+  <si>
+    <t>等待治疗，焦虑</t>
+  </si>
+  <si>
+    <t>PET-CT示ⅢA期（N2），肺功能、心功能可耐受手术</t>
+  </si>
+  <si>
+    <t>知道分期，但不知选哪种治疗</t>
+  </si>
+  <si>
+    <t>新辅助化疗和直接手术哪个好？放疗副作用大吗？</t>
+  </si>
+  <si>
+    <t>肺鳞癌（ⅢA期）</t>
+  </si>
+  <si>
+    <t>已行PET-CT</t>
+  </si>
+  <si>
+    <t>患者经PET-CT评估为ⅢA期（N2），建议新辅助化疗后手术，或同步放化疗。家属犹豫不决。请你向家属解释不同治疗方案的利弊。</t>
+  </si>
+  <si>
+    <t>术后恢复良好，无咳嗽、胸痛</t>
+  </si>
+  <si>
+    <t>生命体征平稳，伤口愈合好</t>
+  </si>
+  <si>
+    <t>术后病理示淋巴结阴性，切缘阴性</t>
+  </si>
+  <si>
+    <t>手术成功，准备出院</t>
+  </si>
+  <si>
+    <t>以后要注意什么？多久复查一次？</t>
+  </si>
+  <si>
+    <t>肺鳞癌术后</t>
+  </si>
+  <si>
+    <t>已行新辅助化疗+手术</t>
+  </si>
+  <si>
+    <t>患者选择新辅助化疗后手术，术后恢复良好，准备出院。需指导定期复查、戒烟及康复。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“胃里的火山”</t>
+  </si>
+  <si>
+    <t>上腹部隐痛，饥饿时加重，进食可缓解，夜间痛醒</t>
+  </si>
+  <si>
+    <t>腹部无明显压痛，生命体征平稳</t>
+  </si>
+  <si>
+    <t>胃镜示十二指肠球部溃疡，Hp阳性</t>
+  </si>
+  <si>
+    <t>紧张，反复问是不是癌症</t>
+  </si>
+  <si>
+    <t>以为是胃炎，但总不好</t>
+  </si>
+  <si>
+    <t>为什么总是饿得疼？会不会癌变？</t>
+  </si>
+  <si>
+    <t>十二指肠球部溃疡</t>
+  </si>
+  <si>
+    <t>赵先生，38岁，销售经理，工作压力大，饮食不规律，近2月上腹痛反复发作，饥饿时明显，夜间常痛醒。来门诊就诊。</t>
+  </si>
+  <si>
+    <t>入院后确诊</t>
+  </si>
+  <si>
+    <t>腹痛减轻，仍时有饥饿不适</t>
+  </si>
+  <si>
+    <t>腹部柔软，无压痛</t>
+  </si>
+  <si>
+    <t>胃镜示A1期溃疡，活检良性，Hp阳性</t>
+  </si>
+  <si>
+    <t>担忧治疗过程</t>
+  </si>
+  <si>
+    <t>知道是溃疡和Hp感染</t>
+  </si>
+  <si>
+    <t>怎么治？多久能好？</t>
+  </si>
+  <si>
+    <t>十二指肠球部溃疡（活动期）</t>
+  </si>
+  <si>
+    <t>Hp阳性</t>
+  </si>
+  <si>
+    <t>患者胃镜结果示十二指肠球部溃疡，活检良性，Hp阳性。医生建议住院抗Hp治疗，患者担心影响工作，犹豫不决。</t>
+  </si>
+  <si>
+    <t>治疗中期</t>
+  </si>
+  <si>
+    <t>症状消失，精神好转</t>
+  </si>
+  <si>
+    <t>复查胃镜溃疡明显缩小，Hp转阴</t>
+  </si>
+  <si>
+    <t>乐观，但仍担心复发</t>
+  </si>
+  <si>
+    <t>知道治疗有效，担心不彻底</t>
+  </si>
+  <si>
+    <t>还需要继续吃药吗？什么时候能好？</t>
+  </si>
+  <si>
+    <t>Hp已根除</t>
+  </si>
+  <si>
+    <t>患者完成2周抗Hp治疗及4周抑酸治疗，症状消失，复查胃镜示溃疡缩小但未完全愈合，Hp转阴。询问后续治疗。</t>
+  </si>
+  <si>
+    <t>胃镜示溃疡完全愈合</t>
+  </si>
+  <si>
+    <t>积极，关心预防</t>
+  </si>
+  <si>
+    <t>溃疡已愈，担心复发</t>
+  </si>
+  <si>
+    <t>十二指肠球部溃疡（瘢痕期）</t>
+  </si>
+  <si>
+    <t>已康复</t>
+  </si>
+  <si>
+    <t>患者溃疡完全愈合，准备出院。医生进行出院指导。</t>
+  </si>
+  <si>
+    <t>“肝胆风云”</t>
+  </si>
+  <si>
+    <t>右上腹剧痛，向右肩放射，恶心呕吐</t>
+  </si>
+  <si>
+    <t>体温37.8℃，右上腹压痛，墨菲征阳性</t>
+  </si>
+  <si>
+    <t>血常规WBC 12×10⁹/L，B超示胆囊多发结石，胆囊壁增厚</t>
+  </si>
+  <si>
+    <t>高血压5年</t>
+  </si>
+  <si>
+    <t>急躁</t>
+  </si>
+  <si>
+    <t>痛苦，大声喊叫</t>
+  </si>
+  <si>
+    <t>以为是胃痛</t>
+  </si>
+  <si>
+    <t>为什么这么疼？要不要手术？</t>
+  </si>
+  <si>
+    <t>胆囊结石伴急性胆囊炎</t>
+  </si>
+  <si>
+    <t>王阿姨，52岁，体型偏胖，喜食油腻。2天前婚宴后突发右上腹剧痛，向右肩放射，伴恶心呕吐。急诊就诊。</t>
+  </si>
+  <si>
+    <t>住院保守治疗</t>
+  </si>
+  <si>
+    <t>腹痛减轻，但仍感右上腹隐痛</t>
+  </si>
+  <si>
+    <t>生命体征平稳，墨菲征阴性</t>
+  </si>
+  <si>
+    <t>复查B超胆囊结石，炎症消退，肝功能正常</t>
+  </si>
+  <si>
+    <t>仍担心手术</t>
+  </si>
+  <si>
+    <t>知道是胆囊炎，但怕开刀</t>
+  </si>
+  <si>
+    <t>可以不手术吗？以后怎么办？</t>
+  </si>
+  <si>
+    <t>胆囊结石、慢性胆囊炎</t>
+  </si>
+  <si>
+    <t>患者经抗感染、解痉治疗后症状缓解，但B超仍见胆囊结石。医生建议择期手术，患者犹豫不决。</t>
+  </si>
+  <si>
+    <t>术后并发症</t>
+  </si>
+  <si>
+    <t>术后3天腹痛、发热、黄疸</t>
+  </si>
+  <si>
+    <t>体温39℃，皮肤巩膜黄染</t>
+  </si>
+  <si>
+    <t>肝功能示梗阻性黄疸，B超胆总管扩张，MRCP示胆总管残余结石</t>
+  </si>
+  <si>
+    <t>慌乱、害怕</t>
+  </si>
+  <si>
+    <t>以为手术成功，却又出问题</t>
+  </si>
+  <si>
+    <t>为什么又痛了？是不是手术失败了？</t>
+  </si>
+  <si>
+    <t>胆囊切除术后，胆总管残余结石</t>
+  </si>
+  <si>
+    <t>已行ERCP</t>
+  </si>
+  <si>
+    <t>患者行腹腔镜胆囊切除术后出现腹痛、发热、黄疸，诊断为胆总管残余结石，需行ERCP取石。患者情绪紧张，需解释病情。</t>
+  </si>
+  <si>
+    <t>康复出院</t>
+  </si>
+  <si>
+    <t>无不适，皮肤黄染消退</t>
+  </si>
+  <si>
+    <t>复查肝功能正常，B超未见异常</t>
+  </si>
+  <si>
+    <t>感激，关心今后</t>
+  </si>
+  <si>
+    <t>知道已治愈，担心复发</t>
+  </si>
+  <si>
+    <t>回家后能吃什么？要注意什么？</t>
+  </si>
+  <si>
+    <t>胆囊切除术后</t>
+  </si>
+  <si>
+    <t>患者行ERCP取石后恢复良好，准备出院。医生进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“肠路惊魂”</t>
+  </si>
+  <si>
+    <t>排便习惯改变，便血，消瘦</t>
+  </si>
+  <si>
+    <t>腹部无明显包块，直肠指诊可触及肿物</t>
+  </si>
+  <si>
+    <t>血CEA升高，结肠镜示直肠癌</t>
+  </si>
+  <si>
+    <t>少言，但焦虑</t>
+  </si>
+  <si>
+    <t>以为是痔疮</t>
+  </si>
+  <si>
+    <t>便血是不是痔疮？</t>
+  </si>
+  <si>
+    <t>直肠癌待查</t>
+  </si>
+  <si>
+    <t>陈大爷，68岁，退休工人，近3月排便习惯改变，便秘与腹泻交替，大便带血，血色暗红，里急后重感，体重下降约5kg。来门诊就诊。</t>
+  </si>
+  <si>
+    <t>症状同前，无明显加重</t>
+  </si>
+  <si>
+    <t>生命体征平稳，腹部未及包块</t>
+  </si>
+  <si>
+    <t>结肠镜及病理示直肠腺癌，CT示淋巴结转移，无远处转移</t>
+  </si>
+  <si>
+    <t>沉默</t>
+  </si>
+  <si>
+    <t>仍少言，但眼神透出恐惧</t>
+  </si>
+  <si>
+    <t>知道是癌，但不知怎么办</t>
+  </si>
+  <si>
+    <t>能治吗？要开刀吗？</t>
+  </si>
+  <si>
+    <t>直肠癌（Ⅲ期）</t>
+  </si>
+  <si>
+    <t>患者住院后完善检查，确诊为直肠癌Ⅲ期。医生建议手术+辅助治疗。患者及家属十分担心，需沟通病情。</t>
+  </si>
+  <si>
+    <t>术后康复</t>
+  </si>
+  <si>
+    <t>术后恢复尚可，偶有腹部不适</t>
+  </si>
+  <si>
+    <t>伤口愈合良好，生命体征平稳</t>
+  </si>
+  <si>
+    <t>术后病理示淋巴结转移，脉管侵犯</t>
+  </si>
+  <si>
+    <t>仍沉默，但逐渐接受</t>
+  </si>
+  <si>
+    <t>知道手术成功，但担心后续治疗</t>
+  </si>
+  <si>
+    <t>还要化疗吗？会不会复发？</t>
+  </si>
+  <si>
+    <t>直肠癌术后（Ⅲ期）</t>
+  </si>
+  <si>
+    <t>患者行直肠癌低位前切除术，术后病理证实淋巴结转移。需行辅助化疗。患者对化疗恐惧，需解释。</t>
+  </si>
+  <si>
+    <t>化疗后随访</t>
+  </si>
+  <si>
+    <t>化疗完成，无特殊不适</t>
+  </si>
+  <si>
+    <t>复查CT无复发转移，CEA正常</t>
+  </si>
+  <si>
+    <t>知道病情稳定，关心长期管理</t>
+  </si>
+  <si>
+    <t>以后要怎么复查？饮食注意什么？</t>
+  </si>
+  <si>
+    <t>直肠癌术后（缓解期）</t>
+  </si>
+  <si>
+    <t>完成辅助化疗</t>
+  </si>
+  <si>
+    <t>患者完成辅助化疗，恢复良好。准备出院，进行长期随访指导。</t>
+  </si>
+  <si>
+    <t>“石破天惊”</t>
+  </si>
+  <si>
+    <t>右侧腰腹部剧痛，向会阴放射，恶心呕吐</t>
+  </si>
+  <si>
+    <t>痛苦面容，辗转不安，右肾区叩痛</t>
+  </si>
+  <si>
+    <t>尿常规：红细胞满视野，腹部X线平片示右输尿管中段阳性结石</t>
+  </si>
+  <si>
+    <t>以为吃坏肚子</t>
+  </si>
+  <si>
+    <t>为什么这么疼？是不是肾坏了？</t>
+  </si>
+  <si>
+    <t>右输尿管结石</t>
+  </si>
+  <si>
+    <t>李先生，45岁，建筑工人，1小时前突发右腰腹部绞痛，向下放射，伴恶心呕吐。急诊就诊。</t>
+  </si>
+  <si>
+    <t>保守治疗期</t>
+  </si>
+  <si>
+    <t>疼痛缓解，仍感腰部不适</t>
+  </si>
+  <si>
+    <t>生命体征平稳，右肾区轻叩痛</t>
+  </si>
+  <si>
+    <t>尿常规：红细胞减少，复查X线示结石位置同前</t>
+  </si>
+  <si>
+    <t>稍缓和，仍担心</t>
+  </si>
+  <si>
+    <t>知道是结石，但不想手术</t>
+  </si>
+  <si>
+    <t>能吃药排掉吗？要做手术吗？</t>
+  </si>
+  <si>
+    <t>已行解痉止痛</t>
+  </si>
+  <si>
+    <t>患者经解痉止痛后疼痛缓解，但结石仍在。医生建议ESWL，患者担心费用和效果。</t>
+  </si>
+  <si>
+    <t>无特殊不适</t>
+  </si>
+  <si>
+    <t>术后复查X线示结石消失</t>
+  </si>
+  <si>
+    <t>还会再长结石吗？以后要注意什么？</t>
+  </si>
+  <si>
+    <t>右输尿管结石术后</t>
+  </si>
+  <si>
+    <t>已行ESWL+输尿管镜</t>
+  </si>
+  <si>
+    <t>患者行ESWL无效后，接受输尿管镜碎石，手术顺利。恢复良好。</t>
+  </si>
+  <si>
+    <t>无特殊</t>
+  </si>
+  <si>
+    <t>回家后怎么预防？多久复查？</t>
+  </si>
+  <si>
+    <t>患者准备出院，医生进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“隐秘的河流”</t>
+  </si>
+  <si>
+    <t>双下肢水肿，尿泡沫增多，乏力</t>
+  </si>
+  <si>
+    <t>血压150/95mmHg，双下肢轻度凹陷性水肿</t>
+  </si>
+  <si>
+    <t>尿常规：蛋白2+，红细胞+，血肌酐105μmol/L</t>
+  </si>
+  <si>
+    <t>沉默，但焦虑</t>
+  </si>
+  <si>
+    <t>以为累的，没重视</t>
+  </si>
+  <si>
+    <t>为什么肿？是不是肾有问题？</t>
+  </si>
+  <si>
+    <t>慢性肾小球肾炎待查</t>
+  </si>
+  <si>
+    <t>张女士，38岁，公司职员，近2月双下肢水肿，尿泡沫增多，伴乏力、腰酸。门诊就诊。</t>
+  </si>
+  <si>
+    <t>血压145/90mmHg，水肿无明显变化</t>
+  </si>
+  <si>
+    <t>24h尿蛋白1.5g，eGFR 65ml/min，免疫学检查阴性</t>
+  </si>
+  <si>
+    <t>仍沉默，但表现出担忧</t>
+  </si>
+  <si>
+    <t>知道可能是肾炎，但不知严重程度</t>
+  </si>
+  <si>
+    <t>能治好吗？会不会尿毒症？</t>
+  </si>
+  <si>
+    <t>慢性肾小球肾炎</t>
+  </si>
+  <si>
+    <t>患者住院后检查明确为慢性肾炎。医生建议长期药物治疗，患者担心终身服药和预后。</t>
+  </si>
+  <si>
+    <t>治疗随访</t>
+  </si>
+  <si>
+    <t>服药后水肿消退，但乏力依旧</t>
+  </si>
+  <si>
+    <t>血压130/80mmHg，无水肿</t>
+  </si>
+  <si>
+    <t>尿蛋白0.8g，血肌酐升至130μmol/L，eGFR 50ml/min</t>
+  </si>
+  <si>
+    <t>情绪低落，焦虑</t>
+  </si>
+  <si>
+    <t>知道病情在进展</t>
+  </si>
+  <si>
+    <t>肌酐为什么还高？会肾衰竭吗？</t>
+  </si>
+  <si>
+    <t>慢性肾小球肾炎（肾功能减退）</t>
+  </si>
+  <si>
+    <t>服用ACEI</t>
+  </si>
+  <si>
+    <t>患者坚持治疗，但肾功能缓慢下降。需进一步调整方案。</t>
+  </si>
+  <si>
+    <t>长期随访</t>
+  </si>
+  <si>
+    <t>乏力、食欲减退，无水肿</t>
+  </si>
+  <si>
+    <t>血压130/85mmHg，贫血貌</t>
+  </si>
+  <si>
+    <t>血肌酐350μmol/L，eGFR 20ml/min，Hb 95g/L，血磷高</t>
+  </si>
+  <si>
+    <t>平静但接受现实</t>
+  </si>
+  <si>
+    <t>知道肾功能差，准备透析</t>
+  </si>
+  <si>
+    <t>什么时候开始透析？能换肾吗？</t>
+  </si>
+  <si>
+    <t>慢性肾衰竭（CKD4期）</t>
+  </si>
+  <si>
+    <t>患者肾功能逐渐下降，eGFR 20ml/min，出现肾性贫血、钙磷代谢紊乱，需准备肾脏替代治疗。</t>
+  </si>
+  <si>
+    <t>“火海警报”</t>
+  </si>
+  <si>
+    <t>尿频、尿急、尿痛，寒战高热</t>
+  </si>
+  <si>
+    <t>体温39.2℃，右肾区叩痛</t>
+  </si>
+  <si>
+    <t>尿常规：白细胞满视野，亚硝酸盐(+)</t>
+  </si>
+  <si>
+    <t>急躁，痛苦</t>
+  </si>
+  <si>
+    <t>以为是普通尿路感染</t>
+  </si>
+  <si>
+    <t>为什么发烧？是不是很严重？</t>
+  </si>
+  <si>
+    <t>急性肾盂肾炎</t>
+  </si>
+  <si>
+    <t>王女士，28岁，教师，2天前劳累后出现尿路刺激症状，今晨高热、腰痛。急诊就诊。</t>
+  </si>
+  <si>
+    <t>热退，但仍腰痛</t>
+  </si>
+  <si>
+    <t>体温37.5℃，右肾区轻叩痛</t>
+  </si>
+  <si>
+    <t>尿培养示大肠埃希菌，药敏敏感，B超未见明显异常</t>
+  </si>
+  <si>
+    <t>知道是肾盂肾炎，但担心反复</t>
+  </si>
+  <si>
+    <t>会变慢性吗？要治多久？</t>
+  </si>
+  <si>
+    <t>抗生素治疗中</t>
+  </si>
+  <si>
+    <t>患者经抗生素治疗，体温下降，但仍有腰痛。需继续治疗。</t>
+  </si>
+  <si>
+    <t>发现结石</t>
+  </si>
+  <si>
+    <t>腰痛反复，时有胀痛</t>
+  </si>
+  <si>
+    <t>生命体征平稳，右肾区叩痛</t>
+  </si>
+  <si>
+    <t>B超示右肾轻度积水，CT示右输尿管中段结石</t>
+  </si>
+  <si>
+    <t>知道有结石，害怕手术</t>
+  </si>
+  <si>
+    <t>一定要手术吗？能不能保守？</t>
+  </si>
+  <si>
+    <t>急性肾盂肾炎，右输尿管结石</t>
+  </si>
+  <si>
+    <t>感染控制后处理结石</t>
+  </si>
+  <si>
+    <t>患者感染控制后，B超发现输尿管结石，导致引流不畅。需处理结石。</t>
+  </si>
+  <si>
+    <t>术后复查无异常</t>
+  </si>
+  <si>
+    <t>手术成功，恢复良好</t>
+  </si>
+  <si>
+    <t>以后怎么预防感染和结石？</t>
+  </si>
+  <si>
+    <t>已行碎石取石</t>
+  </si>
+  <si>
+    <t>患者行输尿管镜碎石取石术，术后恢复良好，准备出院。</t>
+  </si>
+  <si>
+    <t>“折翼天使”</t>
+  </si>
+  <si>
+    <t>右肘肿胀、剧痛，不敢活动</t>
+  </si>
+  <si>
+    <t>右肘肿胀，有压痛，桡动脉搏动减弱，手部感觉、运动正常</t>
+  </si>
+  <si>
+    <t>X线片示右肱骨髁上骨折</t>
+  </si>
+  <si>
+    <t>活泼</t>
+  </si>
+  <si>
+    <t>哭闹、恐惧</t>
+  </si>
+  <si>
+    <t>以为摔一跤没事</t>
+  </si>
+  <si>
+    <t>胳膊会断吗？还能写字吗？</t>
+  </si>
+  <si>
+    <t>右肱骨髁上骨折</t>
+  </si>
+  <si>
+    <t>小明，7岁，课间玩耍从单杠摔下，右手撑地，右肘肿痛。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>肘部肿胀加重，有张力性水疱</t>
+  </si>
+  <si>
+    <t>右肘明显肿胀，张力性水疱，桡动脉搏动减弱，手部感觉正常</t>
+  </si>
+  <si>
+    <t>X线示骨折移位明显</t>
+  </si>
+  <si>
+    <t>为什么要开刀？疼不疼？</t>
+  </si>
+  <si>
+    <t>右肱骨髁上骨折（移位）</t>
+  </si>
+  <si>
+    <t>需急诊手术</t>
+  </si>
+  <si>
+    <t>患儿骨折移位明显，需急诊手术。家长十分担心，需解释手术必要性。</t>
+  </si>
+  <si>
+    <t>术后前臂剧痛，手指发麻</t>
+  </si>
+  <si>
+    <t>前臂肿胀，张力高，被动伸指剧痛，桡动脉搏动消失，手部苍白</t>
+  </si>
+  <si>
+    <t>术后X线示内固定位置可</t>
+  </si>
+  <si>
+    <t>痛苦、惊恐</t>
+  </si>
+  <si>
+    <t>手怎么没知觉了？会不会残废？</t>
+  </si>
+  <si>
+    <t>骨筋膜室综合征</t>
+  </si>
+  <si>
+    <t>需紧急切开减压</t>
+  </si>
+  <si>
+    <t>患儿术后出现骨筋膜室综合征，需紧急处理。向家长解释病情。</t>
+  </si>
+  <si>
+    <t>疼痛缓解，手部活动恢复</t>
+  </si>
+  <si>
+    <t>右肘伤口愈合好，手指活动正常，桡动脉搏动好</t>
+  </si>
+  <si>
+    <t>复查X线示骨折对位可</t>
+  </si>
+  <si>
+    <t>恢复活泼，好奇</t>
+  </si>
+  <si>
+    <t>回家后能马上上学吗？要注意什么？</t>
+  </si>
+  <si>
+    <t>右肱骨髁上骨折术后</t>
+  </si>
+  <si>
+    <t>患儿病情稳定，准备出院。需指导家长后续康复及预防。</t>
+  </si>
+  <si>
+    <t>“行走的齿轮”</t>
+  </si>
+  <si>
+    <t>双膝疼痛5年，活动加重，休息减轻</t>
+  </si>
+  <si>
+    <t>双膝内翻畸形，活动受限，髌骨摩擦试验阳性</t>
+  </si>
+  <si>
+    <t>X线示双膝骨关节炎表现</t>
+  </si>
+  <si>
+    <t>高血压</t>
+  </si>
+  <si>
+    <t>豁达，但抱怨腿不好</t>
+  </si>
+  <si>
+    <t>以为是风湿，没当回事</t>
+  </si>
+  <si>
+    <t>还能走路吗？要换关节吗？</t>
+  </si>
+  <si>
+    <t>双膝骨关节炎</t>
+  </si>
+  <si>
+    <t>李奶奶，68岁，双膝疼痛多年，上下楼梯困难。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>保守治疗</t>
+  </si>
+  <si>
+    <t>疼痛时好时坏，影响睡眠</t>
+  </si>
+  <si>
+    <t>X线同前</t>
+  </si>
+  <si>
+    <t>接受治疗，但担心预后</t>
+  </si>
+  <si>
+    <t>吃药能治好吗？关节里打针有用吗？</t>
+  </si>
+  <si>
+    <t>正在保守治疗</t>
+  </si>
+  <si>
+    <t>患者经保守治疗，效果不理想，咨询进一步方案。</t>
+  </si>
+  <si>
+    <t>疼痛进行性加重，需扶拐行走</t>
+  </si>
+  <si>
+    <t>双膝内翻，活动明显受限</t>
+  </si>
+  <si>
+    <t>X线示关节间隙几乎消失，大量骨赘</t>
+  </si>
+  <si>
+    <t>对手术既期待又害怕</t>
+  </si>
+  <si>
+    <t>换关节疼不疼？能用多久？</t>
+  </si>
+  <si>
+    <t>双膝骨关节炎（终末期）</t>
+  </si>
+  <si>
+    <t>准备手术</t>
+  </si>
+  <si>
+    <t>患者决定行右膝人工关节置换，需术前沟通。</t>
+  </si>
+  <si>
+    <t>术后恢复良好，无不适</t>
+  </si>
+  <si>
+    <t>右膝伤口愈合好，主动伸屈达0-90°</t>
+  </si>
+  <si>
+    <t>复查X线示假体位置可</t>
+  </si>
+  <si>
+    <t>感激，关心后续</t>
+  </si>
+  <si>
+    <t>回家后怎么锻炼？能恢复走路吗？</t>
+  </si>
+  <si>
+    <t>右人工膝关节置换术后</t>
+  </si>
+  <si>
+    <t>已手术</t>
+  </si>
+  <si>
+    <t>患者术后恢复顺利，准备出院。需指导康复及长期管理。</t>
+  </si>
+  <si>
+    <t>“断桥残雪”</t>
+  </si>
+  <si>
+    <t>突发腰痛伴右下肢放射痛</t>
+  </si>
+  <si>
+    <t>右椎旁压痛，直腿抬高试验阳性（30°）</t>
+  </si>
+  <si>
+    <t>MRI示L5-S1椎间盘突出</t>
+  </si>
+  <si>
+    <t>焦虑，痛苦</t>
+  </si>
+  <si>
+    <t>以为扭伤，没想到这么重</t>
+  </si>
+  <si>
+    <t>要手术吗？以后还能久坐吗？</t>
+  </si>
+  <si>
+    <t>腰椎间盘突出症</t>
+  </si>
+  <si>
+    <t>张先生，35岁，程序员，弯腰搬重物后腰痛伴右腿放射痛。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>疼痛持续，卧床稍缓解</t>
+  </si>
+  <si>
+    <t>右足拇趾背伸肌力Ⅳ级，跟腱反射减弱</t>
+  </si>
+  <si>
+    <t>MRI同前</t>
+  </si>
+  <si>
+    <t>仍焦虑，担心工作</t>
+  </si>
+  <si>
+    <t>保守治疗能好吗？要躺多久？</t>
+  </si>
+  <si>
+    <t>保守治疗中</t>
+  </si>
+  <si>
+    <t>患者严格卧床4周，症状改善不明显，咨询后续。</t>
+  </si>
+  <si>
+    <t>出现马尾综合征</t>
+  </si>
+  <si>
+    <t>右下肢剧痛，排尿困难，会阴麻木</t>
+  </si>
+  <si>
+    <t>鞍区感觉减退，肛门括约肌松弛</t>
+  </si>
+  <si>
+    <t>MRI示椎间盘突出加重</t>
+  </si>
+  <si>
+    <t>恐惧、无助</t>
+  </si>
+  <si>
+    <t>我是不是瘫痪了？还能不能大小便？</t>
+  </si>
+  <si>
+    <t>腰椎间盘突出症伴马尾综合征</t>
+  </si>
+  <si>
+    <t>患者出现马尾综合征，需急诊手术。向家属解释病情。</t>
+  </si>
+  <si>
+    <t>症状消失，大小便功能恢复</t>
+  </si>
+  <si>
+    <t>下肢肌力正常，感觉正常，鞍区感觉恢复</t>
+  </si>
+  <si>
+    <t>术后MRI示减压充分</t>
+  </si>
+  <si>
+    <t>平静，感激</t>
+  </si>
+  <si>
+    <t>以后要注意什么？多久能上班？</t>
+  </si>
+  <si>
+    <t>腰椎间盘突出症术后</t>
+  </si>
+  <si>
+    <t>患者术后恢复良好，准备出院。需指导康复和预防复发。</t>
+  </si>
+  <si>
+    <t>“糖衣炮弹”</t>
+  </si>
+  <si>
+    <t>多饮、多尿、多食、体重下降、视物模糊</t>
+  </si>
+  <si>
+    <t>BMI 28kg/m²，血压145/90mmHg，余无特殊</t>
+  </si>
+  <si>
+    <t>空腹血糖8.5mmol/L，餐后2h血糖13.2mmol/L，HbA1c 9.2%</t>
+  </si>
+  <si>
+    <t>焦虑，反复问是不是糖尿病</t>
+  </si>
+  <si>
+    <t>以为只是喝水多</t>
+  </si>
+  <si>
+    <t>这是糖尿病吗？能治好吗？</t>
+  </si>
+  <si>
+    <t>2型糖尿病</t>
+  </si>
+  <si>
+    <t>父亲有糖尿病</t>
+  </si>
+  <si>
+    <t>张先生，45岁，公司经理，近2月口渴多饮、多尿、消瘦。门诊就诊。</t>
+  </si>
+  <si>
+    <t>症状同前</t>
+  </si>
+  <si>
+    <t>C肽释放试验示胰岛素抵抗，尿糖(+++)，尿酮体阴性</t>
+  </si>
+  <si>
+    <t>接受诊断，但对治疗犹豫</t>
+  </si>
+  <si>
+    <t>为什么要吃药？副作用大吗？</t>
+  </si>
+  <si>
+    <t>胰岛素抵抗</t>
+  </si>
+  <si>
+    <t>患者确诊2型糖尿病，医生建议二甲双胍治疗，患者担心副作用。</t>
+  </si>
+  <si>
+    <t>治疗调整</t>
+  </si>
+  <si>
+    <t>恶心、腹泻，自行停药后血糖升高</t>
+  </si>
+  <si>
+    <t>空腹血糖9.5mmol/L，肝肾功能正常</t>
+  </si>
+  <si>
+    <t>担忧药物副作用</t>
+  </si>
+  <si>
+    <t>这药还能吃吗？要不要换药？</t>
+  </si>
+  <si>
+    <t>二甲双胍不耐受</t>
+  </si>
+  <si>
+    <t>患者服用二甲双胍后出现胃肠道反应，自行停药，需调整方案。</t>
+  </si>
+  <si>
+    <t>无不适，血糖控制平稳</t>
+  </si>
+  <si>
+    <t>血压130/80mmHg，心肺腹无异常</t>
+  </si>
+  <si>
+    <t>空腹血糖6.5mmol/L，HbA1c 6.8%</t>
+  </si>
+  <si>
+    <t>乐观，关心长期管理</t>
+  </si>
+  <si>
+    <t>以后要注意什么？多久复查？</t>
+  </si>
+  <si>
+    <t>患者血糖控制良好，准备出院。医生进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“隐形狂飙”</t>
+  </si>
+  <si>
+    <t>心慌、手抖、怕热、多汗、急躁、失眠、消瘦</t>
+  </si>
+  <si>
+    <t>心率110次/分，甲状腺Ⅱ°肿大伴血管杂音，突眼征阳性</t>
+  </si>
+  <si>
+    <t>FT3 18.5pmol/L，FT4 42.6pmol/L，TSH &lt;0.01mIU/L</t>
+  </si>
+  <si>
+    <t>激动、话多</t>
+  </si>
+  <si>
+    <t>以为是自己脾气变差</t>
+  </si>
+  <si>
+    <t>我是不是得了甲亢？怎么治？</t>
+  </si>
+  <si>
+    <t>Graves病</t>
+  </si>
+  <si>
+    <t>李女士，32岁，教师，近3月心慌、手抖、消瘦，情绪急躁。门诊就诊。</t>
+  </si>
+  <si>
+    <t>症状明显，影响工作</t>
+  </si>
+  <si>
+    <t>甲状腺B超示弥漫性肿大，血流丰富，摄碘率升高</t>
+  </si>
+  <si>
+    <t>急切想控制症状</t>
+  </si>
+  <si>
+    <t>吃药要吃多久？会不会复发？</t>
+  </si>
+  <si>
+    <t>开始服用甲巯咪唑</t>
+  </si>
+  <si>
+    <t>患者确诊Graves病，开始抗甲状腺药物治疗。需解释注意事项。</t>
+  </si>
+  <si>
+    <t>出现并发症</t>
+  </si>
+  <si>
+    <t>咽痛、发热、乏力</t>
+  </si>
+  <si>
+    <t>体温38.5℃，咽部充血，余无特殊</t>
+  </si>
+  <si>
+    <t>血常规WBC 2.0×10⁹/L，中性粒细胞0.5×10⁹/L</t>
+  </si>
+  <si>
+    <t>怎么会这样？会不会有危险？</t>
+  </si>
+  <si>
+    <t>药物性粒细胞缺乏</t>
+  </si>
+  <si>
+    <t>甲巯咪唑引起</t>
+  </si>
+  <si>
+    <t>患者服用甲巯咪唑4周后出现粒细胞缺乏，需紧急处理。</t>
+  </si>
+  <si>
+    <t>症状消失，体温正常</t>
+  </si>
+  <si>
+    <t>生命体征平稳，无阳性体征</t>
+  </si>
+  <si>
+    <t>血常规恢复正常，甲功正常</t>
+  </si>
+  <si>
+    <t>以后还能生小孩吗？要注意什么？</t>
+  </si>
+  <si>
+    <t>Graves病（缓解期）</t>
+  </si>
+  <si>
+    <t>已换用丙硫氧嘧啶</t>
+  </si>
+  <si>
+    <t>患者经治疗后恢复良好，准备出院。医生进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“荷尔蒙迷航”</t>
+  </si>
+  <si>
+    <t>月经稀发、不孕、多毛、痤疮、肥胖</t>
+  </si>
+  <si>
+    <t>BMI 27kg/m²，多毛评分8分，面部及背部痤疮</t>
+  </si>
+  <si>
+    <t>性激素：LH/FSH&gt;2，睾酮升高，B超示卵巢多囊样改变</t>
+  </si>
+  <si>
+    <t>焦虑、羞涩</t>
+  </si>
+  <si>
+    <t>是不是不能怀孕了？</t>
+  </si>
+  <si>
+    <t>多囊卵巢综合征</t>
+  </si>
+  <si>
+    <t>未婚未孕</t>
+  </si>
+  <si>
+    <t>王小姐，26岁，因结婚2年未孕就诊。月经稀发，多毛、痤疮明显。</t>
+  </si>
+  <si>
+    <t>基础治疗</t>
+  </si>
+  <si>
+    <t>月经仍不规律</t>
+  </si>
+  <si>
+    <t>空腹胰岛素抵抗指数偏高，OGTT正常</t>
+  </si>
+  <si>
+    <t>仍焦虑，但对治疗有期待</t>
+  </si>
+  <si>
+    <t>减肥真的有用吗？要吃药吗？</t>
+  </si>
+  <si>
+    <t>医生建议生活方式干预+二甲双胍治疗，患者担心效果。</t>
+  </si>
+  <si>
+    <t>促排卵前</t>
+  </si>
+  <si>
+    <t>体重下降5kg，月经仍不规律</t>
+  </si>
+  <si>
+    <t>BMI 25kg/m²，多毛痤疮减轻</t>
+  </si>
+  <si>
+    <t>复查性激素较前改善，但仍未正常排卵</t>
+  </si>
+  <si>
+    <t>急切想怀孕</t>
+  </si>
+  <si>
+    <t>现在能促排卵吗？有风险吗？</t>
+  </si>
+  <si>
+    <t>基础治疗后</t>
+  </si>
+  <si>
+    <t>患者生活方式干预后体重下降，但月经仍不规律，希望怀孕。需讨论促排卵方案。</t>
+  </si>
+  <si>
+    <t>怀孕后随访</t>
+  </si>
+  <si>
+    <t>已怀孕，早孕反应轻微</t>
+  </si>
+  <si>
+    <t>生命体征平稳，腹部无异常</t>
+  </si>
+  <si>
+    <t>血HCG升高，孕酮正常</t>
+  </si>
+  <si>
+    <t>喜悦，担心孕期</t>
+  </si>
+  <si>
+    <t>怀孕后要注意什么？药还要吃吗？</t>
+  </si>
+  <si>
+    <t>多囊卵巢综合征合并妊娠</t>
+  </si>
+  <si>
+    <t>已成功怀孕</t>
+  </si>
+  <si>
+    <t>患者促排卵后成功怀孕，准备从生殖中心转产科随访。需指导孕期注意事项。</t>
   </si>
 </sst>
 </file>
@@ -3169,7 +5167,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="9.02654867256637" style="1"/>
@@ -7222,6 +9220,4346 @@
         <v>725</v>
       </c>
     </row>
+    <row r="82" spans="1:16">
+      <c r="A82">
+        <v>1</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C82" t="s">
+        <v>286</v>
+      </c>
+      <c r="D82">
+        <v>68</v>
+      </c>
+      <c r="E82" t="s">
+        <v>18</v>
+      </c>
+      <c r="F82" t="s">
+        <v>727</v>
+      </c>
+      <c r="G82" t="s">
+        <v>728</v>
+      </c>
+      <c r="H82" t="s">
+        <v>729</v>
+      </c>
+      <c r="I82" t="s">
+        <v>730</v>
+      </c>
+      <c r="J82" t="s">
+        <v>23</v>
+      </c>
+      <c r="K82" t="s">
+        <v>731</v>
+      </c>
+      <c r="L82" t="s">
+        <v>732</v>
+      </c>
+      <c r="M82" t="s">
+        <v>733</v>
+      </c>
+      <c r="N82" t="s">
+        <v>734</v>
+      </c>
+      <c r="O82" t="s">
+        <v>62</v>
+      </c>
+      <c r="P82" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
+      <c r="A83">
+        <v>2</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C83" t="s">
+        <v>443</v>
+      </c>
+      <c r="D83">
+        <v>68</v>
+      </c>
+      <c r="E83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" t="s">
+        <v>736</v>
+      </c>
+      <c r="G83" t="s">
+        <v>737</v>
+      </c>
+      <c r="H83" t="s">
+        <v>738</v>
+      </c>
+      <c r="I83" t="s">
+        <v>34</v>
+      </c>
+      <c r="J83" t="s">
+        <v>23</v>
+      </c>
+      <c r="K83" t="s">
+        <v>331</v>
+      </c>
+      <c r="L83" t="s">
+        <v>739</v>
+      </c>
+      <c r="M83" t="s">
+        <v>740</v>
+      </c>
+      <c r="N83" t="s">
+        <v>741</v>
+      </c>
+      <c r="O83" t="s">
+        <v>742</v>
+      </c>
+      <c r="P83" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
+      <c r="A84">
+        <v>3</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C84" t="s">
+        <v>744</v>
+      </c>
+      <c r="D84">
+        <v>68</v>
+      </c>
+      <c r="E84" t="s">
+        <v>18</v>
+      </c>
+      <c r="F84" t="s">
+        <v>745</v>
+      </c>
+      <c r="G84" t="s">
+        <v>746</v>
+      </c>
+      <c r="H84" t="s">
+        <v>747</v>
+      </c>
+      <c r="I84" t="s">
+        <v>34</v>
+      </c>
+      <c r="J84" t="s">
+        <v>50</v>
+      </c>
+      <c r="K84" t="s">
+        <v>384</v>
+      </c>
+      <c r="L84" t="s">
+        <v>748</v>
+      </c>
+      <c r="M84" t="s">
+        <v>749</v>
+      </c>
+      <c r="N84" t="s">
+        <v>750</v>
+      </c>
+      <c r="O84" t="s">
+        <v>751</v>
+      </c>
+      <c r="P84" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
+      <c r="A85">
+        <v>4</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C85" t="s">
+        <v>125</v>
+      </c>
+      <c r="D85">
+        <v>68</v>
+      </c>
+      <c r="E85" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" t="s">
+        <v>753</v>
+      </c>
+      <c r="G85" t="s">
+        <v>754</v>
+      </c>
+      <c r="H85" t="s">
+        <v>755</v>
+      </c>
+      <c r="I85" t="s">
+        <v>34</v>
+      </c>
+      <c r="J85" t="s">
+        <v>50</v>
+      </c>
+      <c r="K85" t="s">
+        <v>320</v>
+      </c>
+      <c r="L85" t="s">
+        <v>658</v>
+      </c>
+      <c r="M85" t="s">
+        <v>756</v>
+      </c>
+      <c r="N85" t="s">
+        <v>750</v>
+      </c>
+      <c r="O85" t="s">
+        <v>757</v>
+      </c>
+      <c r="P85" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
+      <c r="A86">
+        <v>1</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="C86" t="s">
+        <v>286</v>
+      </c>
+      <c r="D86">
+        <v>68</v>
+      </c>
+      <c r="E86" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" t="s">
+        <v>727</v>
+      </c>
+      <c r="G86" t="s">
+        <v>728</v>
+      </c>
+      <c r="H86" t="s">
+        <v>729</v>
+      </c>
+      <c r="I86" t="s">
+        <v>730</v>
+      </c>
+      <c r="J86" t="s">
+        <v>23</v>
+      </c>
+      <c r="K86" t="s">
+        <v>731</v>
+      </c>
+      <c r="L86" t="s">
+        <v>732</v>
+      </c>
+      <c r="M86" t="s">
+        <v>733</v>
+      </c>
+      <c r="N86" t="s">
+        <v>734</v>
+      </c>
+      <c r="O86" t="s">
+        <v>62</v>
+      </c>
+      <c r="P86" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
+      <c r="A87">
+        <v>2</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="C87" t="s">
+        <v>443</v>
+      </c>
+      <c r="D87">
+        <v>68</v>
+      </c>
+      <c r="E87" t="s">
+        <v>18</v>
+      </c>
+      <c r="F87" t="s">
+        <v>736</v>
+      </c>
+      <c r="G87" t="s">
+        <v>737</v>
+      </c>
+      <c r="H87" t="s">
+        <v>738</v>
+      </c>
+      <c r="I87" t="s">
+        <v>34</v>
+      </c>
+      <c r="J87" t="s">
+        <v>23</v>
+      </c>
+      <c r="K87" t="s">
+        <v>331</v>
+      </c>
+      <c r="L87" t="s">
+        <v>739</v>
+      </c>
+      <c r="M87" t="s">
+        <v>740</v>
+      </c>
+      <c r="N87" t="s">
+        <v>741</v>
+      </c>
+      <c r="O87" t="s">
+        <v>742</v>
+      </c>
+      <c r="P87" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
+      <c r="A88">
+        <v>3</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="C88" t="s">
+        <v>744</v>
+      </c>
+      <c r="D88">
+        <v>68</v>
+      </c>
+      <c r="E88" t="s">
+        <v>18</v>
+      </c>
+      <c r="F88" t="s">
+        <v>745</v>
+      </c>
+      <c r="G88" t="s">
+        <v>746</v>
+      </c>
+      <c r="H88" t="s">
+        <v>747</v>
+      </c>
+      <c r="I88" t="s">
+        <v>34</v>
+      </c>
+      <c r="J88" t="s">
+        <v>50</v>
+      </c>
+      <c r="K88" t="s">
+        <v>384</v>
+      </c>
+      <c r="L88" t="s">
+        <v>748</v>
+      </c>
+      <c r="M88" t="s">
+        <v>749</v>
+      </c>
+      <c r="N88" t="s">
+        <v>750</v>
+      </c>
+      <c r="O88" t="s">
+        <v>751</v>
+      </c>
+      <c r="P88" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
+      <c r="A89">
+        <v>4</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="C89" t="s">
+        <v>125</v>
+      </c>
+      <c r="D89">
+        <v>68</v>
+      </c>
+      <c r="E89" t="s">
+        <v>18</v>
+      </c>
+      <c r="F89" t="s">
+        <v>753</v>
+      </c>
+      <c r="G89" t="s">
+        <v>754</v>
+      </c>
+      <c r="H89" t="s">
+        <v>755</v>
+      </c>
+      <c r="I89" t="s">
+        <v>34</v>
+      </c>
+      <c r="J89" t="s">
+        <v>50</v>
+      </c>
+      <c r="K89" t="s">
+        <v>320</v>
+      </c>
+      <c r="L89" t="s">
+        <v>658</v>
+      </c>
+      <c r="M89" t="s">
+        <v>756</v>
+      </c>
+      <c r="N89" t="s">
+        <v>750</v>
+      </c>
+      <c r="O89" t="s">
+        <v>757</v>
+      </c>
+      <c r="P89" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
+      <c r="A90">
+        <v>1</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C90" t="s">
+        <v>211</v>
+      </c>
+      <c r="D90">
+        <v>25</v>
+      </c>
+      <c r="E90" t="s">
+        <v>18</v>
+      </c>
+      <c r="F90" t="s">
+        <v>761</v>
+      </c>
+      <c r="G90" t="s">
+        <v>762</v>
+      </c>
+      <c r="H90" t="s">
+        <v>763</v>
+      </c>
+      <c r="I90" t="s">
+        <v>62</v>
+      </c>
+      <c r="J90" t="s">
+        <v>23</v>
+      </c>
+      <c r="K90" t="s">
+        <v>764</v>
+      </c>
+      <c r="L90" t="s">
+        <v>732</v>
+      </c>
+      <c r="M90" t="s">
+        <v>765</v>
+      </c>
+      <c r="N90" t="s">
+        <v>766</v>
+      </c>
+      <c r="O90" t="s">
+        <v>62</v>
+      </c>
+      <c r="P90" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
+      <c r="A91">
+        <v>2</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C91" t="s">
+        <v>509</v>
+      </c>
+      <c r="D91">
+        <v>25</v>
+      </c>
+      <c r="E91" t="s">
+        <v>18</v>
+      </c>
+      <c r="F91" t="s">
+        <v>768</v>
+      </c>
+      <c r="G91" t="s">
+        <v>34</v>
+      </c>
+      <c r="H91" t="s">
+        <v>769</v>
+      </c>
+      <c r="I91" t="s">
+        <v>62</v>
+      </c>
+      <c r="J91" t="s">
+        <v>23</v>
+      </c>
+      <c r="K91" t="s">
+        <v>331</v>
+      </c>
+      <c r="L91" t="s">
+        <v>770</v>
+      </c>
+      <c r="M91" t="s">
+        <v>771</v>
+      </c>
+      <c r="N91" t="s">
+        <v>772</v>
+      </c>
+      <c r="O91" t="s">
+        <v>62</v>
+      </c>
+      <c r="P91" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
+      <c r="A92">
+        <v>3</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C92" t="s">
+        <v>548</v>
+      </c>
+      <c r="D92">
+        <v>25</v>
+      </c>
+      <c r="E92" t="s">
+        <v>18</v>
+      </c>
+      <c r="F92" t="s">
+        <v>774</v>
+      </c>
+      <c r="G92" t="s">
+        <v>382</v>
+      </c>
+      <c r="H92" t="s">
+        <v>775</v>
+      </c>
+      <c r="I92" t="s">
+        <v>62</v>
+      </c>
+      <c r="J92" t="s">
+        <v>50</v>
+      </c>
+      <c r="K92" t="s">
+        <v>384</v>
+      </c>
+      <c r="L92" t="s">
+        <v>776</v>
+      </c>
+      <c r="M92" t="s">
+        <v>777</v>
+      </c>
+      <c r="N92" t="s">
+        <v>772</v>
+      </c>
+      <c r="O92" t="s">
+        <v>778</v>
+      </c>
+      <c r="P92" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
+      <c r="A93">
+        <v>4</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C93" t="s">
+        <v>125</v>
+      </c>
+      <c r="D93">
+        <v>25</v>
+      </c>
+      <c r="E93" t="s">
+        <v>18</v>
+      </c>
+      <c r="F93" t="s">
+        <v>780</v>
+      </c>
+      <c r="G93" t="s">
+        <v>781</v>
+      </c>
+      <c r="H93" t="s">
+        <v>782</v>
+      </c>
+      <c r="I93" t="s">
+        <v>62</v>
+      </c>
+      <c r="J93" t="s">
+        <v>50</v>
+      </c>
+      <c r="K93" t="s">
+        <v>320</v>
+      </c>
+      <c r="L93" t="s">
+        <v>783</v>
+      </c>
+      <c r="M93" t="s">
+        <v>784</v>
+      </c>
+      <c r="N93" t="s">
+        <v>785</v>
+      </c>
+      <c r="O93" t="s">
+        <v>786</v>
+      </c>
+      <c r="P93" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
+      <c r="A94">
+        <v>1</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C94" t="s">
+        <v>252</v>
+      </c>
+      <c r="D94">
+        <v>35</v>
+      </c>
+      <c r="E94" t="s">
+        <v>58</v>
+      </c>
+      <c r="F94" t="s">
+        <v>789</v>
+      </c>
+      <c r="G94" t="s">
+        <v>790</v>
+      </c>
+      <c r="H94" t="s">
+        <v>791</v>
+      </c>
+      <c r="I94" t="s">
+        <v>62</v>
+      </c>
+      <c r="J94" t="s">
+        <v>792</v>
+      </c>
+      <c r="K94" t="s">
+        <v>793</v>
+      </c>
+      <c r="L94" t="s">
+        <v>794</v>
+      </c>
+      <c r="M94" t="s">
+        <v>795</v>
+      </c>
+      <c r="N94" t="s">
+        <v>796</v>
+      </c>
+      <c r="O94" t="s">
+        <v>62</v>
+      </c>
+      <c r="P94" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
+      <c r="A95">
+        <v>2</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C95" t="s">
+        <v>548</v>
+      </c>
+      <c r="D95">
+        <v>35</v>
+      </c>
+      <c r="E95" t="s">
+        <v>58</v>
+      </c>
+      <c r="F95" t="s">
+        <v>798</v>
+      </c>
+      <c r="G95" t="s">
+        <v>34</v>
+      </c>
+      <c r="H95" t="s">
+        <v>799</v>
+      </c>
+      <c r="I95" t="s">
+        <v>62</v>
+      </c>
+      <c r="J95" t="s">
+        <v>792</v>
+      </c>
+      <c r="K95" t="s">
+        <v>331</v>
+      </c>
+      <c r="L95" t="s">
+        <v>800</v>
+      </c>
+      <c r="M95" t="s">
+        <v>801</v>
+      </c>
+      <c r="N95" t="s">
+        <v>796</v>
+      </c>
+      <c r="O95" t="s">
+        <v>62</v>
+      </c>
+      <c r="P95" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
+      <c r="A96">
+        <v>3</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C96" t="s">
+        <v>803</v>
+      </c>
+      <c r="D96">
+        <v>35</v>
+      </c>
+      <c r="E96" t="s">
+        <v>58</v>
+      </c>
+      <c r="F96" t="s">
+        <v>804</v>
+      </c>
+      <c r="G96" t="s">
+        <v>382</v>
+      </c>
+      <c r="H96" t="s">
+        <v>805</v>
+      </c>
+      <c r="I96" t="s">
+        <v>62</v>
+      </c>
+      <c r="J96" t="s">
+        <v>792</v>
+      </c>
+      <c r="K96" t="s">
+        <v>384</v>
+      </c>
+      <c r="L96" t="s">
+        <v>806</v>
+      </c>
+      <c r="M96" t="s">
+        <v>807</v>
+      </c>
+      <c r="N96" t="s">
+        <v>796</v>
+      </c>
+      <c r="O96" t="s">
+        <v>808</v>
+      </c>
+      <c r="P96" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
+      <c r="A97">
+        <v>4</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C97" t="s">
+        <v>125</v>
+      </c>
+      <c r="D97">
+        <v>35</v>
+      </c>
+      <c r="E97" t="s">
+        <v>58</v>
+      </c>
+      <c r="F97" t="s">
+        <v>810</v>
+      </c>
+      <c r="G97" t="s">
+        <v>811</v>
+      </c>
+      <c r="H97" t="s">
+        <v>812</v>
+      </c>
+      <c r="I97" t="s">
+        <v>62</v>
+      </c>
+      <c r="J97" t="s">
+        <v>813</v>
+      </c>
+      <c r="K97" t="s">
+        <v>320</v>
+      </c>
+      <c r="L97" t="s">
+        <v>658</v>
+      </c>
+      <c r="M97" t="s">
+        <v>814</v>
+      </c>
+      <c r="N97" t="s">
+        <v>815</v>
+      </c>
+      <c r="O97" t="s">
+        <v>786</v>
+      </c>
+      <c r="P97" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
+      <c r="A98">
+        <v>1</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C98" t="s">
+        <v>252</v>
+      </c>
+      <c r="D98">
+        <v>58</v>
+      </c>
+      <c r="E98" t="s">
+        <v>18</v>
+      </c>
+      <c r="F98" t="s">
+        <v>818</v>
+      </c>
+      <c r="G98" t="s">
+        <v>819</v>
+      </c>
+      <c r="H98" t="s">
+        <v>820</v>
+      </c>
+      <c r="I98" t="s">
+        <v>821</v>
+      </c>
+      <c r="J98" t="s">
+        <v>23</v>
+      </c>
+      <c r="K98" t="s">
+        <v>409</v>
+      </c>
+      <c r="L98" t="s">
+        <v>471</v>
+      </c>
+      <c r="M98" t="s">
+        <v>822</v>
+      </c>
+      <c r="N98" t="s">
+        <v>823</v>
+      </c>
+      <c r="O98" t="s">
+        <v>62</v>
+      </c>
+      <c r="P98" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
+      <c r="A99">
+        <v>2</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C99" t="s">
+        <v>221</v>
+      </c>
+      <c r="D99">
+        <v>58</v>
+      </c>
+      <c r="E99" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" t="s">
+        <v>825</v>
+      </c>
+      <c r="G99" t="s">
+        <v>826</v>
+      </c>
+      <c r="H99" t="s">
+        <v>827</v>
+      </c>
+      <c r="I99" t="s">
+        <v>34</v>
+      </c>
+      <c r="J99" t="s">
+        <v>23</v>
+      </c>
+      <c r="K99" t="s">
+        <v>331</v>
+      </c>
+      <c r="L99" t="s">
+        <v>828</v>
+      </c>
+      <c r="M99" t="s">
+        <v>829</v>
+      </c>
+      <c r="N99" t="s">
+        <v>830</v>
+      </c>
+      <c r="O99" t="s">
+        <v>831</v>
+      </c>
+      <c r="P99" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
+      <c r="A100">
+        <v>3</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C100" t="s">
+        <v>415</v>
+      </c>
+      <c r="D100">
+        <v>58</v>
+      </c>
+      <c r="E100" t="s">
+        <v>18</v>
+      </c>
+      <c r="F100" t="s">
+        <v>833</v>
+      </c>
+      <c r="G100" t="s">
+        <v>834</v>
+      </c>
+      <c r="H100" t="s">
+        <v>835</v>
+      </c>
+      <c r="I100" t="s">
+        <v>34</v>
+      </c>
+      <c r="J100" t="s">
+        <v>50</v>
+      </c>
+      <c r="K100" t="s">
+        <v>384</v>
+      </c>
+      <c r="L100" t="s">
+        <v>836</v>
+      </c>
+      <c r="M100" t="s">
+        <v>837</v>
+      </c>
+      <c r="N100" t="s">
+        <v>323</v>
+      </c>
+      <c r="O100" t="s">
+        <v>838</v>
+      </c>
+      <c r="P100" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
+      <c r="A101">
+        <v>4</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="C101" t="s">
+        <v>125</v>
+      </c>
+      <c r="D101">
+        <v>58</v>
+      </c>
+      <c r="E101" t="s">
+        <v>18</v>
+      </c>
+      <c r="F101" t="s">
+        <v>840</v>
+      </c>
+      <c r="G101" t="s">
+        <v>841</v>
+      </c>
+      <c r="H101" t="s">
+        <v>842</v>
+      </c>
+      <c r="I101" t="s">
+        <v>34</v>
+      </c>
+      <c r="J101" t="s">
+        <v>50</v>
+      </c>
+      <c r="K101" t="s">
+        <v>320</v>
+      </c>
+      <c r="L101" t="s">
+        <v>843</v>
+      </c>
+      <c r="M101" t="s">
+        <v>844</v>
+      </c>
+      <c r="N101" t="s">
+        <v>323</v>
+      </c>
+      <c r="O101" t="s">
+        <v>751</v>
+      </c>
+      <c r="P101" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102">
+        <v>1</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="C102" t="s">
+        <v>211</v>
+      </c>
+      <c r="D102">
+        <v>72</v>
+      </c>
+      <c r="E102" t="s">
+        <v>18</v>
+      </c>
+      <c r="F102" t="s">
+        <v>847</v>
+      </c>
+      <c r="G102" t="s">
+        <v>848</v>
+      </c>
+      <c r="H102" t="s">
+        <v>849</v>
+      </c>
+      <c r="I102" t="s">
+        <v>730</v>
+      </c>
+      <c r="J102" t="s">
+        <v>23</v>
+      </c>
+      <c r="K102" t="s">
+        <v>409</v>
+      </c>
+      <c r="L102" t="s">
+        <v>850</v>
+      </c>
+      <c r="M102" t="s">
+        <v>851</v>
+      </c>
+      <c r="N102" t="s">
+        <v>852</v>
+      </c>
+      <c r="O102" t="s">
+        <v>62</v>
+      </c>
+      <c r="P102" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103">
+        <v>2</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="C103" t="s">
+        <v>443</v>
+      </c>
+      <c r="D103">
+        <v>72</v>
+      </c>
+      <c r="E103" t="s">
+        <v>18</v>
+      </c>
+      <c r="F103" t="s">
+        <v>854</v>
+      </c>
+      <c r="G103" t="s">
+        <v>855</v>
+      </c>
+      <c r="H103" t="s">
+        <v>856</v>
+      </c>
+      <c r="I103" t="s">
+        <v>34</v>
+      </c>
+      <c r="J103" t="s">
+        <v>23</v>
+      </c>
+      <c r="K103" t="s">
+        <v>331</v>
+      </c>
+      <c r="L103" t="s">
+        <v>857</v>
+      </c>
+      <c r="M103" t="s">
+        <v>858</v>
+      </c>
+      <c r="N103" t="s">
+        <v>859</v>
+      </c>
+      <c r="O103" t="s">
+        <v>860</v>
+      </c>
+      <c r="P103" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
+      <c r="A104">
+        <v>3</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="C104" t="s">
+        <v>862</v>
+      </c>
+      <c r="D104">
+        <v>72</v>
+      </c>
+      <c r="E104" t="s">
+        <v>18</v>
+      </c>
+      <c r="F104" t="s">
+        <v>863</v>
+      </c>
+      <c r="G104" t="s">
+        <v>864</v>
+      </c>
+      <c r="H104" t="s">
+        <v>865</v>
+      </c>
+      <c r="I104" t="s">
+        <v>34</v>
+      </c>
+      <c r="J104" t="s">
+        <v>50</v>
+      </c>
+      <c r="K104" t="s">
+        <v>384</v>
+      </c>
+      <c r="L104" t="s">
+        <v>866</v>
+      </c>
+      <c r="M104" t="s">
+        <v>867</v>
+      </c>
+      <c r="N104" t="s">
+        <v>868</v>
+      </c>
+      <c r="O104" t="s">
+        <v>869</v>
+      </c>
+      <c r="P104" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
+      <c r="A105">
+        <v>4</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="C105" t="s">
+        <v>125</v>
+      </c>
+      <c r="D105">
+        <v>72</v>
+      </c>
+      <c r="E105" t="s">
+        <v>18</v>
+      </c>
+      <c r="F105" t="s">
+        <v>193</v>
+      </c>
+      <c r="G105" t="s">
+        <v>871</v>
+      </c>
+      <c r="H105" t="s">
+        <v>872</v>
+      </c>
+      <c r="I105" t="s">
+        <v>34</v>
+      </c>
+      <c r="J105" t="s">
+        <v>50</v>
+      </c>
+      <c r="K105" t="s">
+        <v>320</v>
+      </c>
+      <c r="L105" t="s">
+        <v>873</v>
+      </c>
+      <c r="M105" t="s">
+        <v>874</v>
+      </c>
+      <c r="N105" t="s">
+        <v>875</v>
+      </c>
+      <c r="O105" t="s">
+        <v>876</v>
+      </c>
+      <c r="P105" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
+      <c r="A106">
+        <v>1</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C106" t="s">
+        <v>879</v>
+      </c>
+      <c r="D106">
+        <v>76</v>
+      </c>
+      <c r="E106" t="s">
+        <v>18</v>
+      </c>
+      <c r="F106" t="s">
+        <v>880</v>
+      </c>
+      <c r="G106" t="s">
+        <v>881</v>
+      </c>
+      <c r="H106" t="s">
+        <v>882</v>
+      </c>
+      <c r="I106" t="s">
+        <v>883</v>
+      </c>
+      <c r="J106" t="s">
+        <v>23</v>
+      </c>
+      <c r="K106" t="s">
+        <v>158</v>
+      </c>
+      <c r="L106" t="s">
+        <v>884</v>
+      </c>
+      <c r="M106" t="s">
+        <v>885</v>
+      </c>
+      <c r="N106" t="s">
+        <v>886</v>
+      </c>
+      <c r="O106" t="s">
+        <v>62</v>
+      </c>
+      <c r="P106" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16">
+      <c r="A107">
+        <v>2</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C107" t="s">
+        <v>443</v>
+      </c>
+      <c r="D107">
+        <v>76</v>
+      </c>
+      <c r="E107" t="s">
+        <v>18</v>
+      </c>
+      <c r="F107" t="s">
+        <v>888</v>
+      </c>
+      <c r="G107" t="s">
+        <v>889</v>
+      </c>
+      <c r="H107" t="s">
+        <v>890</v>
+      </c>
+      <c r="I107" t="s">
+        <v>34</v>
+      </c>
+      <c r="J107" t="s">
+        <v>23</v>
+      </c>
+      <c r="K107" t="s">
+        <v>331</v>
+      </c>
+      <c r="L107" t="s">
+        <v>891</v>
+      </c>
+      <c r="M107" t="s">
+        <v>892</v>
+      </c>
+      <c r="N107" t="s">
+        <v>893</v>
+      </c>
+      <c r="O107" t="s">
+        <v>894</v>
+      </c>
+      <c r="P107" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
+      <c r="A108">
+        <v>3</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C108" t="s">
+        <v>617</v>
+      </c>
+      <c r="D108">
+        <v>76</v>
+      </c>
+      <c r="E108" t="s">
+        <v>18</v>
+      </c>
+      <c r="F108" t="s">
+        <v>896</v>
+      </c>
+      <c r="G108" t="s">
+        <v>897</v>
+      </c>
+      <c r="H108" t="s">
+        <v>898</v>
+      </c>
+      <c r="I108" t="s">
+        <v>34</v>
+      </c>
+      <c r="J108" t="s">
+        <v>50</v>
+      </c>
+      <c r="K108" t="s">
+        <v>384</v>
+      </c>
+      <c r="L108" t="s">
+        <v>899</v>
+      </c>
+      <c r="M108" t="s">
+        <v>900</v>
+      </c>
+      <c r="N108" t="s">
+        <v>901</v>
+      </c>
+      <c r="O108" t="s">
+        <v>902</v>
+      </c>
+      <c r="P108" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
+      <c r="A109">
+        <v>4</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C109" t="s">
+        <v>125</v>
+      </c>
+      <c r="D109">
+        <v>76</v>
+      </c>
+      <c r="E109" t="s">
+        <v>18</v>
+      </c>
+      <c r="F109" t="s">
+        <v>904</v>
+      </c>
+      <c r="G109" t="s">
+        <v>905</v>
+      </c>
+      <c r="H109" t="s">
+        <v>906</v>
+      </c>
+      <c r="I109" t="s">
+        <v>34</v>
+      </c>
+      <c r="J109" t="s">
+        <v>50</v>
+      </c>
+      <c r="K109" t="s">
+        <v>320</v>
+      </c>
+      <c r="L109" t="s">
+        <v>658</v>
+      </c>
+      <c r="M109" t="s">
+        <v>907</v>
+      </c>
+      <c r="N109" t="s">
+        <v>908</v>
+      </c>
+      <c r="O109" t="s">
+        <v>909</v>
+      </c>
+      <c r="P109" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
+      <c r="A110">
+        <v>1</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="C110" t="s">
+        <v>211</v>
+      </c>
+      <c r="D110">
+        <v>25</v>
+      </c>
+      <c r="E110" t="s">
+        <v>18</v>
+      </c>
+      <c r="F110" t="s">
+        <v>912</v>
+      </c>
+      <c r="G110" t="s">
+        <v>913</v>
+      </c>
+      <c r="H110" t="s">
+        <v>914</v>
+      </c>
+      <c r="I110" t="s">
+        <v>915</v>
+      </c>
+      <c r="J110" t="s">
+        <v>23</v>
+      </c>
+      <c r="K110" t="s">
+        <v>731</v>
+      </c>
+      <c r="L110" t="s">
+        <v>916</v>
+      </c>
+      <c r="M110" t="s">
+        <v>917</v>
+      </c>
+      <c r="N110" t="s">
+        <v>918</v>
+      </c>
+      <c r="O110" t="s">
+        <v>62</v>
+      </c>
+      <c r="P110" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
+      <c r="A111">
+        <v>2</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="C111" t="s">
+        <v>443</v>
+      </c>
+      <c r="D111">
+        <v>25</v>
+      </c>
+      <c r="E111" t="s">
+        <v>18</v>
+      </c>
+      <c r="F111" t="s">
+        <v>920</v>
+      </c>
+      <c r="G111" t="s">
+        <v>921</v>
+      </c>
+      <c r="H111" t="s">
+        <v>922</v>
+      </c>
+      <c r="I111" t="s">
+        <v>34</v>
+      </c>
+      <c r="J111" t="s">
+        <v>23</v>
+      </c>
+      <c r="K111" t="s">
+        <v>331</v>
+      </c>
+      <c r="L111" t="s">
+        <v>923</v>
+      </c>
+      <c r="M111" t="s">
+        <v>924</v>
+      </c>
+      <c r="N111" t="s">
+        <v>925</v>
+      </c>
+      <c r="O111" t="s">
+        <v>926</v>
+      </c>
+      <c r="P111" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
+      <c r="A112">
+        <v>3</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="C112" t="s">
+        <v>380</v>
+      </c>
+      <c r="D112">
+        <v>25</v>
+      </c>
+      <c r="E112" t="s">
+        <v>18</v>
+      </c>
+      <c r="F112" t="s">
+        <v>928</v>
+      </c>
+      <c r="G112" t="s">
+        <v>929</v>
+      </c>
+      <c r="H112" t="s">
+        <v>930</v>
+      </c>
+      <c r="I112" t="s">
+        <v>34</v>
+      </c>
+      <c r="J112" t="s">
+        <v>50</v>
+      </c>
+      <c r="K112" t="s">
+        <v>384</v>
+      </c>
+      <c r="L112" t="s">
+        <v>931</v>
+      </c>
+      <c r="M112" t="s">
+        <v>932</v>
+      </c>
+      <c r="N112" t="s">
+        <v>933</v>
+      </c>
+      <c r="O112" t="s">
+        <v>934</v>
+      </c>
+      <c r="P112" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
+      <c r="A113">
+        <v>4</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="C113" t="s">
+        <v>125</v>
+      </c>
+      <c r="D113">
+        <v>25</v>
+      </c>
+      <c r="E113" t="s">
+        <v>18</v>
+      </c>
+      <c r="F113" t="s">
+        <v>193</v>
+      </c>
+      <c r="G113" t="s">
+        <v>382</v>
+      </c>
+      <c r="H113" t="s">
+        <v>936</v>
+      </c>
+      <c r="I113" t="s">
+        <v>34</v>
+      </c>
+      <c r="J113" t="s">
+        <v>50</v>
+      </c>
+      <c r="K113" t="s">
+        <v>320</v>
+      </c>
+      <c r="L113" t="s">
+        <v>937</v>
+      </c>
+      <c r="M113" t="s">
+        <v>938</v>
+      </c>
+      <c r="N113" t="s">
+        <v>939</v>
+      </c>
+      <c r="O113" t="s">
+        <v>940</v>
+      </c>
+      <c r="P113" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
+      <c r="A114">
+        <v>1</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="C114" t="s">
+        <v>211</v>
+      </c>
+      <c r="D114">
+        <v>22</v>
+      </c>
+      <c r="E114" t="s">
+        <v>18</v>
+      </c>
+      <c r="F114" t="s">
+        <v>943</v>
+      </c>
+      <c r="G114" t="s">
+        <v>944</v>
+      </c>
+      <c r="H114" t="s">
+        <v>945</v>
+      </c>
+      <c r="I114" t="s">
+        <v>62</v>
+      </c>
+      <c r="J114" t="s">
+        <v>23</v>
+      </c>
+      <c r="K114" t="s">
+        <v>731</v>
+      </c>
+      <c r="L114" t="s">
+        <v>946</v>
+      </c>
+      <c r="M114" t="s">
+        <v>947</v>
+      </c>
+      <c r="N114" t="s">
+        <v>948</v>
+      </c>
+      <c r="O114" t="s">
+        <v>62</v>
+      </c>
+      <c r="P114" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
+      <c r="A115">
+        <v>2</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="C115" t="s">
+        <v>221</v>
+      </c>
+      <c r="D115">
+        <v>22</v>
+      </c>
+      <c r="E115" t="s">
+        <v>18</v>
+      </c>
+      <c r="F115" t="s">
+        <v>950</v>
+      </c>
+      <c r="G115" t="s">
+        <v>951</v>
+      </c>
+      <c r="H115" t="s">
+        <v>952</v>
+      </c>
+      <c r="I115" t="s">
+        <v>62</v>
+      </c>
+      <c r="J115" t="s">
+        <v>23</v>
+      </c>
+      <c r="K115" t="s">
+        <v>331</v>
+      </c>
+      <c r="L115" t="s">
+        <v>953</v>
+      </c>
+      <c r="M115" t="s">
+        <v>954</v>
+      </c>
+      <c r="N115" t="s">
+        <v>955</v>
+      </c>
+      <c r="O115" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
+      <c r="A116">
+        <v>3</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="C116" t="s">
+        <v>415</v>
+      </c>
+      <c r="D116">
+        <v>22</v>
+      </c>
+      <c r="E116" t="s">
+        <v>18</v>
+      </c>
+      <c r="F116" t="s">
+        <v>957</v>
+      </c>
+      <c r="G116" t="s">
+        <v>958</v>
+      </c>
+      <c r="H116" t="s">
+        <v>959</v>
+      </c>
+      <c r="I116" t="s">
+        <v>62</v>
+      </c>
+      <c r="J116" t="s">
+        <v>50</v>
+      </c>
+      <c r="K116" t="s">
+        <v>384</v>
+      </c>
+      <c r="L116" t="s">
+        <v>960</v>
+      </c>
+      <c r="M116" t="s">
+        <v>961</v>
+      </c>
+      <c r="N116" t="s">
+        <v>962</v>
+      </c>
+      <c r="O116" t="s">
+        <v>963</v>
+      </c>
+      <c r="P116" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
+      <c r="A117">
+        <v>4</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="C117" t="s">
+        <v>125</v>
+      </c>
+      <c r="D117">
+        <v>22</v>
+      </c>
+      <c r="E117" t="s">
+        <v>18</v>
+      </c>
+      <c r="F117" t="s">
+        <v>965</v>
+      </c>
+      <c r="G117" t="s">
+        <v>966</v>
+      </c>
+      <c r="H117" t="s">
+        <v>967</v>
+      </c>
+      <c r="I117" t="s">
+        <v>62</v>
+      </c>
+      <c r="J117" t="s">
+        <v>50</v>
+      </c>
+      <c r="K117" t="s">
+        <v>320</v>
+      </c>
+      <c r="L117" t="s">
+        <v>968</v>
+      </c>
+      <c r="M117" t="s">
+        <v>969</v>
+      </c>
+      <c r="N117" t="s">
+        <v>970</v>
+      </c>
+      <c r="O117" t="s">
+        <v>971</v>
+      </c>
+      <c r="P117" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
+      <c r="A118">
+        <v>1</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="C118" t="s">
+        <v>252</v>
+      </c>
+      <c r="D118">
+        <v>65</v>
+      </c>
+      <c r="E118" t="s">
+        <v>18</v>
+      </c>
+      <c r="F118" t="s">
+        <v>974</v>
+      </c>
+      <c r="G118" t="s">
+        <v>975</v>
+      </c>
+      <c r="H118" t="s">
+        <v>976</v>
+      </c>
+      <c r="I118" t="s">
+        <v>977</v>
+      </c>
+      <c r="J118" t="s">
+        <v>23</v>
+      </c>
+      <c r="K118" t="s">
+        <v>978</v>
+      </c>
+      <c r="L118" t="s">
+        <v>979</v>
+      </c>
+      <c r="M118" t="s">
+        <v>980</v>
+      </c>
+      <c r="N118" t="s">
+        <v>981</v>
+      </c>
+      <c r="O118" t="s">
+        <v>62</v>
+      </c>
+      <c r="P118" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
+      <c r="A119">
+        <v>2</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="C119" t="s">
+        <v>509</v>
+      </c>
+      <c r="D119">
+        <v>65</v>
+      </c>
+      <c r="E119" t="s">
+        <v>18</v>
+      </c>
+      <c r="F119" t="s">
+        <v>983</v>
+      </c>
+      <c r="G119" t="s">
+        <v>984</v>
+      </c>
+      <c r="H119" t="s">
+        <v>985</v>
+      </c>
+      <c r="I119" t="s">
+        <v>34</v>
+      </c>
+      <c r="J119" t="s">
+        <v>23</v>
+      </c>
+      <c r="K119" t="s">
+        <v>986</v>
+      </c>
+      <c r="L119" t="s">
+        <v>987</v>
+      </c>
+      <c r="M119" t="s">
+        <v>988</v>
+      </c>
+      <c r="N119" t="s">
+        <v>989</v>
+      </c>
+      <c r="O119" t="s">
+        <v>990</v>
+      </c>
+      <c r="P119" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
+      <c r="A120">
+        <v>3</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="C120" t="s">
+        <v>992</v>
+      </c>
+      <c r="D120">
+        <v>65</v>
+      </c>
+      <c r="E120" t="s">
+        <v>18</v>
+      </c>
+      <c r="F120" t="s">
+        <v>993</v>
+      </c>
+      <c r="G120" t="s">
+        <v>34</v>
+      </c>
+      <c r="H120" t="s">
+        <v>994</v>
+      </c>
+      <c r="I120" t="s">
+        <v>34</v>
+      </c>
+      <c r="J120" t="s">
+        <v>23</v>
+      </c>
+      <c r="K120" t="s">
+        <v>587</v>
+      </c>
+      <c r="L120" t="s">
+        <v>995</v>
+      </c>
+      <c r="M120" t="s">
+        <v>996</v>
+      </c>
+      <c r="N120" t="s">
+        <v>997</v>
+      </c>
+      <c r="O120" t="s">
+        <v>998</v>
+      </c>
+      <c r="P120" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
+      <c r="A121">
+        <v>4</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="C121" t="s">
+        <v>125</v>
+      </c>
+      <c r="D121">
+        <v>65</v>
+      </c>
+      <c r="E121" t="s">
+        <v>18</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G121" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H121" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I121" t="s">
+        <v>34</v>
+      </c>
+      <c r="J121" t="s">
+        <v>50</v>
+      </c>
+      <c r="K121" t="s">
+        <v>320</v>
+      </c>
+      <c r="L121" t="s">
+        <v>1003</v>
+      </c>
+      <c r="M121" t="s">
+        <v>1004</v>
+      </c>
+      <c r="N121" t="s">
+        <v>1005</v>
+      </c>
+      <c r="O121" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P121" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
+      <c r="A122">
+        <v>1</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C122" t="s">
+        <v>174</v>
+      </c>
+      <c r="D122">
+        <v>38</v>
+      </c>
+      <c r="E122" t="s">
+        <v>18</v>
+      </c>
+      <c r="F122" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G122" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H122" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I122" t="s">
+        <v>62</v>
+      </c>
+      <c r="J122" t="s">
+        <v>23</v>
+      </c>
+      <c r="K122" t="s">
+        <v>1012</v>
+      </c>
+      <c r="L122" t="s">
+        <v>1013</v>
+      </c>
+      <c r="M122" t="s">
+        <v>1014</v>
+      </c>
+      <c r="N122" t="s">
+        <v>1015</v>
+      </c>
+      <c r="O122" t="s">
+        <v>62</v>
+      </c>
+      <c r="P122" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
+      <c r="A123">
+        <v>2</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D123">
+        <v>38</v>
+      </c>
+      <c r="E123" t="s">
+        <v>18</v>
+      </c>
+      <c r="F123" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G123" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H123" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I123" t="s">
+        <v>34</v>
+      </c>
+      <c r="J123" t="s">
+        <v>23</v>
+      </c>
+      <c r="K123" t="s">
+        <v>1021</v>
+      </c>
+      <c r="L123" t="s">
+        <v>1022</v>
+      </c>
+      <c r="M123" t="s">
+        <v>1023</v>
+      </c>
+      <c r="N123" t="s">
+        <v>1024</v>
+      </c>
+      <c r="O123" t="s">
+        <v>1025</v>
+      </c>
+      <c r="P123" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
+      <c r="A124">
+        <v>3</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D124">
+        <v>38</v>
+      </c>
+      <c r="E124" t="s">
+        <v>18</v>
+      </c>
+      <c r="F124" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G124" t="s">
+        <v>382</v>
+      </c>
+      <c r="H124" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I124" t="s">
+        <v>34</v>
+      </c>
+      <c r="J124" t="s">
+        <v>50</v>
+      </c>
+      <c r="K124" t="s">
+        <v>1030</v>
+      </c>
+      <c r="L124" t="s">
+        <v>1031</v>
+      </c>
+      <c r="M124" t="s">
+        <v>1032</v>
+      </c>
+      <c r="N124" t="s">
+        <v>131</v>
+      </c>
+      <c r="O124" t="s">
+        <v>1033</v>
+      </c>
+      <c r="P124" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
+      <c r="A125">
+        <v>4</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C125" t="s">
+        <v>125</v>
+      </c>
+      <c r="D125">
+        <v>38</v>
+      </c>
+      <c r="E125" t="s">
+        <v>18</v>
+      </c>
+      <c r="F125" t="s">
+        <v>193</v>
+      </c>
+      <c r="G125" t="s">
+        <v>656</v>
+      </c>
+      <c r="H125" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I125" t="s">
+        <v>34</v>
+      </c>
+      <c r="J125" t="s">
+        <v>50</v>
+      </c>
+      <c r="K125" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L125" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M125" t="s">
+        <v>130</v>
+      </c>
+      <c r="N125" t="s">
+        <v>1038</v>
+      </c>
+      <c r="O125" t="s">
+        <v>1039</v>
+      </c>
+      <c r="P125" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16">
+      <c r="A126">
+        <v>1</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C126" t="s">
+        <v>211</v>
+      </c>
+      <c r="D126">
+        <v>52</v>
+      </c>
+      <c r="E126" t="s">
+        <v>58</v>
+      </c>
+      <c r="F126" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G126" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H126" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I126" t="s">
+        <v>1045</v>
+      </c>
+      <c r="J126" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K126" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L126" t="s">
+        <v>1048</v>
+      </c>
+      <c r="M126" t="s">
+        <v>1049</v>
+      </c>
+      <c r="N126" t="s">
+        <v>1050</v>
+      </c>
+      <c r="O126" t="s">
+        <v>62</v>
+      </c>
+      <c r="P126" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
+      <c r="A127">
+        <v>2</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D127">
+        <v>52</v>
+      </c>
+      <c r="E127" t="s">
+        <v>58</v>
+      </c>
+      <c r="F127" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G127" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H127" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I127" t="s">
+        <v>34</v>
+      </c>
+      <c r="J127" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K127" t="s">
+        <v>1056</v>
+      </c>
+      <c r="L127" t="s">
+        <v>1057</v>
+      </c>
+      <c r="M127" t="s">
+        <v>1058</v>
+      </c>
+      <c r="N127" t="s">
+        <v>1059</v>
+      </c>
+      <c r="O127" t="s">
+        <v>62</v>
+      </c>
+      <c r="P127" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
+      <c r="A128">
+        <v>3</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D128">
+        <v>52</v>
+      </c>
+      <c r="E128" t="s">
+        <v>58</v>
+      </c>
+      <c r="F128" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G128" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H128" t="s">
+        <v>1064</v>
+      </c>
+      <c r="I128" t="s">
+        <v>34</v>
+      </c>
+      <c r="J128" t="s">
+        <v>158</v>
+      </c>
+      <c r="K128" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L128" t="s">
+        <v>1066</v>
+      </c>
+      <c r="M128" t="s">
+        <v>1067</v>
+      </c>
+      <c r="N128" t="s">
+        <v>1068</v>
+      </c>
+      <c r="O128" t="s">
+        <v>1069</v>
+      </c>
+      <c r="P128" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
+      <c r="A129">
+        <v>4</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D129">
+        <v>52</v>
+      </c>
+      <c r="E129" t="s">
+        <v>58</v>
+      </c>
+      <c r="F129" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G129" t="s">
+        <v>382</v>
+      </c>
+      <c r="H129" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J129" t="s">
+        <v>50</v>
+      </c>
+      <c r="K129" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L129" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M129" t="s">
+        <v>1076</v>
+      </c>
+      <c r="N129" t="s">
+        <v>1077</v>
+      </c>
+      <c r="O129" t="s">
+        <v>1039</v>
+      </c>
+      <c r="P129" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
+      <c r="A130">
+        <v>1</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C130" t="s">
+        <v>174</v>
+      </c>
+      <c r="D130">
+        <v>68</v>
+      </c>
+      <c r="E130" t="s">
+        <v>18</v>
+      </c>
+      <c r="F130" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G130" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H130" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I130" t="s">
+        <v>821</v>
+      </c>
+      <c r="J130" t="s">
+        <v>793</v>
+      </c>
+      <c r="K130" t="s">
+        <v>1083</v>
+      </c>
+      <c r="L130" t="s">
+        <v>1084</v>
+      </c>
+      <c r="M130" t="s">
+        <v>1085</v>
+      </c>
+      <c r="N130" t="s">
+        <v>1086</v>
+      </c>
+      <c r="O130" t="s">
+        <v>62</v>
+      </c>
+      <c r="P130" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
+      <c r="A131">
+        <v>2</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C131" t="s">
+        <v>509</v>
+      </c>
+      <c r="D131">
+        <v>68</v>
+      </c>
+      <c r="E131" t="s">
+        <v>18</v>
+      </c>
+      <c r="F131" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G131" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H131" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I131" t="s">
+        <v>34</v>
+      </c>
+      <c r="J131" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K131" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L131" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M131" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N131" t="s">
+        <v>1095</v>
+      </c>
+      <c r="O131" t="s">
+        <v>62</v>
+      </c>
+      <c r="P131" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
+      <c r="A132">
+        <v>3</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D132">
+        <v>68</v>
+      </c>
+      <c r="E132" t="s">
+        <v>18</v>
+      </c>
+      <c r="F132" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G132" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H132" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I132" t="s">
+        <v>34</v>
+      </c>
+      <c r="J132" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K132" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L132" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M132" t="s">
+        <v>1103</v>
+      </c>
+      <c r="N132" t="s">
+        <v>1104</v>
+      </c>
+      <c r="O132" t="s">
+        <v>62</v>
+      </c>
+      <c r="P132" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
+      <c r="A133">
+        <v>4</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D133">
+        <v>68</v>
+      </c>
+      <c r="E133" t="s">
+        <v>18</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G133" t="s">
+        <v>382</v>
+      </c>
+      <c r="H133" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I133" t="s">
+        <v>34</v>
+      </c>
+      <c r="J133" t="s">
+        <v>50</v>
+      </c>
+      <c r="K133" t="s">
+        <v>358</v>
+      </c>
+      <c r="L133" t="s">
+        <v>1109</v>
+      </c>
+      <c r="M133" t="s">
+        <v>1110</v>
+      </c>
+      <c r="N133" t="s">
+        <v>1111</v>
+      </c>
+      <c r="O133" t="s">
+        <v>1112</v>
+      </c>
+      <c r="P133" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134">
+        <v>1</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C134" t="s">
+        <v>211</v>
+      </c>
+      <c r="D134">
+        <v>45</v>
+      </c>
+      <c r="E134" t="s">
+        <v>18</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G134" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H134" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I134" t="s">
+        <v>62</v>
+      </c>
+      <c r="J134" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K134" t="s">
+        <v>534</v>
+      </c>
+      <c r="L134" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M134" t="s">
+        <v>1119</v>
+      </c>
+      <c r="N134" t="s">
+        <v>1120</v>
+      </c>
+      <c r="O134" t="s">
+        <v>62</v>
+      </c>
+      <c r="P134" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135">
+        <v>2</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D135">
+        <v>45</v>
+      </c>
+      <c r="E135" t="s">
+        <v>18</v>
+      </c>
+      <c r="F135" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G135" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H135" t="s">
+        <v>1125</v>
+      </c>
+      <c r="I135" t="s">
+        <v>34</v>
+      </c>
+      <c r="J135" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K135" t="s">
+        <v>1126</v>
+      </c>
+      <c r="L135" t="s">
+        <v>1127</v>
+      </c>
+      <c r="M135" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N135" t="s">
+        <v>1120</v>
+      </c>
+      <c r="O135" t="s">
+        <v>1129</v>
+      </c>
+      <c r="P135" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
+      <c r="A136">
+        <v>3</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C136" t="s">
+        <v>415</v>
+      </c>
+      <c r="D136">
+        <v>45</v>
+      </c>
+      <c r="E136" t="s">
+        <v>18</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G136" t="s">
+        <v>382</v>
+      </c>
+      <c r="H136" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I136" t="s">
+        <v>34</v>
+      </c>
+      <c r="J136" t="s">
+        <v>50</v>
+      </c>
+      <c r="K136" t="s">
+        <v>358</v>
+      </c>
+      <c r="L136" t="s">
+        <v>686</v>
+      </c>
+      <c r="M136" t="s">
+        <v>1133</v>
+      </c>
+      <c r="N136" t="s">
+        <v>1134</v>
+      </c>
+      <c r="O136" t="s">
+        <v>1135</v>
+      </c>
+      <c r="P136" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
+      <c r="A137">
+        <v>4</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C137" t="s">
+        <v>125</v>
+      </c>
+      <c r="D137">
+        <v>45</v>
+      </c>
+      <c r="E137" t="s">
+        <v>18</v>
+      </c>
+      <c r="F137" t="s">
+        <v>193</v>
+      </c>
+      <c r="G137" t="s">
+        <v>656</v>
+      </c>
+      <c r="H137" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I137" t="s">
+        <v>34</v>
+      </c>
+      <c r="J137" t="s">
+        <v>50</v>
+      </c>
+      <c r="K137" t="s">
+        <v>91</v>
+      </c>
+      <c r="L137" t="s">
+        <v>786</v>
+      </c>
+      <c r="M137" t="s">
+        <v>1138</v>
+      </c>
+      <c r="N137" t="s">
+        <v>1134</v>
+      </c>
+      <c r="O137" t="s">
+        <v>1039</v>
+      </c>
+      <c r="P137" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
+      <c r="A138">
+        <v>1</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C138" t="s">
+        <v>174</v>
+      </c>
+      <c r="D138">
+        <v>38</v>
+      </c>
+      <c r="E138" t="s">
+        <v>58</v>
+      </c>
+      <c r="F138" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G138" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H138" t="s">
+        <v>1143</v>
+      </c>
+      <c r="I138" t="s">
+        <v>62</v>
+      </c>
+      <c r="J138" t="s">
+        <v>792</v>
+      </c>
+      <c r="K138" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L138" t="s">
+        <v>1145</v>
+      </c>
+      <c r="M138" t="s">
+        <v>1146</v>
+      </c>
+      <c r="N138" t="s">
+        <v>1147</v>
+      </c>
+      <c r="O138" t="s">
+        <v>62</v>
+      </c>
+      <c r="P138" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
+      <c r="A139">
+        <v>2</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C139" t="s">
+        <v>509</v>
+      </c>
+      <c r="D139">
+        <v>38</v>
+      </c>
+      <c r="E139" t="s">
+        <v>58</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G139" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H139" t="s">
+        <v>1150</v>
+      </c>
+      <c r="I139" t="s">
+        <v>34</v>
+      </c>
+      <c r="J139" t="s">
+        <v>792</v>
+      </c>
+      <c r="K139" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L139" t="s">
+        <v>1152</v>
+      </c>
+      <c r="M139" t="s">
+        <v>1153</v>
+      </c>
+      <c r="N139" t="s">
+        <v>1154</v>
+      </c>
+      <c r="O139" t="s">
+        <v>62</v>
+      </c>
+      <c r="P139" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
+      <c r="A140">
+        <v>3</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D140">
+        <v>38</v>
+      </c>
+      <c r="E140" t="s">
+        <v>58</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G140" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H140" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I140" t="s">
+        <v>34</v>
+      </c>
+      <c r="J140" t="s">
+        <v>792</v>
+      </c>
+      <c r="K140" t="s">
+        <v>1160</v>
+      </c>
+      <c r="L140" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M140" t="s">
+        <v>1162</v>
+      </c>
+      <c r="N140" t="s">
+        <v>1163</v>
+      </c>
+      <c r="O140" t="s">
+        <v>1164</v>
+      </c>
+      <c r="P140" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
+      <c r="A141">
+        <v>4</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D141">
+        <v>43</v>
+      </c>
+      <c r="E141" t="s">
+        <v>58</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G141" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H141" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I141" t="s">
+        <v>34</v>
+      </c>
+      <c r="J141" t="s">
+        <v>792</v>
+      </c>
+      <c r="K141" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L141" t="s">
+        <v>1171</v>
+      </c>
+      <c r="M141" t="s">
+        <v>1172</v>
+      </c>
+      <c r="N141" t="s">
+        <v>1173</v>
+      </c>
+      <c r="O141" t="s">
+        <v>625</v>
+      </c>
+      <c r="P141" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142">
+        <v>1</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C142" t="s">
+        <v>211</v>
+      </c>
+      <c r="D142">
+        <v>28</v>
+      </c>
+      <c r="E142" t="s">
+        <v>58</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G142" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H142" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I142" t="s">
+        <v>62</v>
+      </c>
+      <c r="J142" t="s">
+        <v>813</v>
+      </c>
+      <c r="K142" t="s">
+        <v>1179</v>
+      </c>
+      <c r="L142" t="s">
+        <v>1180</v>
+      </c>
+      <c r="M142" t="s">
+        <v>1181</v>
+      </c>
+      <c r="N142" t="s">
+        <v>1182</v>
+      </c>
+      <c r="O142" t="s">
+        <v>62</v>
+      </c>
+      <c r="P142" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143">
+        <v>2</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C143" t="s">
+        <v>443</v>
+      </c>
+      <c r="D143">
+        <v>28</v>
+      </c>
+      <c r="E143" t="s">
+        <v>58</v>
+      </c>
+      <c r="F143" t="s">
+        <v>1184</v>
+      </c>
+      <c r="G143" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H143" t="s">
+        <v>1186</v>
+      </c>
+      <c r="I143" t="s">
+        <v>34</v>
+      </c>
+      <c r="J143" t="s">
+        <v>813</v>
+      </c>
+      <c r="K143" t="s">
+        <v>23</v>
+      </c>
+      <c r="L143" t="s">
+        <v>1187</v>
+      </c>
+      <c r="M143" t="s">
+        <v>1188</v>
+      </c>
+      <c r="N143" t="s">
+        <v>1182</v>
+      </c>
+      <c r="O143" t="s">
+        <v>1189</v>
+      </c>
+      <c r="P143" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
+      <c r="A144">
+        <v>3</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D144">
+        <v>28</v>
+      </c>
+      <c r="E144" t="s">
+        <v>58</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G144" t="s">
+        <v>1193</v>
+      </c>
+      <c r="H144" t="s">
+        <v>1194</v>
+      </c>
+      <c r="I144" t="s">
+        <v>34</v>
+      </c>
+      <c r="J144" t="s">
+        <v>813</v>
+      </c>
+      <c r="K144" t="s">
+        <v>409</v>
+      </c>
+      <c r="L144" t="s">
+        <v>1195</v>
+      </c>
+      <c r="M144" t="s">
+        <v>1196</v>
+      </c>
+      <c r="N144" t="s">
+        <v>1197</v>
+      </c>
+      <c r="O144" t="s">
+        <v>1198</v>
+      </c>
+      <c r="P144" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
+      <c r="A145">
+        <v>4</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D145">
+        <v>28</v>
+      </c>
+      <c r="E145" t="s">
+        <v>58</v>
+      </c>
+      <c r="F145" t="s">
+        <v>193</v>
+      </c>
+      <c r="G145" t="s">
+        <v>382</v>
+      </c>
+      <c r="H145" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I145" t="s">
+        <v>34</v>
+      </c>
+      <c r="J145" t="s">
+        <v>813</v>
+      </c>
+      <c r="K145" t="s">
+        <v>91</v>
+      </c>
+      <c r="L145" t="s">
+        <v>1201</v>
+      </c>
+      <c r="M145" t="s">
+        <v>1202</v>
+      </c>
+      <c r="N145" t="s">
+        <v>1134</v>
+      </c>
+      <c r="O145" t="s">
+        <v>1203</v>
+      </c>
+      <c r="P145" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
+      <c r="A146">
+        <v>1</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C146" t="s">
+        <v>211</v>
+      </c>
+      <c r="D146">
+        <v>7</v>
+      </c>
+      <c r="E146" t="s">
+        <v>18</v>
+      </c>
+      <c r="F146" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G146" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H146" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I146" t="s">
+        <v>62</v>
+      </c>
+      <c r="J146" t="s">
+        <v>1209</v>
+      </c>
+      <c r="K146" t="s">
+        <v>1210</v>
+      </c>
+      <c r="L146" t="s">
+        <v>1211</v>
+      </c>
+      <c r="M146" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N146" t="s">
+        <v>1213</v>
+      </c>
+      <c r="O146" t="s">
+        <v>62</v>
+      </c>
+      <c r="P146" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
+      <c r="A147">
+        <v>2</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C147" t="s">
+        <v>221</v>
+      </c>
+      <c r="D147">
+        <v>7</v>
+      </c>
+      <c r="E147" t="s">
+        <v>18</v>
+      </c>
+      <c r="F147" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G147" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H147" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I147" t="s">
+        <v>34</v>
+      </c>
+      <c r="J147" t="s">
+        <v>1209</v>
+      </c>
+      <c r="K147" t="s">
+        <v>452</v>
+      </c>
+      <c r="L147" t="s">
+        <v>1218</v>
+      </c>
+      <c r="M147" t="s">
+        <v>1219</v>
+      </c>
+      <c r="N147" t="s">
+        <v>1220</v>
+      </c>
+      <c r="O147" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
+      <c r="A148">
+        <v>3</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D148">
+        <v>7</v>
+      </c>
+      <c r="E148" t="s">
+        <v>18</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G148" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H148" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I148" t="s">
+        <v>34</v>
+      </c>
+      <c r="J148" t="s">
+        <v>1209</v>
+      </c>
+      <c r="K148" t="s">
+        <v>1225</v>
+      </c>
+      <c r="L148" t="s">
+        <v>1226</v>
+      </c>
+      <c r="M148" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N148" t="s">
+        <v>1228</v>
+      </c>
+      <c r="O148" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
+      <c r="A149">
+        <v>4</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D149">
+        <v>7</v>
+      </c>
+      <c r="E149" t="s">
+        <v>18</v>
+      </c>
+      <c r="F149" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I149" t="s">
+        <v>34</v>
+      </c>
+      <c r="J149" t="s">
+        <v>1209</v>
+      </c>
+      <c r="K149" t="s">
+        <v>1233</v>
+      </c>
+      <c r="L149" t="s">
+        <v>1234</v>
+      </c>
+      <c r="M149" t="s">
+        <v>1235</v>
+      </c>
+      <c r="N149" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O149" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16">
+      <c r="A150">
+        <v>1</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C150" t="s">
+        <v>174</v>
+      </c>
+      <c r="D150">
+        <v>68</v>
+      </c>
+      <c r="E150" t="s">
+        <v>58</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H150" t="s">
+        <v>1240</v>
+      </c>
+      <c r="I150" t="s">
+        <v>1241</v>
+      </c>
+      <c r="J150" t="s">
+        <v>358</v>
+      </c>
+      <c r="K150" t="s">
+        <v>1242</v>
+      </c>
+      <c r="L150" t="s">
+        <v>1243</v>
+      </c>
+      <c r="M150" t="s">
+        <v>1244</v>
+      </c>
+      <c r="N150" t="s">
+        <v>1245</v>
+      </c>
+      <c r="O150" t="s">
+        <v>62</v>
+      </c>
+      <c r="P150" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
+      <c r="A151">
+        <v>2</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D151">
+        <v>68</v>
+      </c>
+      <c r="E151" t="s">
+        <v>58</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G151" t="s">
+        <v>34</v>
+      </c>
+      <c r="H151" t="s">
+        <v>1249</v>
+      </c>
+      <c r="I151" t="s">
+        <v>34</v>
+      </c>
+      <c r="J151" t="s">
+        <v>358</v>
+      </c>
+      <c r="K151" t="s">
+        <v>1250</v>
+      </c>
+      <c r="L151" t="s">
+        <v>1251</v>
+      </c>
+      <c r="M151" t="s">
+        <v>1245</v>
+      </c>
+      <c r="N151" t="s">
+        <v>1252</v>
+      </c>
+      <c r="O151" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
+      <c r="A152">
+        <v>3</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C152" t="s">
+        <v>296</v>
+      </c>
+      <c r="D152">
+        <v>68</v>
+      </c>
+      <c r="E152" t="s">
+        <v>58</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1254</v>
+      </c>
+      <c r="G152" t="s">
+        <v>1255</v>
+      </c>
+      <c r="H152" t="s">
+        <v>1256</v>
+      </c>
+      <c r="I152" t="s">
+        <v>34</v>
+      </c>
+      <c r="J152" t="s">
+        <v>358</v>
+      </c>
+      <c r="K152" t="s">
+        <v>1257</v>
+      </c>
+      <c r="L152" t="s">
+        <v>1258</v>
+      </c>
+      <c r="M152" t="s">
+        <v>1259</v>
+      </c>
+      <c r="N152" t="s">
+        <v>1260</v>
+      </c>
+      <c r="O152" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
+      <c r="A153">
+        <v>4</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D153">
+        <v>68</v>
+      </c>
+      <c r="E153" t="s">
+        <v>58</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G153" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H153" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I153" t="s">
+        <v>34</v>
+      </c>
+      <c r="J153" t="s">
+        <v>358</v>
+      </c>
+      <c r="K153" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L153" t="s">
+        <v>1266</v>
+      </c>
+      <c r="M153" t="s">
+        <v>1267</v>
+      </c>
+      <c r="N153" t="s">
+        <v>1268</v>
+      </c>
+      <c r="O153" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16">
+      <c r="A154">
+        <v>1</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C154" t="s">
+        <v>174</v>
+      </c>
+      <c r="D154">
+        <v>35</v>
+      </c>
+      <c r="E154" t="s">
+        <v>18</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G154" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H154" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I154" t="s">
+        <v>62</v>
+      </c>
+      <c r="J154" t="s">
+        <v>792</v>
+      </c>
+      <c r="K154" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L154" t="s">
+        <v>1275</v>
+      </c>
+      <c r="M154" t="s">
+        <v>1276</v>
+      </c>
+      <c r="N154" t="s">
+        <v>1277</v>
+      </c>
+      <c r="O154" t="s">
+        <v>62</v>
+      </c>
+      <c r="P154" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16">
+      <c r="A155">
+        <v>2</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D155">
+        <v>35</v>
+      </c>
+      <c r="E155" t="s">
+        <v>18</v>
+      </c>
+      <c r="F155" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G155" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H155" t="s">
+        <v>1281</v>
+      </c>
+      <c r="I155" t="s">
+        <v>34</v>
+      </c>
+      <c r="J155" t="s">
+        <v>792</v>
+      </c>
+      <c r="K155" t="s">
+        <v>1282</v>
+      </c>
+      <c r="L155" t="s">
+        <v>1283</v>
+      </c>
+      <c r="M155" t="s">
+        <v>1277</v>
+      </c>
+      <c r="N155" t="s">
+        <v>1284</v>
+      </c>
+      <c r="O155" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16">
+      <c r="A156">
+        <v>3</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D156">
+        <v>35</v>
+      </c>
+      <c r="E156" t="s">
+        <v>18</v>
+      </c>
+      <c r="F156" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G156" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H156" t="s">
+        <v>1289</v>
+      </c>
+      <c r="I156" t="s">
+        <v>34</v>
+      </c>
+      <c r="J156" t="s">
+        <v>792</v>
+      </c>
+      <c r="K156" t="s">
+        <v>1290</v>
+      </c>
+      <c r="L156" t="s">
+        <v>1291</v>
+      </c>
+      <c r="M156" t="s">
+        <v>1292</v>
+      </c>
+      <c r="N156" t="s">
+        <v>1220</v>
+      </c>
+      <c r="O156" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16">
+      <c r="A157">
+        <v>4</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D157">
+        <v>35</v>
+      </c>
+      <c r="E157" t="s">
+        <v>18</v>
+      </c>
+      <c r="F157" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G157" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H157" t="s">
+        <v>1296</v>
+      </c>
+      <c r="I157" t="s">
+        <v>34</v>
+      </c>
+      <c r="J157" t="s">
+        <v>792</v>
+      </c>
+      <c r="K157" t="s">
+        <v>1297</v>
+      </c>
+      <c r="L157" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M157" t="s">
+        <v>1299</v>
+      </c>
+      <c r="N157" t="s">
+        <v>1268</v>
+      </c>
+      <c r="O157" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16">
+      <c r="A158">
+        <v>1</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C158" t="s">
+        <v>174</v>
+      </c>
+      <c r="D158">
+        <v>45</v>
+      </c>
+      <c r="E158" t="s">
+        <v>18</v>
+      </c>
+      <c r="F158" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G158" t="s">
+        <v>1303</v>
+      </c>
+      <c r="H158" t="s">
+        <v>1304</v>
+      </c>
+      <c r="I158" t="s">
+        <v>1241</v>
+      </c>
+      <c r="J158" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K158" t="s">
+        <v>1305</v>
+      </c>
+      <c r="L158" t="s">
+        <v>1306</v>
+      </c>
+      <c r="M158" t="s">
+        <v>1307</v>
+      </c>
+      <c r="N158" t="s">
+        <v>1308</v>
+      </c>
+      <c r="O158" t="s">
+        <v>1309</v>
+      </c>
+      <c r="P158" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16">
+      <c r="A159">
+        <v>2</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C159" t="s">
+        <v>509</v>
+      </c>
+      <c r="D159">
+        <v>45</v>
+      </c>
+      <c r="E159" t="s">
+        <v>18</v>
+      </c>
+      <c r="F159" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G159" t="s">
+        <v>34</v>
+      </c>
+      <c r="H159" t="s">
+        <v>1312</v>
+      </c>
+      <c r="I159" t="s">
+        <v>34</v>
+      </c>
+      <c r="J159" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K159" t="s">
+        <v>1313</v>
+      </c>
+      <c r="L159" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M159" t="s">
+        <v>1308</v>
+      </c>
+      <c r="N159" t="s">
+        <v>1315</v>
+      </c>
+      <c r="O159" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16">
+      <c r="A160">
+        <v>3</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D160">
+        <v>45</v>
+      </c>
+      <c r="E160" t="s">
+        <v>18</v>
+      </c>
+      <c r="F160" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G160" t="s">
+        <v>118</v>
+      </c>
+      <c r="H160" t="s">
+        <v>1319</v>
+      </c>
+      <c r="I160" t="s">
+        <v>34</v>
+      </c>
+      <c r="J160" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K160" t="s">
+        <v>1320</v>
+      </c>
+      <c r="L160" t="s">
+        <v>1321</v>
+      </c>
+      <c r="M160" t="s">
+        <v>1308</v>
+      </c>
+      <c r="N160" t="s">
+        <v>1322</v>
+      </c>
+      <c r="O160" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16">
+      <c r="A161">
+        <v>4</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C161" t="s">
+        <v>125</v>
+      </c>
+      <c r="D161">
+        <v>45</v>
+      </c>
+      <c r="E161" t="s">
+        <v>18</v>
+      </c>
+      <c r="F161" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G161" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H161" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I161" t="s">
+        <v>34</v>
+      </c>
+      <c r="J161" t="s">
+        <v>50</v>
+      </c>
+      <c r="K161" t="s">
+        <v>1327</v>
+      </c>
+      <c r="L161" t="s">
+        <v>1328</v>
+      </c>
+      <c r="M161" t="s">
+        <v>1308</v>
+      </c>
+      <c r="N161" t="s">
+        <v>89</v>
+      </c>
+      <c r="O161" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16">
+      <c r="A162">
+        <v>1</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C162" t="s">
+        <v>174</v>
+      </c>
+      <c r="D162">
+        <v>32</v>
+      </c>
+      <c r="E162" t="s">
+        <v>58</v>
+      </c>
+      <c r="F162" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G162" t="s">
+        <v>1332</v>
+      </c>
+      <c r="H162" t="s">
+        <v>1333</v>
+      </c>
+      <c r="I162" t="s">
+        <v>62</v>
+      </c>
+      <c r="J162" t="s">
+        <v>813</v>
+      </c>
+      <c r="K162" t="s">
+        <v>1334</v>
+      </c>
+      <c r="L162" t="s">
+        <v>1335</v>
+      </c>
+      <c r="M162" t="s">
+        <v>1336</v>
+      </c>
+      <c r="N162" t="s">
+        <v>1337</v>
+      </c>
+      <c r="O162" t="s">
+        <v>62</v>
+      </c>
+      <c r="P162" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16">
+      <c r="A163">
+        <v>2</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C163" t="s">
+        <v>443</v>
+      </c>
+      <c r="D163">
+        <v>32</v>
+      </c>
+      <c r="E163" t="s">
+        <v>58</v>
+      </c>
+      <c r="F163" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G163" t="s">
+        <v>34</v>
+      </c>
+      <c r="H163" t="s">
+        <v>1340</v>
+      </c>
+      <c r="I163" t="s">
+        <v>34</v>
+      </c>
+      <c r="J163" t="s">
+        <v>813</v>
+      </c>
+      <c r="K163" t="s">
+        <v>1341</v>
+      </c>
+      <c r="L163" t="s">
+        <v>1342</v>
+      </c>
+      <c r="M163" t="s">
+        <v>1337</v>
+      </c>
+      <c r="N163" t="s">
+        <v>1343</v>
+      </c>
+      <c r="O163" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16">
+      <c r="A164">
+        <v>3</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D164">
+        <v>32</v>
+      </c>
+      <c r="E164" t="s">
+        <v>58</v>
+      </c>
+      <c r="F164" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G164" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H164" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I164" t="s">
+        <v>34</v>
+      </c>
+      <c r="J164" t="s">
+        <v>813</v>
+      </c>
+      <c r="K164" t="s">
+        <v>158</v>
+      </c>
+      <c r="L164" t="s">
+        <v>1349</v>
+      </c>
+      <c r="M164" t="s">
+        <v>1350</v>
+      </c>
+      <c r="N164" t="s">
+        <v>1351</v>
+      </c>
+      <c r="O164" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16">
+      <c r="A165">
+        <v>4</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D165">
+        <v>32</v>
+      </c>
+      <c r="E165" t="s">
+        <v>58</v>
+      </c>
+      <c r="F165" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G165" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H165" t="s">
+        <v>1355</v>
+      </c>
+      <c r="I165" t="s">
+        <v>34</v>
+      </c>
+      <c r="J165" t="s">
+        <v>813</v>
+      </c>
+      <c r="K165" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L165" t="s">
+        <v>1356</v>
+      </c>
+      <c r="M165" t="s">
+        <v>1357</v>
+      </c>
+      <c r="N165" t="s">
+        <v>1358</v>
+      </c>
+      <c r="O165" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16">
+      <c r="A166">
+        <v>1</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C166" t="s">
+        <v>174</v>
+      </c>
+      <c r="D166">
+        <v>26</v>
+      </c>
+      <c r="E166" t="s">
+        <v>58</v>
+      </c>
+      <c r="F166" t="s">
+        <v>1361</v>
+      </c>
+      <c r="G166" t="s">
+        <v>1362</v>
+      </c>
+      <c r="H166" t="s">
+        <v>1363</v>
+      </c>
+      <c r="I166" t="s">
+        <v>62</v>
+      </c>
+      <c r="J166" t="s">
+        <v>792</v>
+      </c>
+      <c r="K166" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L166" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M166" t="s">
+        <v>1366</v>
+      </c>
+      <c r="N166" t="s">
+        <v>1367</v>
+      </c>
+      <c r="O166" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16">
+      <c r="A167">
+        <v>2</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D167">
+        <v>26</v>
+      </c>
+      <c r="E167" t="s">
+        <v>58</v>
+      </c>
+      <c r="F167" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G167" t="s">
+        <v>34</v>
+      </c>
+      <c r="H167" t="s">
+        <v>1371</v>
+      </c>
+      <c r="I167" t="s">
+        <v>34</v>
+      </c>
+      <c r="J167" t="s">
+        <v>792</v>
+      </c>
+      <c r="K167" t="s">
+        <v>1372</v>
+      </c>
+      <c r="L167" t="s">
+        <v>1373</v>
+      </c>
+      <c r="M167" t="s">
+        <v>1366</v>
+      </c>
+      <c r="N167" t="s">
+        <v>1315</v>
+      </c>
+      <c r="O167" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16">
+      <c r="A168">
+        <v>3</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D168">
+        <v>26</v>
+      </c>
+      <c r="E168" t="s">
+        <v>58</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G168" t="s">
+        <v>1377</v>
+      </c>
+      <c r="H168" t="s">
+        <v>1378</v>
+      </c>
+      <c r="I168" t="s">
+        <v>34</v>
+      </c>
+      <c r="J168" t="s">
+        <v>792</v>
+      </c>
+      <c r="K168" t="s">
+        <v>1379</v>
+      </c>
+      <c r="L168" t="s">
+        <v>1380</v>
+      </c>
+      <c r="M168" t="s">
+        <v>1366</v>
+      </c>
+      <c r="N168" t="s">
+        <v>1381</v>
+      </c>
+      <c r="O168" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16">
+      <c r="A169">
+        <v>4</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D169">
+        <v>26</v>
+      </c>
+      <c r="E169" t="s">
+        <v>58</v>
+      </c>
+      <c r="F169" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G169" t="s">
+        <v>1385</v>
+      </c>
+      <c r="H169" t="s">
+        <v>1386</v>
+      </c>
+      <c r="I169" t="s">
+        <v>34</v>
+      </c>
+      <c r="J169" t="s">
+        <v>792</v>
+      </c>
+      <c r="K169" t="s">
+        <v>1387</v>
+      </c>
+      <c r="L169" t="s">
+        <v>1388</v>
+      </c>
+      <c r="M169" t="s">
+        <v>1389</v>
+      </c>
+      <c r="N169" t="s">
+        <v>1390</v>
+      </c>
+      <c r="O169" t="s">
+        <v>1391</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data/病人设定.xlsx
+++ b/data/病人设定.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2359" uniqueCount="1392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="1391">
   <si>
     <t>情境编号</t>
   </si>
@@ -2207,7 +2207,7 @@
     <t>患者行颈椎肿瘤切除内固定+肋骨肿瘤切除术，术后症状好转。病理确诊肺来源转移性腺癌。家属咨询后续治疗方案。请你向家属解释后续治疗（化疗、靶向等）及预后。</t>
   </si>
   <si>
-    <t>“脑中风的警报”</t>
+    <t>“半身风云”</t>
   </si>
   <si>
     <t>突发右侧肢体无力、麻木，言语不清，口角左偏</t>
@@ -2304,9 +2304,6 @@
   </si>
   <si>
     <t>出院前患者右侧肢体肌力恢复至4级，言语清晰。需指导二级预防药物（阿司匹林、他汀）、生活方式调整及定期随访。请你进行出院宣教。</t>
-  </si>
-  <si>
-    <t>“半身风云”</t>
   </si>
   <si>
     <t>“惊厥之舞”</t>
@@ -5167,7 +5164,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P169"/>
+  <dimension ref="A1:P165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="9.02654867256637" style="1"/>
@@ -9428,46 +9425,46 @@
         <v>759</v>
       </c>
       <c r="C86" t="s">
-        <v>286</v>
+        <v>211</v>
       </c>
       <c r="D86">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="E86" t="s">
         <v>18</v>
       </c>
       <c r="F86" t="s">
-        <v>727</v>
+        <v>760</v>
       </c>
       <c r="G86" t="s">
-        <v>728</v>
+        <v>761</v>
       </c>
       <c r="H86" t="s">
-        <v>729</v>
+        <v>762</v>
       </c>
       <c r="I86" t="s">
-        <v>730</v>
+        <v>62</v>
       </c>
       <c r="J86" t="s">
         <v>23</v>
       </c>
       <c r="K86" t="s">
-        <v>731</v>
+        <v>763</v>
       </c>
       <c r="L86" t="s">
         <v>732</v>
       </c>
       <c r="M86" t="s">
-        <v>733</v>
+        <v>764</v>
       </c>
       <c r="N86" t="s">
-        <v>734</v>
+        <v>765</v>
       </c>
       <c r="O86" t="s">
         <v>62</v>
       </c>
       <c r="P86" t="s">
-        <v>735</v>
+        <v>766</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -9478,25 +9475,25 @@
         <v>759</v>
       </c>
       <c r="C87" t="s">
-        <v>443</v>
+        <v>509</v>
       </c>
       <c r="D87">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
         <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>736</v>
+        <v>767</v>
       </c>
       <c r="G87" t="s">
-        <v>737</v>
+        <v>34</v>
       </c>
       <c r="H87" t="s">
-        <v>738</v>
+        <v>768</v>
       </c>
       <c r="I87" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J87" t="s">
         <v>23</v>
@@ -9505,19 +9502,19 @@
         <v>331</v>
       </c>
       <c r="L87" t="s">
-        <v>739</v>
+        <v>769</v>
       </c>
       <c r="M87" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="N87" t="s">
-        <v>741</v>
+        <v>771</v>
       </c>
       <c r="O87" t="s">
-        <v>742</v>
+        <v>62</v>
       </c>
       <c r="P87" t="s">
-        <v>743</v>
+        <v>772</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -9528,25 +9525,25 @@
         <v>759</v>
       </c>
       <c r="C88" t="s">
-        <v>744</v>
+        <v>548</v>
       </c>
       <c r="D88">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="E88" t="s">
         <v>18</v>
       </c>
       <c r="F88" t="s">
-        <v>745</v>
+        <v>773</v>
       </c>
       <c r="G88" t="s">
-        <v>746</v>
+        <v>382</v>
       </c>
       <c r="H88" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="I88" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J88" t="s">
         <v>50</v>
@@ -9555,19 +9552,19 @@
         <v>384</v>
       </c>
       <c r="L88" t="s">
-        <v>748</v>
+        <v>775</v>
       </c>
       <c r="M88" t="s">
-        <v>749</v>
+        <v>776</v>
       </c>
       <c r="N88" t="s">
-        <v>750</v>
+        <v>771</v>
       </c>
       <c r="O88" t="s">
-        <v>751</v>
+        <v>777</v>
       </c>
       <c r="P88" t="s">
-        <v>752</v>
+        <v>778</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -9581,22 +9578,22 @@
         <v>125</v>
       </c>
       <c r="D89">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="E89" t="s">
         <v>18</v>
       </c>
       <c r="F89" t="s">
-        <v>753</v>
+        <v>779</v>
       </c>
       <c r="G89" t="s">
-        <v>754</v>
+        <v>780</v>
       </c>
       <c r="H89" t="s">
-        <v>755</v>
+        <v>781</v>
       </c>
       <c r="I89" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J89" t="s">
         <v>50</v>
@@ -9605,19 +9602,19 @@
         <v>320</v>
       </c>
       <c r="L89" t="s">
-        <v>658</v>
+        <v>782</v>
       </c>
       <c r="M89" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="N89" t="s">
-        <v>750</v>
+        <v>784</v>
       </c>
       <c r="O89" t="s">
-        <v>757</v>
+        <v>785</v>
       </c>
       <c r="P89" t="s">
-        <v>758</v>
+        <v>786</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -9625,49 +9622,49 @@
         <v>1</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="C90" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="D90">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E90" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F90" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="G90" t="s">
-        <v>762</v>
+        <v>789</v>
       </c>
       <c r="H90" t="s">
-        <v>763</v>
+        <v>790</v>
       </c>
       <c r="I90" t="s">
         <v>62</v>
       </c>
       <c r="J90" t="s">
-        <v>23</v>
+        <v>791</v>
       </c>
       <c r="K90" t="s">
-        <v>764</v>
+        <v>792</v>
       </c>
       <c r="L90" t="s">
-        <v>732</v>
+        <v>793</v>
       </c>
       <c r="M90" t="s">
-        <v>765</v>
+        <v>794</v>
       </c>
       <c r="N90" t="s">
-        <v>766</v>
+        <v>795</v>
       </c>
       <c r="O90" t="s">
         <v>62</v>
       </c>
       <c r="P90" t="s">
-        <v>767</v>
+        <v>796</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -9675,49 +9672,49 @@
         <v>2</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="C91" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="D91">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E91" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F91" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="G91" t="s">
         <v>34</v>
       </c>
       <c r="H91" t="s">
-        <v>769</v>
+        <v>798</v>
       </c>
       <c r="I91" t="s">
         <v>62</v>
       </c>
       <c r="J91" t="s">
-        <v>23</v>
+        <v>791</v>
       </c>
       <c r="K91" t="s">
         <v>331</v>
       </c>
       <c r="L91" t="s">
-        <v>770</v>
+        <v>799</v>
       </c>
       <c r="M91" t="s">
-        <v>771</v>
+        <v>800</v>
       </c>
       <c r="N91" t="s">
-        <v>772</v>
+        <v>795</v>
       </c>
       <c r="O91" t="s">
         <v>62</v>
       </c>
       <c r="P91" t="s">
-        <v>773</v>
+        <v>801</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -9725,49 +9722,49 @@
         <v>3</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="C92" t="s">
-        <v>548</v>
+        <v>802</v>
       </c>
       <c r="D92">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E92" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F92" t="s">
-        <v>774</v>
+        <v>803</v>
       </c>
       <c r="G92" t="s">
         <v>382</v>
       </c>
       <c r="H92" t="s">
-        <v>775</v>
+        <v>804</v>
       </c>
       <c r="I92" t="s">
         <v>62</v>
       </c>
       <c r="J92" t="s">
-        <v>50</v>
+        <v>791</v>
       </c>
       <c r="K92" t="s">
         <v>384</v>
       </c>
       <c r="L92" t="s">
-        <v>776</v>
+        <v>805</v>
       </c>
       <c r="M92" t="s">
-        <v>777</v>
+        <v>806</v>
       </c>
       <c r="N92" t="s">
-        <v>772</v>
+        <v>795</v>
       </c>
       <c r="O92" t="s">
-        <v>778</v>
+        <v>807</v>
       </c>
       <c r="P92" t="s">
-        <v>779</v>
+        <v>808</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -9775,49 +9772,49 @@
         <v>4</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="C93" t="s">
         <v>125</v>
       </c>
       <c r="D93">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E93" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F93" t="s">
-        <v>780</v>
+        <v>809</v>
       </c>
       <c r="G93" t="s">
-        <v>781</v>
+        <v>810</v>
       </c>
       <c r="H93" t="s">
-        <v>782</v>
+        <v>811</v>
       </c>
       <c r="I93" t="s">
         <v>62</v>
       </c>
       <c r="J93" t="s">
-        <v>50</v>
+        <v>812</v>
       </c>
       <c r="K93" t="s">
         <v>320</v>
       </c>
       <c r="L93" t="s">
-        <v>783</v>
+        <v>658</v>
       </c>
       <c r="M93" t="s">
-        <v>784</v>
+        <v>813</v>
       </c>
       <c r="N93" t="s">
+        <v>814</v>
+      </c>
+      <c r="O93" t="s">
         <v>785</v>
       </c>
-      <c r="O93" t="s">
-        <v>786</v>
-      </c>
       <c r="P93" t="s">
-        <v>787</v>
+        <v>815</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -9825,49 +9822,49 @@
         <v>1</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="C94" t="s">
         <v>252</v>
       </c>
       <c r="D94">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E94" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F94" t="s">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="G94" t="s">
-        <v>790</v>
+        <v>818</v>
       </c>
       <c r="H94" t="s">
-        <v>791</v>
+        <v>819</v>
       </c>
       <c r="I94" t="s">
-        <v>62</v>
+        <v>820</v>
       </c>
       <c r="J94" t="s">
-        <v>792</v>
+        <v>23</v>
       </c>
       <c r="K94" t="s">
-        <v>793</v>
+        <v>409</v>
       </c>
       <c r="L94" t="s">
-        <v>794</v>
+        <v>471</v>
       </c>
       <c r="M94" t="s">
-        <v>795</v>
+        <v>821</v>
       </c>
       <c r="N94" t="s">
-        <v>796</v>
+        <v>822</v>
       </c>
       <c r="O94" t="s">
         <v>62</v>
       </c>
       <c r="P94" t="s">
-        <v>797</v>
+        <v>823</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -9875,49 +9872,49 @@
         <v>2</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="C95" t="s">
-        <v>548</v>
+        <v>221</v>
       </c>
       <c r="D95">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E95" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F95" t="s">
-        <v>798</v>
+        <v>824</v>
       </c>
       <c r="G95" t="s">
+        <v>825</v>
+      </c>
+      <c r="H95" t="s">
+        <v>826</v>
+      </c>
+      <c r="I95" t="s">
         <v>34</v>
       </c>
-      <c r="H95" t="s">
-        <v>799</v>
-      </c>
-      <c r="I95" t="s">
-        <v>62</v>
-      </c>
       <c r="J95" t="s">
-        <v>792</v>
+        <v>23</v>
       </c>
       <c r="K95" t="s">
         <v>331</v>
       </c>
       <c r="L95" t="s">
-        <v>800</v>
+        <v>827</v>
       </c>
       <c r="M95" t="s">
-        <v>801</v>
+        <v>828</v>
       </c>
       <c r="N95" t="s">
-        <v>796</v>
+        <v>829</v>
       </c>
       <c r="O95" t="s">
-        <v>62</v>
+        <v>830</v>
       </c>
       <c r="P95" t="s">
-        <v>802</v>
+        <v>831</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -9925,49 +9922,49 @@
         <v>3</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="C96" t="s">
-        <v>803</v>
+        <v>415</v>
       </c>
       <c r="D96">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E96" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F96" t="s">
-        <v>804</v>
+        <v>832</v>
       </c>
       <c r="G96" t="s">
-        <v>382</v>
+        <v>833</v>
       </c>
       <c r="H96" t="s">
-        <v>805</v>
+        <v>834</v>
       </c>
       <c r="I96" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="J96" t="s">
-        <v>792</v>
+        <v>50</v>
       </c>
       <c r="K96" t="s">
         <v>384</v>
       </c>
       <c r="L96" t="s">
-        <v>806</v>
+        <v>835</v>
       </c>
       <c r="M96" t="s">
-        <v>807</v>
+        <v>836</v>
       </c>
       <c r="N96" t="s">
-        <v>796</v>
+        <v>323</v>
       </c>
       <c r="O96" t="s">
-        <v>808</v>
+        <v>837</v>
       </c>
       <c r="P96" t="s">
-        <v>809</v>
+        <v>838</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -9975,49 +9972,49 @@
         <v>4</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="C97" t="s">
         <v>125</v>
       </c>
       <c r="D97">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E97" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F97" t="s">
-        <v>810</v>
+        <v>839</v>
       </c>
       <c r="G97" t="s">
-        <v>811</v>
+        <v>840</v>
       </c>
       <c r="H97" t="s">
-        <v>812</v>
+        <v>841</v>
       </c>
       <c r="I97" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="J97" t="s">
-        <v>813</v>
+        <v>50</v>
       </c>
       <c r="K97" t="s">
         <v>320</v>
       </c>
       <c r="L97" t="s">
-        <v>658</v>
+        <v>842</v>
       </c>
       <c r="M97" t="s">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="N97" t="s">
-        <v>815</v>
+        <v>323</v>
       </c>
       <c r="O97" t="s">
-        <v>786</v>
+        <v>751</v>
       </c>
       <c r="P97" t="s">
-        <v>816</v>
+        <v>844</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -10025,28 +10022,28 @@
         <v>1</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>817</v>
+        <v>845</v>
       </c>
       <c r="C98" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="D98">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E98" t="s">
         <v>18</v>
       </c>
       <c r="F98" t="s">
-        <v>818</v>
+        <v>846</v>
       </c>
       <c r="G98" t="s">
-        <v>819</v>
+        <v>847</v>
       </c>
       <c r="H98" t="s">
-        <v>820</v>
+        <v>848</v>
       </c>
       <c r="I98" t="s">
-        <v>821</v>
+        <v>730</v>
       </c>
       <c r="J98" t="s">
         <v>23</v>
@@ -10055,19 +10052,19 @@
         <v>409</v>
       </c>
       <c r="L98" t="s">
-        <v>471</v>
+        <v>849</v>
       </c>
       <c r="M98" t="s">
-        <v>822</v>
+        <v>850</v>
       </c>
       <c r="N98" t="s">
-        <v>823</v>
+        <v>851</v>
       </c>
       <c r="O98" t="s">
         <v>62</v>
       </c>
       <c r="P98" t="s">
-        <v>824</v>
+        <v>852</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -10075,25 +10072,25 @@
         <v>2</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>817</v>
+        <v>845</v>
       </c>
       <c r="C99" t="s">
-        <v>221</v>
+        <v>443</v>
       </c>
       <c r="D99">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E99" t="s">
         <v>18</v>
       </c>
       <c r="F99" t="s">
-        <v>825</v>
+        <v>853</v>
       </c>
       <c r="G99" t="s">
-        <v>826</v>
+        <v>854</v>
       </c>
       <c r="H99" t="s">
-        <v>827</v>
+        <v>855</v>
       </c>
       <c r="I99" t="s">
         <v>34</v>
@@ -10105,19 +10102,19 @@
         <v>331</v>
       </c>
       <c r="L99" t="s">
-        <v>828</v>
+        <v>856</v>
       </c>
       <c r="M99" t="s">
-        <v>829</v>
+        <v>857</v>
       </c>
       <c r="N99" t="s">
-        <v>830</v>
+        <v>858</v>
       </c>
       <c r="O99" t="s">
-        <v>831</v>
+        <v>859</v>
       </c>
       <c r="P99" t="s">
-        <v>832</v>
+        <v>860</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -10125,25 +10122,25 @@
         <v>3</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>817</v>
+        <v>845</v>
       </c>
       <c r="C100" t="s">
-        <v>415</v>
+        <v>861</v>
       </c>
       <c r="D100">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E100" t="s">
         <v>18</v>
       </c>
       <c r="F100" t="s">
-        <v>833</v>
+        <v>862</v>
       </c>
       <c r="G100" t="s">
-        <v>834</v>
+        <v>863</v>
       </c>
       <c r="H100" t="s">
-        <v>835</v>
+        <v>864</v>
       </c>
       <c r="I100" t="s">
         <v>34</v>
@@ -10155,19 +10152,19 @@
         <v>384</v>
       </c>
       <c r="L100" t="s">
-        <v>836</v>
+        <v>865</v>
       </c>
       <c r="M100" t="s">
-        <v>837</v>
+        <v>866</v>
       </c>
       <c r="N100" t="s">
-        <v>323</v>
+        <v>867</v>
       </c>
       <c r="O100" t="s">
-        <v>838</v>
+        <v>868</v>
       </c>
       <c r="P100" t="s">
-        <v>839</v>
+        <v>869</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -10175,25 +10172,25 @@
         <v>4</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>817</v>
+        <v>845</v>
       </c>
       <c r="C101" t="s">
         <v>125</v>
       </c>
       <c r="D101">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E101" t="s">
         <v>18</v>
       </c>
       <c r="F101" t="s">
-        <v>840</v>
+        <v>193</v>
       </c>
       <c r="G101" t="s">
-        <v>841</v>
+        <v>870</v>
       </c>
       <c r="H101" t="s">
-        <v>842</v>
+        <v>871</v>
       </c>
       <c r="I101" t="s">
         <v>34</v>
@@ -10205,19 +10202,19 @@
         <v>320</v>
       </c>
       <c r="L101" t="s">
-        <v>843</v>
+        <v>872</v>
       </c>
       <c r="M101" t="s">
-        <v>844</v>
+        <v>873</v>
       </c>
       <c r="N101" t="s">
-        <v>323</v>
+        <v>874</v>
       </c>
       <c r="O101" t="s">
-        <v>751</v>
+        <v>875</v>
       </c>
       <c r="P101" t="s">
-        <v>845</v>
+        <v>876</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -10225,49 +10222,49 @@
         <v>1</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>846</v>
+        <v>877</v>
       </c>
       <c r="C102" t="s">
-        <v>211</v>
+        <v>878</v>
       </c>
       <c r="D102">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E102" t="s">
         <v>18</v>
       </c>
       <c r="F102" t="s">
-        <v>847</v>
+        <v>879</v>
       </c>
       <c r="G102" t="s">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="H102" t="s">
-        <v>849</v>
+        <v>881</v>
       </c>
       <c r="I102" t="s">
-        <v>730</v>
+        <v>882</v>
       </c>
       <c r="J102" t="s">
         <v>23</v>
       </c>
       <c r="K102" t="s">
-        <v>409</v>
+        <v>158</v>
       </c>
       <c r="L102" t="s">
-        <v>850</v>
+        <v>883</v>
       </c>
       <c r="M102" t="s">
-        <v>851</v>
+        <v>884</v>
       </c>
       <c r="N102" t="s">
-        <v>852</v>
+        <v>885</v>
       </c>
       <c r="O102" t="s">
         <v>62</v>
       </c>
       <c r="P102" t="s">
-        <v>853</v>
+        <v>886</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -10275,25 +10272,25 @@
         <v>2</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>846</v>
+        <v>877</v>
       </c>
       <c r="C103" t="s">
         <v>443</v>
       </c>
       <c r="D103">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E103" t="s">
         <v>18</v>
       </c>
       <c r="F103" t="s">
-        <v>854</v>
+        <v>887</v>
       </c>
       <c r="G103" t="s">
-        <v>855</v>
+        <v>888</v>
       </c>
       <c r="H103" t="s">
-        <v>856</v>
+        <v>889</v>
       </c>
       <c r="I103" t="s">
         <v>34</v>
@@ -10305,19 +10302,19 @@
         <v>331</v>
       </c>
       <c r="L103" t="s">
-        <v>857</v>
+        <v>890</v>
       </c>
       <c r="M103" t="s">
-        <v>858</v>
+        <v>891</v>
       </c>
       <c r="N103" t="s">
-        <v>859</v>
+        <v>892</v>
       </c>
       <c r="O103" t="s">
-        <v>860</v>
+        <v>893</v>
       </c>
       <c r="P103" t="s">
-        <v>861</v>
+        <v>894</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -10325,25 +10322,25 @@
         <v>3</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>846</v>
+        <v>877</v>
       </c>
       <c r="C104" t="s">
-        <v>862</v>
+        <v>617</v>
       </c>
       <c r="D104">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E104" t="s">
         <v>18</v>
       </c>
       <c r="F104" t="s">
-        <v>863</v>
+        <v>895</v>
       </c>
       <c r="G104" t="s">
-        <v>864</v>
+        <v>896</v>
       </c>
       <c r="H104" t="s">
-        <v>865</v>
+        <v>897</v>
       </c>
       <c r="I104" t="s">
         <v>34</v>
@@ -10355,19 +10352,19 @@
         <v>384</v>
       </c>
       <c r="L104" t="s">
-        <v>866</v>
+        <v>898</v>
       </c>
       <c r="M104" t="s">
-        <v>867</v>
+        <v>899</v>
       </c>
       <c r="N104" t="s">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="O104" t="s">
-        <v>869</v>
+        <v>901</v>
       </c>
       <c r="P104" t="s">
-        <v>870</v>
+        <v>902</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -10375,25 +10372,25 @@
         <v>4</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>846</v>
+        <v>877</v>
       </c>
       <c r="C105" t="s">
         <v>125</v>
       </c>
       <c r="D105">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E105" t="s">
         <v>18</v>
       </c>
       <c r="F105" t="s">
-        <v>193</v>
+        <v>903</v>
       </c>
       <c r="G105" t="s">
-        <v>871</v>
+        <v>904</v>
       </c>
       <c r="H105" t="s">
-        <v>872</v>
+        <v>905</v>
       </c>
       <c r="I105" t="s">
         <v>34</v>
@@ -10405,19 +10402,19 @@
         <v>320</v>
       </c>
       <c r="L105" t="s">
-        <v>873</v>
+        <v>658</v>
       </c>
       <c r="M105" t="s">
-        <v>874</v>
+        <v>906</v>
       </c>
       <c r="N105" t="s">
-        <v>875</v>
+        <v>907</v>
       </c>
       <c r="O105" t="s">
-        <v>876</v>
+        <v>908</v>
       </c>
       <c r="P105" t="s">
-        <v>877</v>
+        <v>909</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -10425,49 +10422,49 @@
         <v>1</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>878</v>
+        <v>910</v>
       </c>
       <c r="C106" t="s">
-        <v>879</v>
+        <v>211</v>
       </c>
       <c r="D106">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E106" t="s">
         <v>18</v>
       </c>
       <c r="F106" t="s">
-        <v>880</v>
+        <v>911</v>
       </c>
       <c r="G106" t="s">
-        <v>881</v>
+        <v>912</v>
       </c>
       <c r="H106" t="s">
-        <v>882</v>
+        <v>913</v>
       </c>
       <c r="I106" t="s">
-        <v>883</v>
+        <v>914</v>
       </c>
       <c r="J106" t="s">
         <v>23</v>
       </c>
       <c r="K106" t="s">
-        <v>158</v>
+        <v>731</v>
       </c>
       <c r="L106" t="s">
-        <v>884</v>
+        <v>915</v>
       </c>
       <c r="M106" t="s">
-        <v>885</v>
+        <v>916</v>
       </c>
       <c r="N106" t="s">
-        <v>886</v>
+        <v>917</v>
       </c>
       <c r="O106" t="s">
         <v>62</v>
       </c>
       <c r="P106" t="s">
-        <v>887</v>
+        <v>918</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -10475,25 +10472,25 @@
         <v>2</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>878</v>
+        <v>910</v>
       </c>
       <c r="C107" t="s">
         <v>443</v>
       </c>
       <c r="D107">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E107" t="s">
         <v>18</v>
       </c>
       <c r="F107" t="s">
-        <v>888</v>
+        <v>919</v>
       </c>
       <c r="G107" t="s">
-        <v>889</v>
+        <v>920</v>
       </c>
       <c r="H107" t="s">
-        <v>890</v>
+        <v>921</v>
       </c>
       <c r="I107" t="s">
         <v>34</v>
@@ -10505,19 +10502,19 @@
         <v>331</v>
       </c>
       <c r="L107" t="s">
-        <v>891</v>
+        <v>922</v>
       </c>
       <c r="M107" t="s">
-        <v>892</v>
+        <v>923</v>
       </c>
       <c r="N107" t="s">
-        <v>893</v>
+        <v>924</v>
       </c>
       <c r="O107" t="s">
-        <v>894</v>
+        <v>925</v>
       </c>
       <c r="P107" t="s">
-        <v>895</v>
+        <v>926</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -10525,25 +10522,25 @@
         <v>3</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>878</v>
+        <v>910</v>
       </c>
       <c r="C108" t="s">
-        <v>617</v>
+        <v>380</v>
       </c>
       <c r="D108">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E108" t="s">
         <v>18</v>
       </c>
       <c r="F108" t="s">
-        <v>896</v>
+        <v>927</v>
       </c>
       <c r="G108" t="s">
-        <v>897</v>
+        <v>928</v>
       </c>
       <c r="H108" t="s">
-        <v>898</v>
+        <v>929</v>
       </c>
       <c r="I108" t="s">
         <v>34</v>
@@ -10555,19 +10552,19 @@
         <v>384</v>
       </c>
       <c r="L108" t="s">
-        <v>899</v>
+        <v>930</v>
       </c>
       <c r="M108" t="s">
-        <v>900</v>
+        <v>931</v>
       </c>
       <c r="N108" t="s">
-        <v>901</v>
+        <v>932</v>
       </c>
       <c r="O108" t="s">
-        <v>902</v>
+        <v>933</v>
       </c>
       <c r="P108" t="s">
-        <v>903</v>
+        <v>934</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -10575,25 +10572,25 @@
         <v>4</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>878</v>
+        <v>910</v>
       </c>
       <c r="C109" t="s">
         <v>125</v>
       </c>
       <c r="D109">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E109" t="s">
         <v>18</v>
       </c>
       <c r="F109" t="s">
-        <v>904</v>
+        <v>193</v>
       </c>
       <c r="G109" t="s">
-        <v>905</v>
+        <v>382</v>
       </c>
       <c r="H109" t="s">
-        <v>906</v>
+        <v>935</v>
       </c>
       <c r="I109" t="s">
         <v>34</v>
@@ -10605,19 +10602,19 @@
         <v>320</v>
       </c>
       <c r="L109" t="s">
-        <v>658</v>
+        <v>936</v>
       </c>
       <c r="M109" t="s">
-        <v>907</v>
+        <v>937</v>
       </c>
       <c r="N109" t="s">
-        <v>908</v>
+        <v>938</v>
       </c>
       <c r="O109" t="s">
-        <v>909</v>
+        <v>939</v>
       </c>
       <c r="P109" t="s">
-        <v>910</v>
+        <v>940</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -10625,28 +10622,28 @@
         <v>1</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>911</v>
+        <v>941</v>
       </c>
       <c r="C110" t="s">
         <v>211</v>
       </c>
       <c r="D110">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E110" t="s">
         <v>18</v>
       </c>
       <c r="F110" t="s">
-        <v>912</v>
+        <v>942</v>
       </c>
       <c r="G110" t="s">
-        <v>913</v>
+        <v>943</v>
       </c>
       <c r="H110" t="s">
-        <v>914</v>
+        <v>944</v>
       </c>
       <c r="I110" t="s">
-        <v>915</v>
+        <v>62</v>
       </c>
       <c r="J110" t="s">
         <v>23</v>
@@ -10655,19 +10652,19 @@
         <v>731</v>
       </c>
       <c r="L110" t="s">
-        <v>916</v>
+        <v>945</v>
       </c>
       <c r="M110" t="s">
-        <v>917</v>
+        <v>946</v>
       </c>
       <c r="N110" t="s">
-        <v>918</v>
+        <v>947</v>
       </c>
       <c r="O110" t="s">
         <v>62</v>
       </c>
       <c r="P110" t="s">
-        <v>919</v>
+        <v>948</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -10675,28 +10672,28 @@
         <v>2</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>911</v>
+        <v>941</v>
       </c>
       <c r="C111" t="s">
-        <v>443</v>
+        <v>221</v>
       </c>
       <c r="D111">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E111" t="s">
         <v>18</v>
       </c>
       <c r="F111" t="s">
-        <v>920</v>
+        <v>949</v>
       </c>
       <c r="G111" t="s">
-        <v>921</v>
+        <v>950</v>
       </c>
       <c r="H111" t="s">
-        <v>922</v>
+        <v>951</v>
       </c>
       <c r="I111" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J111" t="s">
         <v>23</v>
@@ -10705,19 +10702,16 @@
         <v>331</v>
       </c>
       <c r="L111" t="s">
-        <v>923</v>
+        <v>952</v>
       </c>
       <c r="M111" t="s">
-        <v>924</v>
+        <v>953</v>
       </c>
       <c r="N111" t="s">
-        <v>925</v>
+        <v>954</v>
       </c>
       <c r="O111" t="s">
-        <v>926</v>
-      </c>
-      <c r="P111" t="s">
-        <v>927</v>
+        <v>955</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -10725,28 +10719,28 @@
         <v>3</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>911</v>
+        <v>941</v>
       </c>
       <c r="C112" t="s">
-        <v>380</v>
+        <v>415</v>
       </c>
       <c r="D112">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E112" t="s">
         <v>18</v>
       </c>
       <c r="F112" t="s">
-        <v>928</v>
+        <v>956</v>
       </c>
       <c r="G112" t="s">
-        <v>929</v>
+        <v>957</v>
       </c>
       <c r="H112" t="s">
-        <v>930</v>
+        <v>958</v>
       </c>
       <c r="I112" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J112" t="s">
         <v>50</v>
@@ -10755,19 +10749,19 @@
         <v>384</v>
       </c>
       <c r="L112" t="s">
-        <v>931</v>
+        <v>959</v>
       </c>
       <c r="M112" t="s">
-        <v>932</v>
+        <v>960</v>
       </c>
       <c r="N112" t="s">
-        <v>933</v>
+        <v>961</v>
       </c>
       <c r="O112" t="s">
-        <v>934</v>
+        <v>962</v>
       </c>
       <c r="P112" t="s">
-        <v>935</v>
+        <v>963</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -10775,28 +10769,28 @@
         <v>4</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>911</v>
+        <v>941</v>
       </c>
       <c r="C113" t="s">
         <v>125</v>
       </c>
       <c r="D113">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E113" t="s">
         <v>18</v>
       </c>
       <c r="F113" t="s">
-        <v>193</v>
+        <v>964</v>
       </c>
       <c r="G113" t="s">
-        <v>382</v>
+        <v>965</v>
       </c>
       <c r="H113" t="s">
-        <v>936</v>
+        <v>966</v>
       </c>
       <c r="I113" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J113" t="s">
         <v>50</v>
@@ -10805,19 +10799,19 @@
         <v>320</v>
       </c>
       <c r="L113" t="s">
-        <v>937</v>
+        <v>967</v>
       </c>
       <c r="M113" t="s">
-        <v>938</v>
+        <v>968</v>
       </c>
       <c r="N113" t="s">
-        <v>939</v>
+        <v>969</v>
       </c>
       <c r="O113" t="s">
-        <v>940</v>
+        <v>970</v>
       </c>
       <c r="P113" t="s">
-        <v>941</v>
+        <v>971</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -10825,49 +10819,49 @@
         <v>1</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>942</v>
+        <v>972</v>
       </c>
       <c r="C114" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="D114">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="E114" t="s">
         <v>18</v>
       </c>
       <c r="F114" t="s">
-        <v>943</v>
+        <v>973</v>
       </c>
       <c r="G114" t="s">
-        <v>944</v>
+        <v>974</v>
       </c>
       <c r="H114" t="s">
-        <v>945</v>
+        <v>975</v>
       </c>
       <c r="I114" t="s">
-        <v>62</v>
+        <v>976</v>
       </c>
       <c r="J114" t="s">
         <v>23</v>
       </c>
       <c r="K114" t="s">
-        <v>731</v>
+        <v>977</v>
       </c>
       <c r="L114" t="s">
-        <v>946</v>
+        <v>978</v>
       </c>
       <c r="M114" t="s">
-        <v>947</v>
+        <v>979</v>
       </c>
       <c r="N114" t="s">
-        <v>948</v>
+        <v>980</v>
       </c>
       <c r="O114" t="s">
         <v>62</v>
       </c>
       <c r="P114" t="s">
-        <v>949</v>
+        <v>981</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -10875,46 +10869,49 @@
         <v>2</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>942</v>
+        <v>972</v>
       </c>
       <c r="C115" t="s">
-        <v>221</v>
+        <v>509</v>
       </c>
       <c r="D115">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="E115" t="s">
         <v>18</v>
       </c>
       <c r="F115" t="s">
-        <v>950</v>
+        <v>982</v>
       </c>
       <c r="G115" t="s">
-        <v>951</v>
+        <v>983</v>
       </c>
       <c r="H115" t="s">
-        <v>952</v>
+        <v>984</v>
       </c>
       <c r="I115" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="J115" t="s">
         <v>23</v>
       </c>
       <c r="K115" t="s">
-        <v>331</v>
+        <v>985</v>
       </c>
       <c r="L115" t="s">
-        <v>953</v>
+        <v>986</v>
       </c>
       <c r="M115" t="s">
-        <v>954</v>
+        <v>987</v>
       </c>
       <c r="N115" t="s">
-        <v>955</v>
+        <v>988</v>
       </c>
       <c r="O115" t="s">
-        <v>956</v>
+        <v>989</v>
+      </c>
+      <c r="P115" t="s">
+        <v>990</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -10922,49 +10919,49 @@
         <v>3</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>942</v>
+        <v>972</v>
       </c>
       <c r="C116" t="s">
-        <v>415</v>
+        <v>991</v>
       </c>
       <c r="D116">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="E116" t="s">
         <v>18</v>
       </c>
       <c r="F116" t="s">
-        <v>957</v>
+        <v>992</v>
       </c>
       <c r="G116" t="s">
-        <v>958</v>
+        <v>34</v>
       </c>
       <c r="H116" t="s">
-        <v>959</v>
+        <v>993</v>
       </c>
       <c r="I116" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="J116" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="K116" t="s">
-        <v>384</v>
+        <v>587</v>
       </c>
       <c r="L116" t="s">
-        <v>960</v>
+        <v>994</v>
       </c>
       <c r="M116" t="s">
-        <v>961</v>
+        <v>995</v>
       </c>
       <c r="N116" t="s">
-        <v>962</v>
+        <v>996</v>
       </c>
       <c r="O116" t="s">
-        <v>963</v>
+        <v>997</v>
       </c>
       <c r="P116" t="s">
-        <v>964</v>
+        <v>998</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -10972,28 +10969,28 @@
         <v>4</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>942</v>
+        <v>972</v>
       </c>
       <c r="C117" t="s">
         <v>125</v>
       </c>
       <c r="D117">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="E117" t="s">
         <v>18</v>
       </c>
       <c r="F117" t="s">
-        <v>965</v>
+        <v>999</v>
       </c>
       <c r="G117" t="s">
-        <v>966</v>
+        <v>1000</v>
       </c>
       <c r="H117" t="s">
-        <v>967</v>
+        <v>1001</v>
       </c>
       <c r="I117" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="J117" t="s">
         <v>50</v>
@@ -11002,19 +10999,19 @@
         <v>320</v>
       </c>
       <c r="L117" t="s">
-        <v>968</v>
+        <v>1002</v>
       </c>
       <c r="M117" t="s">
-        <v>969</v>
+        <v>1003</v>
       </c>
       <c r="N117" t="s">
-        <v>970</v>
+        <v>1004</v>
       </c>
       <c r="O117" t="s">
-        <v>971</v>
+        <v>1005</v>
       </c>
       <c r="P117" t="s">
-        <v>972</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -11022,49 +11019,49 @@
         <v>1</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>973</v>
+        <v>1007</v>
       </c>
       <c r="C118" t="s">
-        <v>252</v>
+        <v>174</v>
       </c>
       <c r="D118">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="E118" t="s">
         <v>18</v>
       </c>
       <c r="F118" t="s">
-        <v>974</v>
+        <v>1008</v>
       </c>
       <c r="G118" t="s">
-        <v>975</v>
+        <v>1009</v>
       </c>
       <c r="H118" t="s">
-        <v>976</v>
+        <v>1010</v>
       </c>
       <c r="I118" t="s">
-        <v>977</v>
+        <v>62</v>
       </c>
       <c r="J118" t="s">
         <v>23</v>
       </c>
       <c r="K118" t="s">
-        <v>978</v>
+        <v>1011</v>
       </c>
       <c r="L118" t="s">
-        <v>979</v>
+        <v>1012</v>
       </c>
       <c r="M118" t="s">
-        <v>980</v>
+        <v>1013</v>
       </c>
       <c r="N118" t="s">
-        <v>981</v>
+        <v>1014</v>
       </c>
       <c r="O118" t="s">
         <v>62</v>
       </c>
       <c r="P118" t="s">
-        <v>982</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -11072,25 +11069,25 @@
         <v>2</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>973</v>
+        <v>1007</v>
       </c>
       <c r="C119" t="s">
-        <v>509</v>
+        <v>1016</v>
       </c>
       <c r="D119">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="E119" t="s">
         <v>18</v>
       </c>
       <c r="F119" t="s">
-        <v>983</v>
+        <v>1017</v>
       </c>
       <c r="G119" t="s">
-        <v>984</v>
+        <v>1018</v>
       </c>
       <c r="H119" t="s">
-        <v>985</v>
+        <v>1019</v>
       </c>
       <c r="I119" t="s">
         <v>34</v>
@@ -11099,22 +11096,22 @@
         <v>23</v>
       </c>
       <c r="K119" t="s">
-        <v>986</v>
+        <v>1020</v>
       </c>
       <c r="L119" t="s">
-        <v>987</v>
+        <v>1021</v>
       </c>
       <c r="M119" t="s">
-        <v>988</v>
+        <v>1022</v>
       </c>
       <c r="N119" t="s">
-        <v>989</v>
+        <v>1023</v>
       </c>
       <c r="O119" t="s">
-        <v>990</v>
+        <v>1024</v>
       </c>
       <c r="P119" t="s">
-        <v>991</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -11122,49 +11119,49 @@
         <v>3</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>973</v>
+        <v>1007</v>
       </c>
       <c r="C120" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="D120">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="E120" t="s">
         <v>18</v>
       </c>
       <c r="F120" t="s">
-        <v>993</v>
+        <v>1027</v>
       </c>
       <c r="G120" t="s">
-        <v>34</v>
+        <v>382</v>
       </c>
       <c r="H120" t="s">
-        <v>994</v>
+        <v>1028</v>
       </c>
       <c r="I120" t="s">
         <v>34</v>
       </c>
       <c r="J120" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="K120" t="s">
-        <v>587</v>
+        <v>1029</v>
       </c>
       <c r="L120" t="s">
-        <v>995</v>
+        <v>1030</v>
       </c>
       <c r="M120" t="s">
-        <v>996</v>
+        <v>1031</v>
       </c>
       <c r="N120" t="s">
-        <v>997</v>
+        <v>131</v>
       </c>
       <c r="O120" t="s">
-        <v>998</v>
+        <v>1032</v>
       </c>
       <c r="P120" t="s">
-        <v>999</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -11172,25 +11169,25 @@
         <v>4</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>973</v>
+        <v>1007</v>
       </c>
       <c r="C121" t="s">
         <v>125</v>
       </c>
       <c r="D121">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="E121" t="s">
         <v>18</v>
       </c>
       <c r="F121" t="s">
-        <v>1000</v>
+        <v>193</v>
       </c>
       <c r="G121" t="s">
-        <v>1001</v>
+        <v>656</v>
       </c>
       <c r="H121" t="s">
-        <v>1002</v>
+        <v>1034</v>
       </c>
       <c r="I121" t="s">
         <v>34</v>
@@ -11199,22 +11196,22 @@
         <v>50</v>
       </c>
       <c r="K121" t="s">
-        <v>320</v>
+        <v>1035</v>
       </c>
       <c r="L121" t="s">
-        <v>1003</v>
+        <v>1036</v>
       </c>
       <c r="M121" t="s">
-        <v>1004</v>
+        <v>130</v>
       </c>
       <c r="N121" t="s">
-        <v>1005</v>
+        <v>1037</v>
       </c>
       <c r="O121" t="s">
-        <v>1006</v>
+        <v>1038</v>
       </c>
       <c r="P121" t="s">
-        <v>1007</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -11222,49 +11219,49 @@
         <v>1</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>1008</v>
+        <v>1040</v>
       </c>
       <c r="C122" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="D122">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E122" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F122" t="s">
-        <v>1009</v>
+        <v>1041</v>
       </c>
       <c r="G122" t="s">
-        <v>1010</v>
+        <v>1042</v>
       </c>
       <c r="H122" t="s">
-        <v>1011</v>
+        <v>1043</v>
       </c>
       <c r="I122" t="s">
-        <v>62</v>
+        <v>1044</v>
       </c>
       <c r="J122" t="s">
-        <v>23</v>
+        <v>1045</v>
       </c>
       <c r="K122" t="s">
-        <v>1012</v>
+        <v>1046</v>
       </c>
       <c r="L122" t="s">
-        <v>1013</v>
+        <v>1047</v>
       </c>
       <c r="M122" t="s">
-        <v>1014</v>
+        <v>1048</v>
       </c>
       <c r="N122" t="s">
-        <v>1015</v>
+        <v>1049</v>
       </c>
       <c r="O122" t="s">
         <v>62</v>
       </c>
       <c r="P122" t="s">
-        <v>1016</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -11272,49 +11269,49 @@
         <v>2</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>1008</v>
+        <v>1040</v>
       </c>
       <c r="C123" t="s">
-        <v>1017</v>
+        <v>1051</v>
       </c>
       <c r="D123">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E123" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F123" t="s">
-        <v>1018</v>
+        <v>1052</v>
       </c>
       <c r="G123" t="s">
-        <v>1019</v>
+        <v>1053</v>
       </c>
       <c r="H123" t="s">
-        <v>1020</v>
+        <v>1054</v>
       </c>
       <c r="I123" t="s">
         <v>34</v>
       </c>
       <c r="J123" t="s">
-        <v>23</v>
+        <v>1045</v>
       </c>
       <c r="K123" t="s">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="L123" t="s">
-        <v>1022</v>
+        <v>1056</v>
       </c>
       <c r="M123" t="s">
-        <v>1023</v>
+        <v>1057</v>
       </c>
       <c r="N123" t="s">
-        <v>1024</v>
+        <v>1058</v>
       </c>
       <c r="O123" t="s">
-        <v>1025</v>
+        <v>62</v>
       </c>
       <c r="P123" t="s">
-        <v>1026</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -11322,49 +11319,49 @@
         <v>3</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>1008</v>
+        <v>1040</v>
       </c>
       <c r="C124" t="s">
-        <v>1027</v>
+        <v>1060</v>
       </c>
       <c r="D124">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E124" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F124" t="s">
-        <v>1028</v>
+        <v>1061</v>
       </c>
       <c r="G124" t="s">
-        <v>382</v>
+        <v>1062</v>
       </c>
       <c r="H124" t="s">
-        <v>1029</v>
+        <v>1063</v>
       </c>
       <c r="I124" t="s">
         <v>34</v>
       </c>
       <c r="J124" t="s">
-        <v>50</v>
+        <v>158</v>
       </c>
       <c r="K124" t="s">
-        <v>1030</v>
+        <v>1064</v>
       </c>
       <c r="L124" t="s">
-        <v>1031</v>
+        <v>1065</v>
       </c>
       <c r="M124" t="s">
-        <v>1032</v>
+        <v>1066</v>
       </c>
       <c r="N124" t="s">
-        <v>131</v>
+        <v>1067</v>
       </c>
       <c r="O124" t="s">
-        <v>1033</v>
+        <v>1068</v>
       </c>
       <c r="P124" t="s">
-        <v>1034</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -11372,25 +11369,25 @@
         <v>4</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>1008</v>
+        <v>1040</v>
       </c>
       <c r="C125" t="s">
-        <v>125</v>
+        <v>1070</v>
       </c>
       <c r="D125">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E125" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F125" t="s">
-        <v>193</v>
+        <v>1071</v>
       </c>
       <c r="G125" t="s">
-        <v>656</v>
+        <v>382</v>
       </c>
       <c r="H125" t="s">
-        <v>1035</v>
+        <v>1072</v>
       </c>
       <c r="I125" t="s">
         <v>34</v>
@@ -11399,22 +11396,22 @@
         <v>50</v>
       </c>
       <c r="K125" t="s">
-        <v>1036</v>
+        <v>1073</v>
       </c>
       <c r="L125" t="s">
-        <v>1037</v>
+        <v>1074</v>
       </c>
       <c r="M125" t="s">
-        <v>130</v>
+        <v>1075</v>
       </c>
       <c r="N125" t="s">
+        <v>1076</v>
+      </c>
+      <c r="O125" t="s">
         <v>1038</v>
       </c>
-      <c r="O125" t="s">
-        <v>1039</v>
-      </c>
       <c r="P125" t="s">
-        <v>1040</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -11422,49 +11419,49 @@
         <v>1</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>1041</v>
+        <v>1078</v>
       </c>
       <c r="C126" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D126">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E126" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F126" t="s">
-        <v>1042</v>
+        <v>1079</v>
       </c>
       <c r="G126" t="s">
-        <v>1043</v>
+        <v>1080</v>
       </c>
       <c r="H126" t="s">
-        <v>1044</v>
+        <v>1081</v>
       </c>
       <c r="I126" t="s">
-        <v>1045</v>
+        <v>820</v>
       </c>
       <c r="J126" t="s">
-        <v>1046</v>
+        <v>792</v>
       </c>
       <c r="K126" t="s">
-        <v>1047</v>
+        <v>1082</v>
       </c>
       <c r="L126" t="s">
-        <v>1048</v>
+        <v>1083</v>
       </c>
       <c r="M126" t="s">
-        <v>1049</v>
+        <v>1084</v>
       </c>
       <c r="N126" t="s">
-        <v>1050</v>
+        <v>1085</v>
       </c>
       <c r="O126" t="s">
         <v>62</v>
       </c>
       <c r="P126" t="s">
-        <v>1051</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -11472,49 +11469,49 @@
         <v>2</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>1041</v>
+        <v>1078</v>
       </c>
       <c r="C127" t="s">
-        <v>1052</v>
+        <v>509</v>
       </c>
       <c r="D127">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E127" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F127" t="s">
-        <v>1053</v>
+        <v>1087</v>
       </c>
       <c r="G127" t="s">
-        <v>1054</v>
+        <v>1088</v>
       </c>
       <c r="H127" t="s">
-        <v>1055</v>
+        <v>1089</v>
       </c>
       <c r="I127" t="s">
         <v>34</v>
       </c>
       <c r="J127" t="s">
-        <v>1046</v>
+        <v>1090</v>
       </c>
       <c r="K127" t="s">
-        <v>1056</v>
+        <v>1091</v>
       </c>
       <c r="L127" t="s">
-        <v>1057</v>
+        <v>1092</v>
       </c>
       <c r="M127" t="s">
-        <v>1058</v>
+        <v>1093</v>
       </c>
       <c r="N127" t="s">
-        <v>1059</v>
+        <v>1094</v>
       </c>
       <c r="O127" t="s">
         <v>62</v>
       </c>
       <c r="P127" t="s">
-        <v>1060</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -11522,49 +11519,49 @@
         <v>3</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>1041</v>
+        <v>1078</v>
       </c>
       <c r="C128" t="s">
-        <v>1061</v>
+        <v>1096</v>
       </c>
       <c r="D128">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E128" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F128" t="s">
-        <v>1062</v>
+        <v>1097</v>
       </c>
       <c r="G128" t="s">
-        <v>1063</v>
+        <v>1098</v>
       </c>
       <c r="H128" t="s">
-        <v>1064</v>
+        <v>1099</v>
       </c>
       <c r="I128" t="s">
         <v>34</v>
       </c>
       <c r="J128" t="s">
-        <v>158</v>
+        <v>1090</v>
       </c>
       <c r="K128" t="s">
-        <v>1065</v>
+        <v>1100</v>
       </c>
       <c r="L128" t="s">
-        <v>1066</v>
+        <v>1101</v>
       </c>
       <c r="M128" t="s">
-        <v>1067</v>
+        <v>1102</v>
       </c>
       <c r="N128" t="s">
-        <v>1068</v>
+        <v>1103</v>
       </c>
       <c r="O128" t="s">
-        <v>1069</v>
+        <v>62</v>
       </c>
       <c r="P128" t="s">
-        <v>1070</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -11572,25 +11569,25 @@
         <v>4</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>1041</v>
+        <v>1078</v>
       </c>
       <c r="C129" t="s">
-        <v>1071</v>
+        <v>1105</v>
       </c>
       <c r="D129">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E129" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F129" t="s">
-        <v>1072</v>
+        <v>1106</v>
       </c>
       <c r="G129" t="s">
         <v>382</v>
       </c>
       <c r="H129" t="s">
-        <v>1073</v>
+        <v>1107</v>
       </c>
       <c r="I129" t="s">
         <v>34</v>
@@ -11599,22 +11596,22 @@
         <v>50</v>
       </c>
       <c r="K129" t="s">
-        <v>1074</v>
+        <v>358</v>
       </c>
       <c r="L129" t="s">
-        <v>1075</v>
+        <v>1108</v>
       </c>
       <c r="M129" t="s">
-        <v>1076</v>
+        <v>1109</v>
       </c>
       <c r="N129" t="s">
-        <v>1077</v>
+        <v>1110</v>
       </c>
       <c r="O129" t="s">
-        <v>1039</v>
+        <v>1111</v>
       </c>
       <c r="P129" t="s">
-        <v>1078</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -11622,49 +11619,49 @@
         <v>1</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>1079</v>
+        <v>1113</v>
       </c>
       <c r="C130" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="D130">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="E130" t="s">
         <v>18</v>
       </c>
       <c r="F130" t="s">
-        <v>1080</v>
+        <v>1114</v>
       </c>
       <c r="G130" t="s">
-        <v>1081</v>
+        <v>1115</v>
       </c>
       <c r="H130" t="s">
-        <v>1082</v>
+        <v>1116</v>
       </c>
       <c r="I130" t="s">
-        <v>821</v>
+        <v>62</v>
       </c>
       <c r="J130" t="s">
-        <v>793</v>
+        <v>1045</v>
       </c>
       <c r="K130" t="s">
-        <v>1083</v>
+        <v>534</v>
       </c>
       <c r="L130" t="s">
-        <v>1084</v>
+        <v>1117</v>
       </c>
       <c r="M130" t="s">
-        <v>1085</v>
+        <v>1118</v>
       </c>
       <c r="N130" t="s">
-        <v>1086</v>
+        <v>1119</v>
       </c>
       <c r="O130" t="s">
         <v>62</v>
       </c>
       <c r="P130" t="s">
-        <v>1087</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -11672,49 +11669,49 @@
         <v>2</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1079</v>
+        <v>1113</v>
       </c>
       <c r="C131" t="s">
-        <v>509</v>
+        <v>1121</v>
       </c>
       <c r="D131">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="E131" t="s">
         <v>18</v>
       </c>
       <c r="F131" t="s">
-        <v>1088</v>
+        <v>1122</v>
       </c>
       <c r="G131" t="s">
-        <v>1089</v>
+        <v>1123</v>
       </c>
       <c r="H131" t="s">
-        <v>1090</v>
+        <v>1124</v>
       </c>
       <c r="I131" t="s">
         <v>34</v>
       </c>
       <c r="J131" t="s">
-        <v>1091</v>
+        <v>1045</v>
       </c>
       <c r="K131" t="s">
-        <v>1092</v>
+        <v>1125</v>
       </c>
       <c r="L131" t="s">
-        <v>1093</v>
+        <v>1126</v>
       </c>
       <c r="M131" t="s">
-        <v>1094</v>
+        <v>1127</v>
       </c>
       <c r="N131" t="s">
-        <v>1095</v>
+        <v>1119</v>
       </c>
       <c r="O131" t="s">
-        <v>62</v>
+        <v>1128</v>
       </c>
       <c r="P131" t="s">
-        <v>1096</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -11722,49 +11719,49 @@
         <v>3</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>1079</v>
+        <v>1113</v>
       </c>
       <c r="C132" t="s">
-        <v>1097</v>
+        <v>415</v>
       </c>
       <c r="D132">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="E132" t="s">
         <v>18</v>
       </c>
       <c r="F132" t="s">
-        <v>1098</v>
+        <v>1130</v>
       </c>
       <c r="G132" t="s">
-        <v>1099</v>
+        <v>382</v>
       </c>
       <c r="H132" t="s">
-        <v>1100</v>
+        <v>1131</v>
       </c>
       <c r="I132" t="s">
         <v>34</v>
       </c>
       <c r="J132" t="s">
-        <v>1091</v>
+        <v>50</v>
       </c>
       <c r="K132" t="s">
-        <v>1101</v>
+        <v>358</v>
       </c>
       <c r="L132" t="s">
-        <v>1102</v>
+        <v>686</v>
       </c>
       <c r="M132" t="s">
-        <v>1103</v>
+        <v>1132</v>
       </c>
       <c r="N132" t="s">
-        <v>1104</v>
+        <v>1133</v>
       </c>
       <c r="O132" t="s">
-        <v>62</v>
+        <v>1134</v>
       </c>
       <c r="P132" t="s">
-        <v>1105</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -11772,25 +11769,25 @@
         <v>4</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>1079</v>
+        <v>1113</v>
       </c>
       <c r="C133" t="s">
-        <v>1106</v>
+        <v>125</v>
       </c>
       <c r="D133">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="E133" t="s">
         <v>18</v>
       </c>
       <c r="F133" t="s">
-        <v>1107</v>
+        <v>193</v>
       </c>
       <c r="G133" t="s">
-        <v>382</v>
+        <v>656</v>
       </c>
       <c r="H133" t="s">
-        <v>1108</v>
+        <v>1136</v>
       </c>
       <c r="I133" t="s">
         <v>34</v>
@@ -11799,22 +11796,22 @@
         <v>50</v>
       </c>
       <c r="K133" t="s">
-        <v>358</v>
+        <v>91</v>
       </c>
       <c r="L133" t="s">
-        <v>1109</v>
+        <v>785</v>
       </c>
       <c r="M133" t="s">
-        <v>1110</v>
+        <v>1137</v>
       </c>
       <c r="N133" t="s">
-        <v>1111</v>
+        <v>1133</v>
       </c>
       <c r="O133" t="s">
-        <v>1112</v>
+        <v>1038</v>
       </c>
       <c r="P133" t="s">
-        <v>1113</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -11822,49 +11819,49 @@
         <v>1</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
       <c r="C134" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D134">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E134" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F134" t="s">
-        <v>1115</v>
+        <v>1140</v>
       </c>
       <c r="G134" t="s">
-        <v>1116</v>
+        <v>1141</v>
       </c>
       <c r="H134" t="s">
-        <v>1117</v>
+        <v>1142</v>
       </c>
       <c r="I134" t="s">
         <v>62</v>
       </c>
       <c r="J134" t="s">
-        <v>1046</v>
+        <v>791</v>
       </c>
       <c r="K134" t="s">
-        <v>534</v>
+        <v>1143</v>
       </c>
       <c r="L134" t="s">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="M134" t="s">
-        <v>1119</v>
+        <v>1145</v>
       </c>
       <c r="N134" t="s">
-        <v>1120</v>
+        <v>1146</v>
       </c>
       <c r="O134" t="s">
         <v>62</v>
       </c>
       <c r="P134" t="s">
-        <v>1121</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -11872,49 +11869,49 @@
         <v>2</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
       <c r="C135" t="s">
-        <v>1122</v>
+        <v>509</v>
       </c>
       <c r="D135">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E135" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F135" t="s">
-        <v>1123</v>
+        <v>1087</v>
       </c>
       <c r="G135" t="s">
-        <v>1124</v>
+        <v>1148</v>
       </c>
       <c r="H135" t="s">
-        <v>1125</v>
+        <v>1149</v>
       </c>
       <c r="I135" t="s">
         <v>34</v>
       </c>
       <c r="J135" t="s">
-        <v>1046</v>
+        <v>791</v>
       </c>
       <c r="K135" t="s">
-        <v>1126</v>
+        <v>1150</v>
       </c>
       <c r="L135" t="s">
-        <v>1127</v>
+        <v>1151</v>
       </c>
       <c r="M135" t="s">
-        <v>1128</v>
+        <v>1152</v>
       </c>
       <c r="N135" t="s">
-        <v>1120</v>
+        <v>1153</v>
       </c>
       <c r="O135" t="s">
-        <v>1129</v>
+        <v>62</v>
       </c>
       <c r="P135" t="s">
-        <v>1130</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -11922,49 +11919,49 @@
         <v>3</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
       <c r="C136" t="s">
-        <v>415</v>
+        <v>1155</v>
       </c>
       <c r="D136">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E136" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F136" t="s">
-        <v>1131</v>
+        <v>1156</v>
       </c>
       <c r="G136" t="s">
-        <v>382</v>
+        <v>1157</v>
       </c>
       <c r="H136" t="s">
-        <v>1132</v>
+        <v>1158</v>
       </c>
       <c r="I136" t="s">
         <v>34</v>
       </c>
       <c r="J136" t="s">
-        <v>50</v>
+        <v>791</v>
       </c>
       <c r="K136" t="s">
-        <v>358</v>
+        <v>1159</v>
       </c>
       <c r="L136" t="s">
-        <v>686</v>
+        <v>1160</v>
       </c>
       <c r="M136" t="s">
-        <v>1133</v>
+        <v>1161</v>
       </c>
       <c r="N136" t="s">
-        <v>1134</v>
+        <v>1162</v>
       </c>
       <c r="O136" t="s">
-        <v>1135</v>
+        <v>1163</v>
       </c>
       <c r="P136" t="s">
-        <v>1136</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -11972,49 +11969,49 @@
         <v>4</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>1114</v>
+        <v>1139</v>
       </c>
       <c r="C137" t="s">
-        <v>125</v>
+        <v>1165</v>
       </c>
       <c r="D137">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E137" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F137" t="s">
-        <v>193</v>
+        <v>1166</v>
       </c>
       <c r="G137" t="s">
-        <v>656</v>
+        <v>1167</v>
       </c>
       <c r="H137" t="s">
-        <v>1137</v>
+        <v>1168</v>
       </c>
       <c r="I137" t="s">
         <v>34</v>
       </c>
       <c r="J137" t="s">
-        <v>50</v>
+        <v>791</v>
       </c>
       <c r="K137" t="s">
-        <v>91</v>
+        <v>1169</v>
       </c>
       <c r="L137" t="s">
-        <v>786</v>
+        <v>1170</v>
       </c>
       <c r="M137" t="s">
-        <v>1138</v>
+        <v>1171</v>
       </c>
       <c r="N137" t="s">
-        <v>1134</v>
+        <v>1172</v>
       </c>
       <c r="O137" t="s">
-        <v>1039</v>
+        <v>625</v>
       </c>
       <c r="P137" t="s">
-        <v>1139</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -12022,49 +12019,49 @@
         <v>1</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>1140</v>
+        <v>1174</v>
       </c>
       <c r="C138" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="D138">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E138" t="s">
         <v>58</v>
       </c>
       <c r="F138" t="s">
-        <v>1141</v>
+        <v>1175</v>
       </c>
       <c r="G138" t="s">
-        <v>1142</v>
+        <v>1176</v>
       </c>
       <c r="H138" t="s">
-        <v>1143</v>
+        <v>1177</v>
       </c>
       <c r="I138" t="s">
         <v>62</v>
       </c>
       <c r="J138" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="K138" t="s">
-        <v>1144</v>
+        <v>1178</v>
       </c>
       <c r="L138" t="s">
-        <v>1145</v>
+        <v>1179</v>
       </c>
       <c r="M138" t="s">
-        <v>1146</v>
+        <v>1180</v>
       </c>
       <c r="N138" t="s">
-        <v>1147</v>
+        <v>1181</v>
       </c>
       <c r="O138" t="s">
         <v>62</v>
       </c>
       <c r="P138" t="s">
-        <v>1148</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -12072,49 +12069,49 @@
         <v>2</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1140</v>
+        <v>1174</v>
       </c>
       <c r="C139" t="s">
-        <v>509</v>
+        <v>443</v>
       </c>
       <c r="D139">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E139" t="s">
         <v>58</v>
       </c>
       <c r="F139" t="s">
-        <v>1088</v>
+        <v>1183</v>
       </c>
       <c r="G139" t="s">
-        <v>1149</v>
+        <v>1184</v>
       </c>
       <c r="H139" t="s">
-        <v>1150</v>
+        <v>1185</v>
       </c>
       <c r="I139" t="s">
         <v>34</v>
       </c>
       <c r="J139" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="K139" t="s">
-        <v>1151</v>
+        <v>23</v>
       </c>
       <c r="L139" t="s">
-        <v>1152</v>
+        <v>1186</v>
       </c>
       <c r="M139" t="s">
-        <v>1153</v>
+        <v>1187</v>
       </c>
       <c r="N139" t="s">
-        <v>1154</v>
+        <v>1181</v>
       </c>
       <c r="O139" t="s">
-        <v>62</v>
+        <v>1188</v>
       </c>
       <c r="P139" t="s">
-        <v>1155</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -12122,49 +12119,49 @@
         <v>3</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>1140</v>
+        <v>1174</v>
       </c>
       <c r="C140" t="s">
-        <v>1156</v>
+        <v>1190</v>
       </c>
       <c r="D140">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E140" t="s">
         <v>58</v>
       </c>
       <c r="F140" t="s">
-        <v>1157</v>
+        <v>1191</v>
       </c>
       <c r="G140" t="s">
-        <v>1158</v>
+        <v>1192</v>
       </c>
       <c r="H140" t="s">
-        <v>1159</v>
+        <v>1193</v>
       </c>
       <c r="I140" t="s">
         <v>34</v>
       </c>
       <c r="J140" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="K140" t="s">
-        <v>1160</v>
+        <v>409</v>
       </c>
       <c r="L140" t="s">
-        <v>1161</v>
+        <v>1194</v>
       </c>
       <c r="M140" t="s">
-        <v>1162</v>
+        <v>1195</v>
       </c>
       <c r="N140" t="s">
-        <v>1163</v>
+        <v>1196</v>
       </c>
       <c r="O140" t="s">
-        <v>1164</v>
+        <v>1197</v>
       </c>
       <c r="P140" t="s">
-        <v>1165</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -12172,49 +12169,49 @@
         <v>4</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>1140</v>
+        <v>1174</v>
       </c>
       <c r="C141" t="s">
-        <v>1166</v>
+        <v>1070</v>
       </c>
       <c r="D141">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E141" t="s">
         <v>58</v>
       </c>
       <c r="F141" t="s">
-        <v>1167</v>
+        <v>193</v>
       </c>
       <c r="G141" t="s">
-        <v>1168</v>
+        <v>382</v>
       </c>
       <c r="H141" t="s">
-        <v>1169</v>
+        <v>1199</v>
       </c>
       <c r="I141" t="s">
         <v>34</v>
       </c>
       <c r="J141" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="K141" t="s">
-        <v>1170</v>
+        <v>91</v>
       </c>
       <c r="L141" t="s">
-        <v>1171</v>
+        <v>1200</v>
       </c>
       <c r="M141" t="s">
-        <v>1172</v>
+        <v>1201</v>
       </c>
       <c r="N141" t="s">
-        <v>1173</v>
+        <v>1133</v>
       </c>
       <c r="O141" t="s">
-        <v>625</v>
+        <v>1202</v>
       </c>
       <c r="P141" t="s">
-        <v>1174</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -12222,49 +12219,49 @@
         <v>1</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>1175</v>
+        <v>1204</v>
       </c>
       <c r="C142" t="s">
         <v>211</v>
       </c>
       <c r="D142">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E142" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F142" t="s">
-        <v>1176</v>
+        <v>1205</v>
       </c>
       <c r="G142" t="s">
-        <v>1177</v>
+        <v>1206</v>
       </c>
       <c r="H142" t="s">
-        <v>1178</v>
+        <v>1207</v>
       </c>
       <c r="I142" t="s">
         <v>62</v>
       </c>
       <c r="J142" t="s">
-        <v>813</v>
+        <v>1208</v>
       </c>
       <c r="K142" t="s">
-        <v>1179</v>
+        <v>1209</v>
       </c>
       <c r="L142" t="s">
-        <v>1180</v>
+        <v>1210</v>
       </c>
       <c r="M142" t="s">
-        <v>1181</v>
+        <v>1211</v>
       </c>
       <c r="N142" t="s">
-        <v>1182</v>
+        <v>1212</v>
       </c>
       <c r="O142" t="s">
         <v>62</v>
       </c>
       <c r="P142" t="s">
-        <v>1183</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -12272,49 +12269,46 @@
         <v>2</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>1175</v>
+        <v>1204</v>
       </c>
       <c r="C143" t="s">
-        <v>443</v>
+        <v>221</v>
       </c>
       <c r="D143">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E143" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F143" t="s">
-        <v>1184</v>
+        <v>1214</v>
       </c>
       <c r="G143" t="s">
-        <v>1185</v>
+        <v>1215</v>
       </c>
       <c r="H143" t="s">
-        <v>1186</v>
+        <v>1216</v>
       </c>
       <c r="I143" t="s">
         <v>34</v>
       </c>
       <c r="J143" t="s">
-        <v>813</v>
+        <v>1208</v>
       </c>
       <c r="K143" t="s">
-        <v>23</v>
+        <v>452</v>
       </c>
       <c r="L143" t="s">
-        <v>1187</v>
+        <v>1217</v>
       </c>
       <c r="M143" t="s">
-        <v>1188</v>
+        <v>1218</v>
       </c>
       <c r="N143" t="s">
-        <v>1182</v>
+        <v>1219</v>
       </c>
       <c r="O143" t="s">
-        <v>1189</v>
-      </c>
-      <c r="P143" t="s">
-        <v>1190</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -12322,49 +12316,46 @@
         <v>3</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>1175</v>
+        <v>1204</v>
       </c>
       <c r="C144" t="s">
-        <v>1191</v>
+        <v>1060</v>
       </c>
       <c r="D144">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E144" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F144" t="s">
-        <v>1192</v>
+        <v>1221</v>
       </c>
       <c r="G144" t="s">
-        <v>1193</v>
+        <v>1222</v>
       </c>
       <c r="H144" t="s">
-        <v>1194</v>
+        <v>1223</v>
       </c>
       <c r="I144" t="s">
         <v>34</v>
       </c>
       <c r="J144" t="s">
-        <v>813</v>
+        <v>1208</v>
       </c>
       <c r="K144" t="s">
-        <v>409</v>
+        <v>1224</v>
       </c>
       <c r="L144" t="s">
-        <v>1195</v>
+        <v>1225</v>
       </c>
       <c r="M144" t="s">
-        <v>1196</v>
+        <v>1226</v>
       </c>
       <c r="N144" t="s">
-        <v>1197</v>
+        <v>1227</v>
       </c>
       <c r="O144" t="s">
-        <v>1198</v>
-      </c>
-      <c r="P144" t="s">
-        <v>1199</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -12372,49 +12363,46 @@
         <v>4</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>1175</v>
+        <v>1204</v>
       </c>
       <c r="C145" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="D145">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E145" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F145" t="s">
-        <v>193</v>
+        <v>1229</v>
       </c>
       <c r="G145" t="s">
-        <v>382</v>
+        <v>1230</v>
       </c>
       <c r="H145" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="I145" t="s">
         <v>34</v>
       </c>
       <c r="J145" t="s">
-        <v>813</v>
+        <v>1208</v>
       </c>
       <c r="K145" t="s">
-        <v>91</v>
+        <v>1232</v>
       </c>
       <c r="L145" t="s">
-        <v>1201</v>
+        <v>1233</v>
       </c>
       <c r="M145" t="s">
-        <v>1202</v>
+        <v>1234</v>
       </c>
       <c r="N145" t="s">
-        <v>1134</v>
+        <v>1038</v>
       </c>
       <c r="O145" t="s">
-        <v>1203</v>
-      </c>
-      <c r="P145" t="s">
-        <v>1204</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -12422,49 +12410,49 @@
         <v>1</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1205</v>
+        <v>1236</v>
       </c>
       <c r="C146" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D146">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="E146" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F146" t="s">
-        <v>1206</v>
+        <v>1237</v>
       </c>
       <c r="G146" t="s">
-        <v>1207</v>
+        <v>1238</v>
       </c>
       <c r="H146" t="s">
-        <v>1208</v>
+        <v>1239</v>
       </c>
       <c r="I146" t="s">
-        <v>62</v>
+        <v>1240</v>
       </c>
       <c r="J146" t="s">
-        <v>1209</v>
+        <v>358</v>
       </c>
       <c r="K146" t="s">
-        <v>1210</v>
+        <v>1241</v>
       </c>
       <c r="L146" t="s">
-        <v>1211</v>
+        <v>1242</v>
       </c>
       <c r="M146" t="s">
-        <v>1212</v>
+        <v>1243</v>
       </c>
       <c r="N146" t="s">
-        <v>1213</v>
+        <v>1244</v>
       </c>
       <c r="O146" t="s">
         <v>62</v>
       </c>
       <c r="P146" t="s">
-        <v>1214</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -12472,46 +12460,46 @@
         <v>2</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>1205</v>
+        <v>1236</v>
       </c>
       <c r="C147" t="s">
-        <v>221</v>
+        <v>1246</v>
       </c>
       <c r="D147">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="E147" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F147" t="s">
-        <v>1215</v>
+        <v>1247</v>
       </c>
       <c r="G147" t="s">
-        <v>1216</v>
+        <v>34</v>
       </c>
       <c r="H147" t="s">
-        <v>1217</v>
+        <v>1248</v>
       </c>
       <c r="I147" t="s">
         <v>34</v>
       </c>
       <c r="J147" t="s">
-        <v>1209</v>
+        <v>358</v>
       </c>
       <c r="K147" t="s">
-        <v>452</v>
+        <v>1249</v>
       </c>
       <c r="L147" t="s">
-        <v>1218</v>
+        <v>1250</v>
       </c>
       <c r="M147" t="s">
-        <v>1219</v>
+        <v>1244</v>
       </c>
       <c r="N147" t="s">
-        <v>1220</v>
+        <v>1251</v>
       </c>
       <c r="O147" t="s">
-        <v>1221</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -12519,46 +12507,46 @@
         <v>3</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1205</v>
+        <v>1236</v>
       </c>
       <c r="C148" t="s">
-        <v>1061</v>
+        <v>296</v>
       </c>
       <c r="D148">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="E148" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F148" t="s">
-        <v>1222</v>
+        <v>1253</v>
       </c>
       <c r="G148" t="s">
-        <v>1223</v>
+        <v>1254</v>
       </c>
       <c r="H148" t="s">
-        <v>1224</v>
+        <v>1255</v>
       </c>
       <c r="I148" t="s">
         <v>34</v>
       </c>
       <c r="J148" t="s">
-        <v>1209</v>
+        <v>358</v>
       </c>
       <c r="K148" t="s">
-        <v>1225</v>
+        <v>1256</v>
       </c>
       <c r="L148" t="s">
-        <v>1226</v>
+        <v>1257</v>
       </c>
       <c r="M148" t="s">
-        <v>1227</v>
+        <v>1258</v>
       </c>
       <c r="N148" t="s">
-        <v>1228</v>
+        <v>1259</v>
       </c>
       <c r="O148" t="s">
-        <v>1229</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -12566,46 +12554,46 @@
         <v>4</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>1205</v>
+        <v>1236</v>
       </c>
       <c r="C149" t="s">
-        <v>1071</v>
+        <v>1096</v>
       </c>
       <c r="D149">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="E149" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F149" t="s">
-        <v>1230</v>
+        <v>1261</v>
       </c>
       <c r="G149" t="s">
-        <v>1231</v>
+        <v>1262</v>
       </c>
       <c r="H149" t="s">
-        <v>1232</v>
+        <v>1263</v>
       </c>
       <c r="I149" t="s">
         <v>34</v>
       </c>
       <c r="J149" t="s">
-        <v>1209</v>
+        <v>358</v>
       </c>
       <c r="K149" t="s">
-        <v>1233</v>
+        <v>1264</v>
       </c>
       <c r="L149" t="s">
-        <v>1234</v>
+        <v>1265</v>
       </c>
       <c r="M149" t="s">
-        <v>1235</v>
+        <v>1266</v>
       </c>
       <c r="N149" t="s">
-        <v>1039</v>
+        <v>1267</v>
       </c>
       <c r="O149" t="s">
-        <v>1236</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -12613,49 +12601,49 @@
         <v>1</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1237</v>
+        <v>1269</v>
       </c>
       <c r="C150" t="s">
         <v>174</v>
       </c>
       <c r="D150">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="E150" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F150" t="s">
-        <v>1238</v>
+        <v>1270</v>
       </c>
       <c r="G150" t="s">
-        <v>1239</v>
+        <v>1271</v>
       </c>
       <c r="H150" t="s">
-        <v>1240</v>
+        <v>1272</v>
       </c>
       <c r="I150" t="s">
-        <v>1241</v>
+        <v>62</v>
       </c>
       <c r="J150" t="s">
-        <v>358</v>
+        <v>791</v>
       </c>
       <c r="K150" t="s">
-        <v>1242</v>
+        <v>1273</v>
       </c>
       <c r="L150" t="s">
-        <v>1243</v>
+        <v>1274</v>
       </c>
       <c r="M150" t="s">
-        <v>1244</v>
+        <v>1275</v>
       </c>
       <c r="N150" t="s">
-        <v>1245</v>
+        <v>1276</v>
       </c>
       <c r="O150" t="s">
         <v>62</v>
       </c>
       <c r="P150" t="s">
-        <v>1246</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -12663,46 +12651,46 @@
         <v>2</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>1237</v>
+        <v>1269</v>
       </c>
       <c r="C151" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="D151">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="E151" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F151" t="s">
-        <v>1248</v>
+        <v>1278</v>
       </c>
       <c r="G151" t="s">
-        <v>34</v>
+        <v>1279</v>
       </c>
       <c r="H151" t="s">
-        <v>1249</v>
+        <v>1280</v>
       </c>
       <c r="I151" t="s">
         <v>34</v>
       </c>
       <c r="J151" t="s">
-        <v>358</v>
+        <v>791</v>
       </c>
       <c r="K151" t="s">
-        <v>1250</v>
+        <v>1281</v>
       </c>
       <c r="L151" t="s">
-        <v>1251</v>
+        <v>1282</v>
       </c>
       <c r="M151" t="s">
-        <v>1245</v>
+        <v>1276</v>
       </c>
       <c r="N151" t="s">
-        <v>1252</v>
+        <v>1283</v>
       </c>
       <c r="O151" t="s">
-        <v>1253</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -12710,46 +12698,46 @@
         <v>3</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1237</v>
+        <v>1269</v>
       </c>
       <c r="C152" t="s">
-        <v>296</v>
+        <v>1285</v>
       </c>
       <c r="D152">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="E152" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F152" t="s">
-        <v>1254</v>
+        <v>1286</v>
       </c>
       <c r="G152" t="s">
-        <v>1255</v>
+        <v>1287</v>
       </c>
       <c r="H152" t="s">
-        <v>1256</v>
+        <v>1288</v>
       </c>
       <c r="I152" t="s">
         <v>34</v>
       </c>
       <c r="J152" t="s">
-        <v>358</v>
+        <v>791</v>
       </c>
       <c r="K152" t="s">
-        <v>1257</v>
+        <v>1289</v>
       </c>
       <c r="L152" t="s">
-        <v>1258</v>
+        <v>1290</v>
       </c>
       <c r="M152" t="s">
-        <v>1259</v>
+        <v>1291</v>
       </c>
       <c r="N152" t="s">
-        <v>1260</v>
+        <v>1219</v>
       </c>
       <c r="O152" t="s">
-        <v>1261</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -12757,46 +12745,46 @@
         <v>4</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>1237</v>
+        <v>1269</v>
       </c>
       <c r="C153" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D153">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="E153" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F153" t="s">
-        <v>1262</v>
+        <v>1293</v>
       </c>
       <c r="G153" t="s">
-        <v>1263</v>
+        <v>1294</v>
       </c>
       <c r="H153" t="s">
-        <v>1264</v>
+        <v>1295</v>
       </c>
       <c r="I153" t="s">
         <v>34</v>
       </c>
       <c r="J153" t="s">
-        <v>358</v>
+        <v>791</v>
       </c>
       <c r="K153" t="s">
-        <v>1265</v>
+        <v>1296</v>
       </c>
       <c r="L153" t="s">
-        <v>1266</v>
+        <v>1297</v>
       </c>
       <c r="M153" t="s">
+        <v>1298</v>
+      </c>
+      <c r="N153" t="s">
         <v>1267</v>
       </c>
-      <c r="N153" t="s">
-        <v>1268</v>
-      </c>
       <c r="O153" t="s">
-        <v>1269</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -12804,49 +12792,49 @@
         <v>1</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1270</v>
+        <v>1300</v>
       </c>
       <c r="C154" t="s">
         <v>174</v>
       </c>
       <c r="D154">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E154" t="s">
         <v>18</v>
       </c>
       <c r="F154" t="s">
-        <v>1271</v>
+        <v>1301</v>
       </c>
       <c r="G154" t="s">
-        <v>1272</v>
+        <v>1302</v>
       </c>
       <c r="H154" t="s">
-        <v>1273</v>
+        <v>1303</v>
       </c>
       <c r="I154" t="s">
-        <v>62</v>
+        <v>1240</v>
       </c>
       <c r="J154" t="s">
-        <v>792</v>
+        <v>1045</v>
       </c>
       <c r="K154" t="s">
-        <v>1274</v>
+        <v>1304</v>
       </c>
       <c r="L154" t="s">
-        <v>1275</v>
+        <v>1305</v>
       </c>
       <c r="M154" t="s">
-        <v>1276</v>
+        <v>1306</v>
       </c>
       <c r="N154" t="s">
-        <v>1277</v>
+        <v>1307</v>
       </c>
       <c r="O154" t="s">
-        <v>62</v>
+        <v>1308</v>
       </c>
       <c r="P154" t="s">
-        <v>1278</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -12854,46 +12842,46 @@
         <v>2</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>1270</v>
+        <v>1300</v>
       </c>
       <c r="C155" t="s">
-        <v>1247</v>
+        <v>509</v>
       </c>
       <c r="D155">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E155" t="s">
         <v>18</v>
       </c>
       <c r="F155" t="s">
-        <v>1279</v>
+        <v>1310</v>
       </c>
       <c r="G155" t="s">
-        <v>1280</v>
+        <v>34</v>
       </c>
       <c r="H155" t="s">
-        <v>1281</v>
+        <v>1311</v>
       </c>
       <c r="I155" t="s">
         <v>34</v>
       </c>
       <c r="J155" t="s">
-        <v>792</v>
+        <v>1045</v>
       </c>
       <c r="K155" t="s">
-        <v>1282</v>
+        <v>1312</v>
       </c>
       <c r="L155" t="s">
-        <v>1283</v>
+        <v>1313</v>
       </c>
       <c r="M155" t="s">
-        <v>1277</v>
+        <v>1307</v>
       </c>
       <c r="N155" t="s">
-        <v>1284</v>
+        <v>1314</v>
       </c>
       <c r="O155" t="s">
-        <v>1285</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -12901,46 +12889,46 @@
         <v>3</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1270</v>
+        <v>1300</v>
       </c>
       <c r="C156" t="s">
-        <v>1286</v>
+        <v>1316</v>
       </c>
       <c r="D156">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E156" t="s">
         <v>18</v>
       </c>
       <c r="F156" t="s">
-        <v>1287</v>
+        <v>1317</v>
       </c>
       <c r="G156" t="s">
-        <v>1288</v>
+        <v>118</v>
       </c>
       <c r="H156" t="s">
-        <v>1289</v>
+        <v>1318</v>
       </c>
       <c r="I156" t="s">
         <v>34</v>
       </c>
       <c r="J156" t="s">
-        <v>792</v>
+        <v>1045</v>
       </c>
       <c r="K156" t="s">
-        <v>1290</v>
+        <v>1319</v>
       </c>
       <c r="L156" t="s">
-        <v>1291</v>
+        <v>1320</v>
       </c>
       <c r="M156" t="s">
-        <v>1292</v>
+        <v>1307</v>
       </c>
       <c r="N156" t="s">
-        <v>1220</v>
+        <v>1321</v>
       </c>
       <c r="O156" t="s">
-        <v>1293</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -12948,46 +12936,46 @@
         <v>4</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>1270</v>
+        <v>1300</v>
       </c>
       <c r="C157" t="s">
-        <v>1097</v>
+        <v>125</v>
       </c>
       <c r="D157">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E157" t="s">
         <v>18</v>
       </c>
       <c r="F157" t="s">
-        <v>1294</v>
+        <v>1323</v>
       </c>
       <c r="G157" t="s">
-        <v>1295</v>
+        <v>1324</v>
       </c>
       <c r="H157" t="s">
-        <v>1296</v>
+        <v>1325</v>
       </c>
       <c r="I157" t="s">
         <v>34</v>
       </c>
       <c r="J157" t="s">
-        <v>792</v>
+        <v>50</v>
       </c>
       <c r="K157" t="s">
-        <v>1297</v>
+        <v>1326</v>
       </c>
       <c r="L157" t="s">
-        <v>1298</v>
+        <v>1327</v>
       </c>
       <c r="M157" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="N157" t="s">
-        <v>1268</v>
+        <v>89</v>
       </c>
       <c r="O157" t="s">
-        <v>1300</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -12995,49 +12983,49 @@
         <v>1</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1301</v>
+        <v>1329</v>
       </c>
       <c r="C158" t="s">
         <v>174</v>
       </c>
       <c r="D158">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E158" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F158" t="s">
-        <v>1302</v>
+        <v>1330</v>
       </c>
       <c r="G158" t="s">
-        <v>1303</v>
+        <v>1331</v>
       </c>
       <c r="H158" t="s">
-        <v>1304</v>
+        <v>1332</v>
       </c>
       <c r="I158" t="s">
-        <v>1241</v>
+        <v>62</v>
       </c>
       <c r="J158" t="s">
-        <v>1046</v>
+        <v>812</v>
       </c>
       <c r="K158" t="s">
-        <v>1305</v>
+        <v>1333</v>
       </c>
       <c r="L158" t="s">
-        <v>1306</v>
+        <v>1334</v>
       </c>
       <c r="M158" t="s">
-        <v>1307</v>
+        <v>1335</v>
       </c>
       <c r="N158" t="s">
-        <v>1308</v>
+        <v>1336</v>
       </c>
       <c r="O158" t="s">
-        <v>1309</v>
+        <v>62</v>
       </c>
       <c r="P158" t="s">
-        <v>1310</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -13045,46 +13033,46 @@
         <v>2</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>1301</v>
+        <v>1329</v>
       </c>
       <c r="C159" t="s">
-        <v>509</v>
+        <v>443</v>
       </c>
       <c r="D159">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E159" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F159" t="s">
-        <v>1311</v>
+        <v>1338</v>
       </c>
       <c r="G159" t="s">
         <v>34</v>
       </c>
       <c r="H159" t="s">
-        <v>1312</v>
+        <v>1339</v>
       </c>
       <c r="I159" t="s">
         <v>34</v>
       </c>
       <c r="J159" t="s">
-        <v>1046</v>
+        <v>812</v>
       </c>
       <c r="K159" t="s">
-        <v>1313</v>
+        <v>1340</v>
       </c>
       <c r="L159" t="s">
-        <v>1314</v>
+        <v>1341</v>
       </c>
       <c r="M159" t="s">
-        <v>1308</v>
+        <v>1336</v>
       </c>
       <c r="N159" t="s">
-        <v>1315</v>
+        <v>1342</v>
       </c>
       <c r="O159" t="s">
-        <v>1316</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -13092,472 +13080,281 @@
         <v>3</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>1301</v>
+        <v>1329</v>
       </c>
       <c r="C160" t="s">
-        <v>1317</v>
+        <v>1344</v>
       </c>
       <c r="D160">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E160" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F160" t="s">
-        <v>1318</v>
+        <v>1345</v>
       </c>
       <c r="G160" t="s">
-        <v>118</v>
+        <v>1346</v>
       </c>
       <c r="H160" t="s">
-        <v>1319</v>
+        <v>1347</v>
       </c>
       <c r="I160" t="s">
         <v>34</v>
       </c>
       <c r="J160" t="s">
-        <v>1046</v>
+        <v>812</v>
       </c>
       <c r="K160" t="s">
-        <v>1320</v>
+        <v>158</v>
       </c>
       <c r="L160" t="s">
-        <v>1321</v>
+        <v>1348</v>
       </c>
       <c r="M160" t="s">
-        <v>1308</v>
+        <v>1349</v>
       </c>
       <c r="N160" t="s">
-        <v>1322</v>
+        <v>1350</v>
       </c>
       <c r="O160" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15">
       <c r="A161">
         <v>4</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>1301</v>
+        <v>1329</v>
       </c>
       <c r="C161" t="s">
-        <v>125</v>
+        <v>1070</v>
       </c>
       <c r="D161">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E161" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F161" t="s">
-        <v>1324</v>
+        <v>1352</v>
       </c>
       <c r="G161" t="s">
-        <v>1325</v>
+        <v>1353</v>
       </c>
       <c r="H161" t="s">
-        <v>1326</v>
+        <v>1354</v>
       </c>
       <c r="I161" t="s">
         <v>34</v>
       </c>
       <c r="J161" t="s">
-        <v>50</v>
+        <v>812</v>
       </c>
       <c r="K161" t="s">
-        <v>1327</v>
+        <v>1264</v>
       </c>
       <c r="L161" t="s">
-        <v>1328</v>
+        <v>1355</v>
       </c>
       <c r="M161" t="s">
-        <v>1308</v>
+        <v>1356</v>
       </c>
       <c r="N161" t="s">
-        <v>89</v>
+        <v>1357</v>
       </c>
       <c r="O161" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="162" spans="1:16">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15">
       <c r="A162">
         <v>1</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1330</v>
+        <v>1359</v>
       </c>
       <c r="C162" t="s">
         <v>174</v>
       </c>
       <c r="D162">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E162" t="s">
         <v>58</v>
       </c>
       <c r="F162" t="s">
-        <v>1331</v>
+        <v>1360</v>
       </c>
       <c r="G162" t="s">
-        <v>1332</v>
+        <v>1361</v>
       </c>
       <c r="H162" t="s">
-        <v>1333</v>
+        <v>1362</v>
       </c>
       <c r="I162" t="s">
         <v>62</v>
       </c>
       <c r="J162" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="K162" t="s">
-        <v>1334</v>
+        <v>1363</v>
       </c>
       <c r="L162" t="s">
-        <v>1335</v>
+        <v>1364</v>
       </c>
       <c r="M162" t="s">
-        <v>1336</v>
+        <v>1365</v>
       </c>
       <c r="N162" t="s">
-        <v>1337</v>
+        <v>1366</v>
       </c>
       <c r="O162" t="s">
-        <v>62</v>
-      </c>
-      <c r="P162" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
       <c r="A163">
         <v>2</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>1330</v>
+        <v>1359</v>
       </c>
       <c r="C163" t="s">
-        <v>443</v>
+        <v>1368</v>
       </c>
       <c r="D163">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E163" t="s">
         <v>58</v>
       </c>
       <c r="F163" t="s">
-        <v>1339</v>
+        <v>1369</v>
       </c>
       <c r="G163" t="s">
         <v>34</v>
       </c>
       <c r="H163" t="s">
-        <v>1340</v>
+        <v>1370</v>
       </c>
       <c r="I163" t="s">
         <v>34</v>
       </c>
       <c r="J163" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="K163" t="s">
-        <v>1341</v>
+        <v>1371</v>
       </c>
       <c r="L163" t="s">
-        <v>1342</v>
+        <v>1372</v>
       </c>
       <c r="M163" t="s">
-        <v>1337</v>
+        <v>1365</v>
       </c>
       <c r="N163" t="s">
-        <v>1343</v>
+        <v>1314</v>
       </c>
       <c r="O163" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15">
       <c r="A164">
         <v>3</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>1330</v>
+        <v>1359</v>
       </c>
       <c r="C164" t="s">
-        <v>1345</v>
+        <v>1374</v>
       </c>
       <c r="D164">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E164" t="s">
         <v>58</v>
       </c>
       <c r="F164" t="s">
-        <v>1346</v>
+        <v>1375</v>
       </c>
       <c r="G164" t="s">
-        <v>1347</v>
+        <v>1376</v>
       </c>
       <c r="H164" t="s">
-        <v>1348</v>
+        <v>1377</v>
       </c>
       <c r="I164" t="s">
         <v>34</v>
       </c>
       <c r="J164" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="K164" t="s">
-        <v>158</v>
+        <v>1378</v>
       </c>
       <c r="L164" t="s">
-        <v>1349</v>
+        <v>1379</v>
       </c>
       <c r="M164" t="s">
-        <v>1350</v>
+        <v>1365</v>
       </c>
       <c r="N164" t="s">
-        <v>1351</v>
+        <v>1380</v>
       </c>
       <c r="O164" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
       <c r="A165">
         <v>4</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>1330</v>
+        <v>1359</v>
       </c>
       <c r="C165" t="s">
-        <v>1071</v>
+        <v>1382</v>
       </c>
       <c r="D165">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E165" t="s">
         <v>58</v>
       </c>
       <c r="F165" t="s">
-        <v>1353</v>
+        <v>1383</v>
       </c>
       <c r="G165" t="s">
-        <v>1354</v>
+        <v>1384</v>
       </c>
       <c r="H165" t="s">
-        <v>1355</v>
+        <v>1385</v>
       </c>
       <c r="I165" t="s">
         <v>34</v>
       </c>
       <c r="J165" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="K165" t="s">
-        <v>1265</v>
+        <v>1386</v>
       </c>
       <c r="L165" t="s">
-        <v>1356</v>
+        <v>1387</v>
       </c>
       <c r="M165" t="s">
-        <v>1357</v>
+        <v>1388</v>
       </c>
       <c r="N165" t="s">
-        <v>1358</v>
+        <v>1389</v>
       </c>
       <c r="O165" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16">
-      <c r="A166">
-        <v>1</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C166" t="s">
-        <v>174</v>
-      </c>
-      <c r="D166">
-        <v>26</v>
-      </c>
-      <c r="E166" t="s">
-        <v>58</v>
-      </c>
-      <c r="F166" t="s">
-        <v>1361</v>
-      </c>
-      <c r="G166" t="s">
-        <v>1362</v>
-      </c>
-      <c r="H166" t="s">
-        <v>1363</v>
-      </c>
-      <c r="I166" t="s">
-        <v>62</v>
-      </c>
-      <c r="J166" t="s">
-        <v>792</v>
-      </c>
-      <c r="K166" t="s">
-        <v>1364</v>
-      </c>
-      <c r="L166" t="s">
-        <v>1365</v>
-      </c>
-      <c r="M166" t="s">
-        <v>1366</v>
-      </c>
-      <c r="N166" t="s">
-        <v>1367</v>
-      </c>
-      <c r="O166" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16">
-      <c r="A167">
-        <v>2</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C167" t="s">
-        <v>1369</v>
-      </c>
-      <c r="D167">
-        <v>26</v>
-      </c>
-      <c r="E167" t="s">
-        <v>58</v>
-      </c>
-      <c r="F167" t="s">
-        <v>1370</v>
-      </c>
-      <c r="G167" t="s">
-        <v>34</v>
-      </c>
-      <c r="H167" t="s">
-        <v>1371</v>
-      </c>
-      <c r="I167" t="s">
-        <v>34</v>
-      </c>
-      <c r="J167" t="s">
-        <v>792</v>
-      </c>
-      <c r="K167" t="s">
-        <v>1372</v>
-      </c>
-      <c r="L167" t="s">
-        <v>1373</v>
-      </c>
-      <c r="M167" t="s">
-        <v>1366</v>
-      </c>
-      <c r="N167" t="s">
-        <v>1315</v>
-      </c>
-      <c r="O167" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16">
-      <c r="A168">
-        <v>3</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1375</v>
-      </c>
-      <c r="D168">
-        <v>26</v>
-      </c>
-      <c r="E168" t="s">
-        <v>58</v>
-      </c>
-      <c r="F168" t="s">
-        <v>1376</v>
-      </c>
-      <c r="G168" t="s">
-        <v>1377</v>
-      </c>
-      <c r="H168" t="s">
-        <v>1378</v>
-      </c>
-      <c r="I168" t="s">
-        <v>34</v>
-      </c>
-      <c r="J168" t="s">
-        <v>792</v>
-      </c>
-      <c r="K168" t="s">
-        <v>1379</v>
-      </c>
-      <c r="L168" t="s">
-        <v>1380</v>
-      </c>
-      <c r="M168" t="s">
-        <v>1366</v>
-      </c>
-      <c r="N168" t="s">
-        <v>1381</v>
-      </c>
-      <c r="O168" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16">
-      <c r="A169">
-        <v>4</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1383</v>
-      </c>
-      <c r="D169">
-        <v>26</v>
-      </c>
-      <c r="E169" t="s">
-        <v>58</v>
-      </c>
-      <c r="F169" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G169" t="s">
-        <v>1385</v>
-      </c>
-      <c r="H169" t="s">
-        <v>1386</v>
-      </c>
-      <c r="I169" t="s">
-        <v>34</v>
-      </c>
-      <c r="J169" t="s">
-        <v>792</v>
-      </c>
-      <c r="K169" t="s">
-        <v>1387</v>
-      </c>
-      <c r="L169" t="s">
-        <v>1388</v>
-      </c>
-      <c r="M169" t="s">
-        <v>1389</v>
-      </c>
-      <c r="N169" t="s">
         <v>1390</v>
-      </c>
-      <c r="O169" t="s">
-        <v>1391</v>
       </c>
     </row>
   </sheetData>
